--- a/docs/StructureDefinition-VitalSignsBPObservation.xlsx
+++ b/docs/StructureDefinition-VitalSignsBPObservation.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5035" uniqueCount="754">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5035" uniqueCount="756">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-29T18:32:47+00:00</t>
+    <t>2024-03-30T09:34:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1707,6 +1707,9 @@
   <si>
     <t>obs-6
 vs-2</t>
+  </si>
+  <si>
+    <t>1792: target not supported</t>
   </si>
   <si>
     <t>value.nullFlavor</t>
@@ -2201,6 +2204,9 @@
   <si>
     <t>obs-6
 vs-3</t>
+  </si>
+  <si>
+    <t>1793: target not supported</t>
   </si>
   <si>
     <t>Observation.component.interpretation</t>
@@ -10932,7 +10938,7 @@
         <v>106</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>84</v>
+        <v>543</v>
       </c>
       <c r="AL65" t="s" s="2">
         <v>84</v>
@@ -10947,7 +10953,7 @@
         <v>137</v>
       </c>
       <c r="AP65" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="AQ65" t="s" s="2">
         <v>84</v>
@@ -10958,14 +10964,14 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
@@ -10987,16 +10993,16 @@
         <v>183</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="O66" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>84</v>
@@ -11024,10 +11030,10 @@
         <v>188</v>
       </c>
       <c r="Y66" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="Z66" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>84</v>
@@ -11045,7 +11051,7 @@
         <v>84</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>82</v>
@@ -11069,27 +11075,27 @@
         <v>84</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="AO66" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="AP66" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="AQ66" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR66" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -11112,19 +11118,19 @@
         <v>84</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="O67" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>84</v>
@@ -11173,7 +11179,7 @@
         <v>84</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>82</v>
@@ -11200,10 +11206,10 @@
         <v>84</v>
       </c>
       <c r="AO67" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="AP67" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="AQ67" t="s" s="2">
         <v>84</v>
@@ -11214,10 +11220,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -11243,13 +11249,13 @@
         <v>183</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
@@ -11275,13 +11281,13 @@
         <v>84</v>
       </c>
       <c r="X68" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="Y68" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="Z68" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>84</v>
@@ -11299,7 +11305,7 @@
         <v>84</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>82</v>
@@ -11323,27 +11329,27 @@
         <v>84</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="AO68" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="AP68" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="AQ68" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR68" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -11369,16 +11375,16 @@
         <v>183</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="O69" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>84</v>
@@ -11407,7 +11413,7 @@
       </c>
       <c r="Y69" s="2"/>
       <c r="Z69" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>84</v>
@@ -11425,7 +11431,7 @@
         <v>84</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>82</v>
@@ -11440,7 +11446,7 @@
         <v>106</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="AL69" t="s" s="2">
         <v>84</v>
@@ -11452,10 +11458,10 @@
         <v>84</v>
       </c>
       <c r="AO69" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="AP69" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AQ69" t="s" s="2">
         <v>84</v>
@@ -11466,10 +11472,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -11492,16 +11498,16 @@
         <v>84</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
@@ -11551,7 +11557,7 @@
         <v>84</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>82</v>
@@ -11575,27 +11581,27 @@
         <v>84</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="AO70" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="AP70" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="AQ70" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR70" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -11618,16 +11624,16 @@
         <v>84</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -11677,7 +11683,7 @@
         <v>84</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>82</v>
@@ -11692,7 +11698,7 @@
         <v>106</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="AL71" t="s" s="2">
         <v>84</v>
@@ -11701,27 +11707,27 @@
         <v>84</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="AO71" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="AP71" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="AQ71" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR71" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11744,19 +11750,19 @@
         <v>84</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="O72" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>84</v>
@@ -11805,7 +11811,7 @@
         <v>84</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>82</v>
@@ -11817,7 +11823,7 @@
         <v>84</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="AK72" t="s" s="2">
         <v>84</v>
@@ -11832,10 +11838,10 @@
         <v>84</v>
       </c>
       <c r="AO72" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="AP72" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="AQ72" t="s" s="2">
         <v>84</v>
@@ -11846,10 +11852,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11970,10 +11976,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -12096,14 +12102,14 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
@@ -12125,10 +12131,10 @@
         <v>140</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="N75" t="s" s="2">
         <v>143</v>
@@ -12183,7 +12189,7 @@
         <v>84</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>82</v>
@@ -12224,10 +12230,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -12250,13 +12256,13 @@
         <v>84</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" s="2"/>
@@ -12307,7 +12313,7 @@
         <v>84</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>82</v>
@@ -12316,7 +12322,7 @@
         <v>94</v>
       </c>
       <c r="AI76" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="AJ76" t="s" s="2">
         <v>106</v>
@@ -12334,10 +12340,10 @@
         <v>84</v>
       </c>
       <c r="AO76" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="AP76" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="AQ76" t="s" s="2">
         <v>84</v>
@@ -12348,10 +12354,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -12374,13 +12380,13 @@
         <v>84</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -12431,7 +12437,7 @@
         <v>84</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>82</v>
@@ -12440,7 +12446,7 @@
         <v>94</v>
       </c>
       <c r="AI77" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="AJ77" t="s" s="2">
         <v>106</v>
@@ -12458,10 +12464,10 @@
         <v>84</v>
       </c>
       <c r="AO77" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="AP77" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="AQ77" t="s" s="2">
         <v>84</v>
@@ -12472,10 +12478,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -12501,16 +12507,16 @@
         <v>183</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="O78" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>84</v>
@@ -12538,10 +12544,10 @@
         <v>118</v>
       </c>
       <c r="Y78" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="Z78" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="AA78" t="s" s="2">
         <v>84</v>
@@ -12559,7 +12565,7 @@
         <v>84</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>82</v>
@@ -12583,13 +12589,13 @@
         <v>84</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="AO78" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="AP78" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="AQ78" t="s" s="2">
         <v>84</v>
@@ -12600,10 +12606,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -12629,16 +12635,16 @@
         <v>183</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="O79" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>84</v>
@@ -12663,13 +12669,13 @@
         <v>84</v>
       </c>
       <c r="X79" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="Y79" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="Z79" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="AA79" t="s" s="2">
         <v>84</v>
@@ -12687,7 +12693,7 @@
         <v>84</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>82</v>
@@ -12711,13 +12717,13 @@
         <v>84</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="AO79" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="AP79" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="AQ79" t="s" s="2">
         <v>84</v>
@@ -12728,10 +12734,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -12754,17 +12760,17 @@
         <v>84</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="P80" t="s" s="2">
         <v>84</v>
@@ -12813,7 +12819,7 @@
         <v>84</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>82</v>
@@ -12843,7 +12849,7 @@
         <v>84</v>
       </c>
       <c r="AP80" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="AQ80" t="s" s="2">
         <v>84</v>
@@ -12854,10 +12860,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12883,10 +12889,10 @@
         <v>161</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="N81" s="2"/>
       <c r="O81" s="2"/>
@@ -12937,7 +12943,7 @@
         <v>84</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>82</v>
@@ -12964,10 +12970,10 @@
         <v>84</v>
       </c>
       <c r="AO81" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="AP81" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="AQ81" t="s" s="2">
         <v>84</v>
@@ -12978,10 +12984,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -13004,16 +13010,16 @@
         <v>95</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
@@ -13063,7 +13069,7 @@
         <v>84</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>82</v>
@@ -13090,10 +13096,10 @@
         <v>84</v>
       </c>
       <c r="AO82" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="AP82" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="AQ82" t="s" s="2">
         <v>84</v>
@@ -13104,10 +13110,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -13130,16 +13136,16 @@
         <v>95</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
@@ -13189,7 +13195,7 @@
         <v>84</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>82</v>
@@ -13216,10 +13222,10 @@
         <v>84</v>
       </c>
       <c r="AO83" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="AP83" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="AQ83" t="s" s="2">
         <v>84</v>
@@ -13230,10 +13236,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -13241,7 +13247,7 @@
       </c>
       <c r="E84" s="2"/>
       <c r="F84" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="G84" t="s" s="2">
         <v>83</v>
@@ -13256,19 +13262,19 @@
         <v>95</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="O84" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>84</v>
@@ -13305,7 +13311,7 @@
         <v>84</v>
       </c>
       <c r="AB84" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="AC84" s="2"/>
       <c r="AD84" t="s" s="2">
@@ -13315,7 +13321,7 @@
         <v>170</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>82</v>
@@ -13327,7 +13333,7 @@
         <v>84</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="AK84" t="s" s="2">
         <v>84</v>
@@ -13342,10 +13348,10 @@
         <v>84</v>
       </c>
       <c r="AO84" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="AP84" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="AQ84" t="s" s="2">
         <v>84</v>
@@ -13356,10 +13362,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -13480,10 +13486,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -13606,14 +13612,14 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="E87" s="2"/>
       <c r="F87" t="s" s="2">
@@ -13635,10 +13641,10 @@
         <v>140</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="N87" t="s" s="2">
         <v>143</v>
@@ -13693,7 +13699,7 @@
         <v>84</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>82</v>
@@ -13734,10 +13740,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -13763,16 +13769,16 @@
         <v>183</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="O88" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="P88" t="s" s="2">
         <v>84</v>
@@ -13821,7 +13827,7 @@
         <v>84</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>94</v>
@@ -13845,7 +13851,7 @@
         <v>84</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="AO88" t="s" s="2">
         <v>353</v>
@@ -13862,10 +13868,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13891,13 +13897,13 @@
         <v>431</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="O89" t="s" s="2">
         <v>435</v>
@@ -13949,7 +13955,7 @@
         <v>84</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>82</v>
@@ -13958,7 +13964,7 @@
         <v>94</v>
       </c>
       <c r="AI89" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="AJ89" t="s" s="2">
         <v>106</v>
@@ -13973,7 +13979,7 @@
         <v>84</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="AO89" t="s" s="2">
         <v>440</v>
@@ -13990,10 +13996,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -14019,13 +14025,13 @@
         <v>183</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="O90" t="s" s="2">
         <v>539</v>
@@ -14077,7 +14083,7 @@
         <v>84</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>82</v>
@@ -14086,13 +14092,13 @@
         <v>94</v>
       </c>
       <c r="AI90" t="s" s="2">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="AJ90" t="s" s="2">
         <v>106</v>
       </c>
       <c r="AK90" t="s" s="2">
-        <v>84</v>
+        <v>700</v>
       </c>
       <c r="AL90" t="s" s="2">
         <v>84</v>
@@ -14107,7 +14113,7 @@
         <v>137</v>
       </c>
       <c r="AP90" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="AQ90" t="s" s="2">
         <v>84</v>
@@ -14118,14 +14124,14 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="E91" s="2"/>
       <c r="F91" t="s" s="2">
@@ -14147,16 +14153,16 @@
         <v>183</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="O91" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>84</v>
@@ -14184,10 +14190,10 @@
         <v>188</v>
       </c>
       <c r="Y91" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="Z91" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="AA91" t="s" s="2">
         <v>84</v>
@@ -14205,7 +14211,7 @@
         <v>84</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>82</v>
@@ -14229,27 +14235,27 @@
         <v>84</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="AO91" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="AP91" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="AQ91" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR91" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -14275,16 +14281,16 @@
         <v>85</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="O92" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>84</v>
@@ -14333,7 +14339,7 @@
         <v>84</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>82</v>
@@ -14360,10 +14366,10 @@
         <v>84</v>
       </c>
       <c r="AO92" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="AP92" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="AQ92" t="s" s="2">
         <v>84</v>
@@ -14374,13 +14380,13 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="C93" t="s" s="2">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="D93" t="s" s="2">
         <v>84</v>
@@ -14402,19 +14408,19 @@
         <v>95</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="O93" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>84</v>
@@ -14463,7 +14469,7 @@
         <v>84</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>82</v>
@@ -14475,7 +14481,7 @@
         <v>84</v>
       </c>
       <c r="AJ93" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="AK93" t="s" s="2">
         <v>84</v>
@@ -14490,10 +14496,10 @@
         <v>84</v>
       </c>
       <c r="AO93" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="AP93" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="AQ93" t="s" s="2">
         <v>84</v>
@@ -14504,10 +14510,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -14628,10 +14634,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -14754,14 +14760,14 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="E96" s="2"/>
       <c r="F96" t="s" s="2">
@@ -14783,10 +14789,10 @@
         <v>140</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="N96" t="s" s="2">
         <v>143</v>
@@ -14841,7 +14847,7 @@
         <v>84</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>82</v>
@@ -14882,10 +14888,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -14911,16 +14917,16 @@
         <v>183</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="O97" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="P97" t="s" s="2">
         <v>84</v>
@@ -14930,7 +14936,7 @@
         <v>84</v>
       </c>
       <c r="S97" t="s" s="2">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="T97" t="s" s="2">
         <v>84</v>
@@ -14969,7 +14975,7 @@
         <v>84</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>94</v>
@@ -14993,7 +14999,7 @@
         <v>84</v>
       </c>
       <c r="AN97" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="AO97" t="s" s="2">
         <v>353</v>
@@ -15010,10 +15016,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -15039,13 +15045,13 @@
         <v>445</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="O98" t="s" s="2">
         <v>435</v>
@@ -15097,7 +15103,7 @@
         <v>84</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>82</v>
@@ -15106,7 +15112,7 @@
         <v>94</v>
       </c>
       <c r="AI98" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="AJ98" t="s" s="2">
         <v>106</v>
@@ -15121,7 +15127,7 @@
         <v>84</v>
       </c>
       <c r="AN98" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="AO98" t="s" s="2">
         <v>440</v>
@@ -15138,10 +15144,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -15262,10 +15268,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>715</v>
+        <v>717</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>716</v>
+        <v>718</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -15388,10 +15394,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>717</v>
+        <v>719</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>718</v>
+        <v>720</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -15490,7 +15496,7 @@
         <v>106</v>
       </c>
       <c r="AK101" t="s" s="2">
-        <v>719</v>
+        <v>721</v>
       </c>
       <c r="AL101" t="s" s="2">
         <v>459</v>
@@ -15516,10 +15522,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>720</v>
+        <v>722</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>721</v>
+        <v>723</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -15644,10 +15650,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>723</v>
+        <v>725</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -15770,10 +15776,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>724</v>
+        <v>726</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>725</v>
+        <v>727</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -15813,7 +15819,7 @@
       </c>
       <c r="Q104" s="2"/>
       <c r="R104" t="s" s="2">
-        <v>726</v>
+        <v>728</v>
       </c>
       <c r="S104" t="s" s="2">
         <v>84</v>
@@ -15896,10 +15902,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>727</v>
+        <v>729</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>728</v>
+        <v>730</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -15941,7 +15947,7 @@
       </c>
       <c r="Q105" s="2"/>
       <c r="R105" t="s" s="2">
-        <v>729</v>
+        <v>731</v>
       </c>
       <c r="S105" t="s" s="2">
         <v>84</v>
@@ -16024,10 +16030,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>730</v>
+        <v>732</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -16053,13 +16059,13 @@
         <v>183</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="N106" t="s" s="2">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="O106" t="s" s="2">
         <v>539</v>
@@ -16111,7 +16117,7 @@
         <v>84</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>82</v>
@@ -16120,7 +16126,7 @@
         <v>94</v>
       </c>
       <c r="AI106" t="s" s="2">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="AJ106" t="s" s="2">
         <v>106</v>
@@ -16141,7 +16147,7 @@
         <v>137</v>
       </c>
       <c r="AP106" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="AQ106" t="s" s="2">
         <v>84</v>
@@ -16152,14 +16158,14 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>731</v>
+        <v>733</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="E107" s="2"/>
       <c r="F107" t="s" s="2">
@@ -16181,16 +16187,16 @@
         <v>183</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="N107" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="O107" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="P107" t="s" s="2">
         <v>84</v>
@@ -16218,10 +16224,10 @@
         <v>188</v>
       </c>
       <c r="Y107" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="Z107" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="AA107" t="s" s="2">
         <v>84</v>
@@ -16239,7 +16245,7 @@
         <v>84</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>82</v>
@@ -16263,27 +16269,27 @@
         <v>84</v>
       </c>
       <c r="AN107" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="AO107" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="AP107" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="AQ107" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR107" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -16309,16 +16315,16 @@
         <v>85</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="N108" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="O108" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="P108" t="s" s="2">
         <v>84</v>
@@ -16367,7 +16373,7 @@
         <v>84</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>82</v>
@@ -16394,10 +16400,10 @@
         <v>84</v>
       </c>
       <c r="AO108" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="AP108" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="AQ108" t="s" s="2">
         <v>84</v>
@@ -16408,13 +16414,13 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>733</v>
+        <v>735</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="C109" t="s" s="2">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="D109" t="s" s="2">
         <v>84</v>
@@ -16436,19 +16442,19 @@
         <v>95</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>735</v>
+        <v>737</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="N109" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="O109" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="P109" t="s" s="2">
         <v>84</v>
@@ -16497,7 +16503,7 @@
         <v>84</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>82</v>
@@ -16509,7 +16515,7 @@
         <v>84</v>
       </c>
       <c r="AJ109" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="AK109" t="s" s="2">
         <v>84</v>
@@ -16524,10 +16530,10 @@
         <v>84</v>
       </c>
       <c r="AO109" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="AP109" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="AQ109" t="s" s="2">
         <v>84</v>
@@ -16538,10 +16544,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>736</v>
+        <v>738</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -16662,10 +16668,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>737</v>
+        <v>739</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -16788,14 +16794,14 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>738</v>
+        <v>740</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="E112" s="2"/>
       <c r="F112" t="s" s="2">
@@ -16817,10 +16823,10 @@
         <v>140</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="N112" t="s" s="2">
         <v>143</v>
@@ -16875,7 +16881,7 @@
         <v>84</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>82</v>
@@ -16916,10 +16922,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>739</v>
+        <v>741</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -16945,16 +16951,16 @@
         <v>183</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>740</v>
+        <v>742</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="N113" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="O113" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="P113" t="s" s="2">
         <v>84</v>
@@ -16964,7 +16970,7 @@
         <v>84</v>
       </c>
       <c r="S113" t="s" s="2">
-        <v>741</v>
+        <v>743</v>
       </c>
       <c r="T113" t="s" s="2">
         <v>84</v>
@@ -17003,7 +17009,7 @@
         <v>84</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>94</v>
@@ -17027,7 +17033,7 @@
         <v>84</v>
       </c>
       <c r="AN113" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="AO113" t="s" s="2">
         <v>353</v>
@@ -17044,10 +17050,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>742</v>
+        <v>744</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -17073,13 +17079,13 @@
         <v>445</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="N114" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="O114" t="s" s="2">
         <v>435</v>
@@ -17131,7 +17137,7 @@
         <v>84</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>82</v>
@@ -17140,7 +17146,7 @@
         <v>94</v>
       </c>
       <c r="AI114" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="AJ114" t="s" s="2">
         <v>106</v>
@@ -17155,7 +17161,7 @@
         <v>84</v>
       </c>
       <c r="AN114" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="AO114" t="s" s="2">
         <v>440</v>
@@ -17172,10 +17178,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>743</v>
+        <v>745</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -17296,10 +17302,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>744</v>
+        <v>746</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>716</v>
+        <v>718</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -17422,10 +17428,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>745</v>
+        <v>747</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>718</v>
+        <v>720</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -17524,7 +17530,7 @@
         <v>106</v>
       </c>
       <c r="AK117" t="s" s="2">
-        <v>746</v>
+        <v>748</v>
       </c>
       <c r="AL117" t="s" s="2">
         <v>459</v>
@@ -17550,10 +17556,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>747</v>
+        <v>749</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>721</v>
+        <v>723</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -17678,10 +17684,10 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>748</v>
+        <v>750</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>723</v>
+        <v>725</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -17804,10 +17810,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>749</v>
+        <v>751</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>725</v>
+        <v>727</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -17847,7 +17853,7 @@
       </c>
       <c r="Q120" s="2"/>
       <c r="R120" t="s" s="2">
-        <v>726</v>
+        <v>728</v>
       </c>
       <c r="S120" t="s" s="2">
         <v>84</v>
@@ -17930,10 +17936,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>750</v>
+        <v>752</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>728</v>
+        <v>730</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -17975,7 +17981,7 @@
       </c>
       <c r="Q121" s="2"/>
       <c r="R121" t="s" s="2">
-        <v>729</v>
+        <v>731</v>
       </c>
       <c r="S121" t="s" s="2">
         <v>84</v>
@@ -18058,10 +18064,10 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>751</v>
+        <v>753</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -18087,13 +18093,13 @@
         <v>183</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="N122" t="s" s="2">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="O122" t="s" s="2">
         <v>539</v>
@@ -18145,7 +18151,7 @@
         <v>84</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>82</v>
@@ -18154,7 +18160,7 @@
         <v>94</v>
       </c>
       <c r="AI122" t="s" s="2">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="AJ122" t="s" s="2">
         <v>106</v>
@@ -18175,7 +18181,7 @@
         <v>137</v>
       </c>
       <c r="AP122" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="AQ122" t="s" s="2">
         <v>84</v>
@@ -18186,14 +18192,14 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>752</v>
+        <v>754</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="E123" s="2"/>
       <c r="F123" t="s" s="2">
@@ -18215,16 +18221,16 @@
         <v>183</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="N123" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="O123" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="P123" t="s" s="2">
         <v>84</v>
@@ -18252,10 +18258,10 @@
         <v>188</v>
       </c>
       <c r="Y123" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="Z123" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="AA123" t="s" s="2">
         <v>84</v>
@@ -18273,7 +18279,7 @@
         <v>84</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>82</v>
@@ -18297,27 +18303,27 @@
         <v>84</v>
       </c>
       <c r="AN123" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="AO123" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="AP123" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="AQ123" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR123" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>753</v>
+        <v>755</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -18343,16 +18349,16 @@
         <v>85</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="N124" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="O124" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="P124" t="s" s="2">
         <v>84</v>
@@ -18401,7 +18407,7 @@
         <v>84</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>82</v>
@@ -18428,10 +18434,10 @@
         <v>84</v>
       </c>
       <c r="AO124" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="AP124" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="AQ124" t="s" s="2">
         <v>84</v>

--- a/docs/StructureDefinition-VitalSignsBPObservation.xlsx
+++ b/docs/StructureDefinition-VitalSignsBPObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.34.0</t>
+    <t>0.36.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-30T09:34:15+00:00</t>
+    <t>2024-04-03T07:33:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1709,7 +1709,7 @@
 vs-2</t>
   </si>
   <si>
-    <t>1792: target not supported</t>
+    <t>1793: target not supported</t>
   </si>
   <si>
     <t>value.nullFlavor</t>
@@ -2206,7 +2206,7 @@
 vs-3</t>
   </si>
   <si>
-    <t>1793: target not supported</t>
+    <t>1794: target not supported</t>
   </si>
   <si>
     <t>Observation.component.interpretation</t>

--- a/docs/StructureDefinition-VitalSignsBPObservation.xlsx
+++ b/docs/StructureDefinition-VitalSignsBPObservation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-03T07:33:38+00:00</t>
+    <t>2024-04-03T08:58:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsBPObservation.xlsx
+++ b/docs/StructureDefinition-VitalSignsBPObservation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-03T08:58:56+00:00</t>
+    <t>2024-04-10T18:17:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for VistA file GMRV VITAL MEASUREMENT (#120.5) to us-core-blood-pressure</t>
+    <t>This StructureDefinition contains the maps for VistA file GMRV VITAL MEASUREMENT (120.5) to us-core-blood-pressure</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -662,7 +662,7 @@
     <t>Identifier.value</t>
   </si>
   <si>
-    <t>660: source value from GMRV VITAL MEASUREMENT - IEN (#120.5-.001)</t>
+    <t>660: source value from GMRV VITAL MEASUREMENT - IEN (120.5-.001)</t>
   </si>
   <si>
     <t>CX.1 / EI.1</t>
@@ -794,7 +794,7 @@
     <t>http://hl7.org/fhir/ValueSet/observation-status|4.0.1</t>
   </si>
   <si>
-    <t>656: fixed value = #entered-in-error when GMRV VITAL MEASUREMENT - REASON ENTERED IN ERROR (#120.5-4) case not null</t>
+    <t>656: fixed value = #entered-in-error when GMRV VITAL MEASUREMENT - REASON ENTERED IN ERROR (120.5-4) case not null</t>
   </si>
   <si>
     <t>Event.status</t>
@@ -1141,7 +1141,7 @@
     <t>http://va.gov/fhir/ValueSet/VSVFVitalsCodes</t>
   </si>
   <si>
-    <t>661: terminologyMaps using VF_VitalsCodes on GMRV VITAL MEASUREMENT - VITAL TYPE (#120.5-.03)</t>
+    <t>661: terminologyMaps using VF_VitalsCodes on GMRV VITAL MEASUREMENT - VITAL TYPE (120.5-.03)</t>
   </si>
   <si>
     <t>Observation.code.text</t>
@@ -1166,7 +1166,7 @@
     <t>Observations have no value if you don't know who or what they're about.</t>
   </si>
   <si>
-    <t>659: reference from GMRV VITAL MEASUREMENT - PATIENT (#120.5-.02)</t>
+    <t>659: reference from GMRV VITAL MEASUREMENT - PATIENT (120.5-.02)</t>
   </si>
   <si>
     <t>Event.subject</t>
@@ -1292,7 +1292,7 @@
 </t>
   </si>
   <si>
-    <t>657: source value from GMRV VITAL MEASUREMENT - DATE/TIME VITALS TAKEN (#120.5-.01)</t>
+    <t>657: source value from GMRV VITAL MEASUREMENT - DATE/TIME VITALS TAKEN (120.5-.01)</t>
   </si>
   <si>
     <t>Vital.VitalSign.VitalSignTakenDateTime,Vital.VitalSignQualifier.VitalSignTakenDateTime</t>
@@ -1314,7 +1314,7 @@
     <t>For Observations that don’t require review and verification, it may be the same as the [`lastUpdated` ](http://hl7.org/fhir/resource-definitions.html#Meta.lastUpdated) time of the resource itself.  For Observations that do require review and verification for certain updates, it might not be the same as the `lastUpdated` time of the resource itself due to a non-clinically significant update that doesn’t require the new version to be reviewed and verified again.</t>
   </si>
   <si>
-    <t>652: source value from GMRV VITAL MEASUREMENT - DATE/TIME VITALS ENTERED (#120.5-.04)</t>
+    <t>652: source value from GMRV VITAL MEASUREMENT - DATE/TIME VITALS ENTERED (120.5-.04)</t>
   </si>
   <si>
     <t>Vital.VitalSign.VitalSignEnteredDateTime</t>
@@ -1345,7 +1345,7 @@
     <t>May give a degree of confidence in the observation and also indicates where follow-up questions should be directed.</t>
   </si>
   <si>
-    <t>1653: reference from GMRV VITAL MEASUREMENT - HOSPITAL LOCATION (#120.5-.05)</t>
+    <t>1653: reference from GMRV VITAL MEASUREMENT - HOSPITAL LOCATION (120.5-.05)</t>
   </si>
   <si>
     <t>Event.performer.actor</t>
@@ -1448,7 +1448,7 @@
     <t>Quantity.value</t>
   </si>
   <si>
-    <t>664: source value from GMRV VITAL MEASUREMENT - RATE (#120.5-1.2) case VUID not = 4500634</t>
+    <t>664: source value from GMRV VITAL MEASUREMENT - RATE (120.5-1.2) case VUID not = 4500634</t>
   </si>
   <si>
     <t>Vital.VitalSign.Diastolic,Vital.VitalSign.Systolic,Vital.VitalSign.VitalResult,Vital.VitalSign.VitalResultNumeric</t>
@@ -1563,7 +1563,7 @@
     <t>Quantity.code</t>
   </si>
   <si>
-    <t>665: transform using VF_VitalsUnits on GMRV VITAL MEASUREMENT - VITAL TYPE (#120.5-.03)</t>
+    <t>665: transform using VF_VitalsUnits on GMRV VITAL MEASUREMENT - VITAL TYPE (120.5-.03)</t>
   </si>
   <si>
     <t>PQ.code, MO.currency, PQ.translation.code</t>
@@ -1829,7 +1829,7 @@
     <t>http://va.gov/fhir/ValueSet/VSVFVitalsMethod</t>
   </si>
   <si>
-    <t>867: terminologyMaps using VF_VitalsMethod on GMRV VITAL MEASUREMENT - QUALIFIER (#120.5-5)</t>
+    <t>867: terminologyMaps using VF_VitalsMethod on GMRV VITAL MEASUREMENT - QUALIFIER (120.5-5)</t>
   </si>
   <si>
     <t>OBX-17</t>
@@ -1882,7 +1882,7 @@
     <t>Note that this is not meant to represent a device involved in the transmission of the result, e.g., a gateway.  Such devices may be documented using the Provenance resource where relevant.</t>
   </si>
   <si>
-    <t>1655: reference from GMRV VITAL MEASUREMENT - QUALIFIER &gt; GMRV VITAL QUALIFIER - VUID (#120.5-5 &gt; 120.52-99.99)</t>
+    <t>1655: reference from GMRV VITAL MEASUREMENT - QUALIFIER &gt; GMRV VITAL QUALIFIER - VUID (120.5-5 &gt; 120.52-99.99)</t>
   </si>
   <si>
     <t>&lt; 49062001 |Device|</t>
@@ -2274,7 +2274,7 @@
     <t>Observation.component.value[x].value</t>
   </si>
   <si>
-    <t>666: transform using Split_rate_value.Systolic() on GMRV VITAL MEASUREMENT - RATE (#120.5-1.2) case VUID = 4500634</t>
+    <t>666: transform using Split_rate_value.Systolic() on GMRV VITAL MEASUREMENT - RATE (120.5-1.2) case VUID = 4500634</t>
   </si>
   <si>
     <t>Observation.component:systolic.value[x].comparator</t>
@@ -2360,7 +2360,7 @@
     <t>Observation.component:diastolic.value[x].value</t>
   </si>
   <si>
-    <t>667: transform using Split_rate_value.Diastolic() on GMRV VITAL MEASUREMENT - RATE (#120.5-1.2) case VUID = 4500634</t>
+    <t>667: transform using Split_rate_value.Diastolic() on GMRV VITAL MEASUREMENT - RATE (120.5-1.2) case VUID = 4500634</t>
   </si>
   <si>
     <t>Observation.component:diastolic.value[x].comparator</t>
@@ -2736,7 +2736,7 @@
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="118.1171875" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="116.58203125" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="98.75" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="29.69921875" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="247.40625" customWidth="true" bestFit="true"/>

--- a/docs/StructureDefinition-VitalSignsBPObservation.xlsx
+++ b/docs/StructureDefinition-VitalSignsBPObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.36.0</t>
+    <t>0.37.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-10T18:17:58+00:00</t>
+    <t>2024-04-10T21:21:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsBPObservation.xlsx
+++ b/docs/StructureDefinition-VitalSignsBPObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.37.0</t>
+    <t>0.38.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-10T21:21:54+00:00</t>
+    <t>2024-04-12T10:04:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -72,7 +72,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>No display for ContactDetail</t>
+    <t>VA (https://www.va.gov)</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/docs/StructureDefinition-VitalSignsBPObservation.xlsx
+++ b/docs/StructureDefinition-VitalSignsBPObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.38.0</t>
+    <t>0.39.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-12T10:04:01+00:00</t>
+    <t>2024-04-12T16:57:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsBPObservation.xlsx
+++ b/docs/StructureDefinition-VitalSignsBPObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.39.0</t>
+    <t>0.40.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-12T16:57:46+00:00</t>
+    <t>2024-04-13T07:20:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsBPObservation.xlsx
+++ b/docs/StructureDefinition-VitalSignsBPObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.40.0</t>
+    <t>0.41.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-13T07:20:06+00:00</t>
+    <t>2024-04-21T15:38:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsBPObservation.xlsx
+++ b/docs/StructureDefinition-VitalSignsBPObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.41.0</t>
+    <t>0.42.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-21T15:38:45+00:00</t>
+    <t>2024-04-22T07:04:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsBPObservation.xlsx
+++ b/docs/StructureDefinition-VitalSignsBPObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.42.0</t>
+    <t>0.43.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-22T07:04:34+00:00</t>
+    <t>2024-04-24T08:47:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsBPObservation.xlsx
+++ b/docs/StructureDefinition-VitalSignsBPObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.43.0</t>
+    <t>0.44.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-24T08:47:54+00:00</t>
+    <t>2024-04-25T08:17:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsBPObservation.xlsx
+++ b/docs/StructureDefinition-VitalSignsBPObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.45.0</t>
+    <t>0.46.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-01T09:37:14+00:00</t>
+    <t>2024-05-01T10:34:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsBPObservation.xlsx
+++ b/docs/StructureDefinition-VitalSignsBPObservation.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5430" uniqueCount="781">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5430" uniqueCount="784">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.46.0</t>
+    <t>0.47.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-01T10:34:27+00:00</t>
+    <t>2024-05-04T09:18:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1225,6 +1225,9 @@
     <t>661: terminologyMaps using VF_VitalsCodes on GMRV VITAL MEASUREMENT - VITAL TYPE (120.5-.03)</t>
   </si>
   <si>
+    <t>Vital.VitalSign.VitalTypeIEN</t>
+  </si>
+  <si>
     <t>Observation.code.text</t>
   </si>
   <si>
@@ -1250,6 +1253,9 @@
     <t>659: reference from GMRV VITAL MEASUREMENT - PATIENT (120.5-.02)</t>
   </si>
   <si>
+    <t>Vital.VitalSign.PatientIEN</t>
+  </si>
+  <si>
     <t>Event.subject</t>
   </si>
   <si>
@@ -1427,6 +1433,9 @@
   </si>
   <si>
     <t>1653: reference from GMRV VITAL MEASUREMENT - HOSPITAL LOCATION (120.5-.05)</t>
+  </si>
+  <si>
+    <t>Vital.VitalSign.LocationIEN</t>
   </si>
   <si>
     <t>Event.performer.actor</t>
@@ -8352,7 +8361,7 @@
         <v>387</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>84</v>
+        <v>388</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>84</v>
@@ -8375,10 +8384,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -8503,10 +8512,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -8529,19 +8538,19 @@
         <v>95</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>84</v>
@@ -8590,7 +8599,7 @@
         <v>84</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>82</v>
@@ -8605,25 +8614,25 @@
         <v>106</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>84</v>
+        <v>397</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="AP46" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="AQ46" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="AR46" t="s" s="2">
         <v>84</v>
@@ -8631,10 +8640,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8657,16 +8666,16 @@
         <v>95</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -8716,7 +8725,7 @@
         <v>84</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>82</v>
@@ -8746,10 +8755,10 @@
         <v>379</v>
       </c>
       <c r="AP47" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="AQ47" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="AR47" t="s" s="2">
         <v>84</v>
@@ -8757,14 +8766,14 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
@@ -8783,19 +8792,19 @@
         <v>95</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>84</v>
@@ -8844,7 +8853,7 @@
         <v>84</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>82</v>
@@ -8865,19 +8874,19 @@
         <v>84</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="AQ48" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="AR48" t="s" s="2">
         <v>84</v>
@@ -8885,14 +8894,14 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
@@ -8911,19 +8920,19 @@
         <v>95</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>84</v>
@@ -8960,7 +8969,7 @@
         <v>84</v>
       </c>
       <c r="AB49" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="AC49" s="2"/>
       <c r="AD49" t="s" s="2">
@@ -8970,7 +8979,7 @@
         <v>143</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>82</v>
@@ -8979,10 +8988,10 @@
         <v>94</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>84</v>
@@ -8991,19 +9000,19 @@
         <v>84</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="AQ49" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="AR49" t="s" s="2">
         <v>84</v>
@@ -9011,16 +9020,16 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="C50" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="D50" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
@@ -9039,19 +9048,19 @@
         <v>95</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>84</v>
@@ -9100,7 +9109,7 @@
         <v>84</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>82</v>
@@ -9109,31 +9118,31 @@
         <v>94</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="AQ50" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="AR50" t="s" s="2">
         <v>84</v>
@@ -9141,10 +9150,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -9167,16 +9176,16 @@
         <v>95</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -9226,7 +9235,7 @@
         <v>84</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>82</v>
@@ -9241,10 +9250,10 @@
         <v>106</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>84</v>
@@ -9253,13 +9262,13 @@
         <v>84</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="AQ51" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="AR51" t="s" s="2">
         <v>84</v>
@@ -9267,10 +9276,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -9293,17 +9302,17 @@
         <v>95</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>84</v>
@@ -9352,7 +9361,7 @@
         <v>84</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>82</v>
@@ -9367,25 +9376,25 @@
         <v>106</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>84</v>
+        <v>454</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="AQ52" t="s" s="2">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="AR52" t="s" s="2">
         <v>84</v>
@@ -9393,10 +9402,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -9419,19 +9428,19 @@
         <v>95</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="O53" t="s" s="2">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>84</v>
@@ -9459,16 +9468,16 @@
         <v>214</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AB53" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="AC53" s="2"/>
       <c r="AD53" t="s" s="2">
@@ -9478,7 +9487,7 @@
         <v>143</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>82</v>
@@ -9487,7 +9496,7 @@
         <v>94</v>
       </c>
       <c r="AI53" t="s" s="2">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="AJ53" t="s" s="2">
         <v>106</v>
@@ -9502,30 +9511,30 @@
         <v>84</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="AP53" t="s" s="2">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="AQ53" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR53" t="s" s="2">
-        <v>468</v>
+        <v>471</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="C54" t="s" s="2">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="D54" t="s" s="2">
         <v>84</v>
@@ -9547,19 +9556,19 @@
         <v>95</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>84</v>
@@ -9587,10 +9596,10 @@
         <v>214</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>84</v>
@@ -9608,7 +9617,7 @@
         <v>84</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>82</v>
@@ -9617,7 +9626,7 @@
         <v>94</v>
       </c>
       <c r="AI54" t="s" s="2">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="AJ54" t="s" s="2">
         <v>106</v>
@@ -9632,27 +9641,27 @@
         <v>84</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="AP54" t="s" s="2">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="AQ54" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR54" t="s" s="2">
-        <v>468</v>
+        <v>471</v>
       </c>
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -9773,10 +9782,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9899,10 +9908,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9925,19 +9934,19 @@
         <v>95</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="O57" t="s" s="2">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>84</v>
@@ -9986,7 +9995,7 @@
         <v>84</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>82</v>
@@ -10001,10 +10010,10 @@
         <v>106</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>84</v>
@@ -10013,10 +10022,10 @@
         <v>84</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="AP57" t="s" s="2">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="AQ57" t="s" s="2">
         <v>84</v>
@@ -10027,10 +10036,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -10056,20 +10065,20 @@
         <v>114</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" t="s" s="2">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>84</v>
       </c>
       <c r="Q58" t="s" s="2">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="R58" t="s" s="2">
         <v>84</v>
@@ -10093,10 +10102,10 @@
         <v>174</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>84</v>
@@ -10114,7 +10123,7 @@
         <v>84</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>82</v>
@@ -10141,10 +10150,10 @@
         <v>84</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="AP58" t="s" s="2">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="AQ58" t="s" s="2">
         <v>84</v>
@@ -10155,10 +10164,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -10184,14 +10193,14 @@
         <v>196</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" t="s" s="2">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>84</v>
@@ -10240,7 +10249,7 @@
         <v>84</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>82</v>
@@ -10267,10 +10276,10 @@
         <v>84</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="AP59" t="s" s="2">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="AQ59" t="s" s="2">
         <v>84</v>
@@ -10281,10 +10290,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -10310,14 +10319,14 @@
         <v>108</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" t="s" s="2">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>84</v>
@@ -10366,7 +10375,7 @@
         <v>84</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>82</v>
@@ -10375,7 +10384,7 @@
         <v>94</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="AJ60" t="s" s="2">
         <v>106</v>
@@ -10393,10 +10402,10 @@
         <v>84</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="AP60" t="s" s="2">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="AQ60" t="s" s="2">
         <v>84</v>
@@ -10407,10 +10416,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -10436,16 +10445,16 @@
         <v>114</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="O61" t="s" s="2">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>84</v>
@@ -10494,7 +10503,7 @@
         <v>84</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>82</v>
@@ -10509,10 +10518,10 @@
         <v>106</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>84</v>
+        <v>388</v>
       </c>
       <c r="AM61" t="s" s="2">
         <v>84</v>
@@ -10521,10 +10530,10 @@
         <v>84</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="AP61" t="s" s="2">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="AQ61" t="s" s="2">
         <v>84</v>
@@ -10535,10 +10544,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -10564,10 +10573,10 @@
         <v>196</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -10659,10 +10668,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10781,13 +10790,13 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="C64" t="s" s="2">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="D64" t="s" s="2">
         <v>84</v>
@@ -10809,16 +10818,16 @@
         <v>84</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -10909,10 +10918,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -11033,10 +11042,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -11157,10 +11166,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -11200,7 +11209,7 @@
       </c>
       <c r="Q67" s="2"/>
       <c r="R67" t="s" s="2">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="S67" t="s" s="2">
         <v>84</v>
@@ -11283,10 +11292,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -11309,7 +11318,7 @@
         <v>84</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>545</v>
+        <v>548</v>
       </c>
       <c r="L68" t="s" s="2">
         <v>172</v>
@@ -11327,7 +11336,7 @@
         <v>84</v>
       </c>
       <c r="S68" t="s" s="2">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="T68" t="s" s="2">
         <v>84</v>
@@ -11407,10 +11416,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -11436,10 +11445,10 @@
         <v>196</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -11490,7 +11499,7 @@
         <v>84</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>82</v>
@@ -11531,10 +11540,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -11560,16 +11569,16 @@
         <v>171</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>554</v>
+        <v>557</v>
       </c>
       <c r="O70" t="s" s="2">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>84</v>
@@ -11597,10 +11606,10 @@
         <v>214</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="Z70" t="s" s="2">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>84</v>
@@ -11618,7 +11627,7 @@
         <v>84</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>82</v>
@@ -11627,13 +11636,13 @@
         <v>94</v>
       </c>
       <c r="AI70" t="s" s="2">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="AJ70" t="s" s="2">
         <v>106</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="AL70" t="s" s="2">
         <v>84</v>
@@ -11648,7 +11657,7 @@
         <v>137</v>
       </c>
       <c r="AP70" t="s" s="2">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="AQ70" t="s" s="2">
         <v>84</v>
@@ -11659,14 +11668,14 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
@@ -11688,16 +11697,16 @@
         <v>171</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="O71" t="s" s="2">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>84</v>
@@ -11725,10 +11734,10 @@
         <v>214</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>567</v>
+        <v>570</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>84</v>
@@ -11746,7 +11755,7 @@
         <v>84</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>82</v>
@@ -11770,27 +11779,27 @@
         <v>84</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>569</v>
+        <v>572</v>
       </c>
       <c r="AO71" t="s" s="2">
-        <v>570</v>
+        <v>573</v>
       </c>
       <c r="AP71" t="s" s="2">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="AQ71" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR71" t="s" s="2">
-        <v>572</v>
+        <v>575</v>
       </c>
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>573</v>
+        <v>576</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>573</v>
+        <v>576</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11813,19 +11822,19 @@
         <v>84</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="O72" t="s" s="2">
-        <v>578</v>
+        <v>581</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>84</v>
@@ -11874,7 +11883,7 @@
         <v>84</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>573</v>
+        <v>576</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>82</v>
@@ -11901,10 +11910,10 @@
         <v>84</v>
       </c>
       <c r="AO72" t="s" s="2">
-        <v>579</v>
+        <v>582</v>
       </c>
       <c r="AP72" t="s" s="2">
-        <v>580</v>
+        <v>583</v>
       </c>
       <c r="AQ72" t="s" s="2">
         <v>84</v>
@@ -11915,10 +11924,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>581</v>
+        <v>584</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>581</v>
+        <v>584</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11944,13 +11953,13 @@
         <v>171</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>582</v>
+        <v>585</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>583</v>
+        <v>586</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
@@ -11976,13 +11985,13 @@
         <v>84</v>
       </c>
       <c r="X73" t="s" s="2">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="Y73" t="s" s="2">
-        <v>586</v>
+        <v>589</v>
       </c>
       <c r="Z73" t="s" s="2">
-        <v>587</v>
+        <v>590</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>84</v>
@@ -12000,7 +12009,7 @@
         <v>84</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>581</v>
+        <v>584</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>82</v>
@@ -12024,27 +12033,27 @@
         <v>84</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="AO73" t="s" s="2">
-        <v>589</v>
+        <v>592</v>
       </c>
       <c r="AP73" t="s" s="2">
-        <v>590</v>
+        <v>593</v>
       </c>
       <c r="AQ73" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR73" t="s" s="2">
-        <v>591</v>
+        <v>594</v>
       </c>
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>592</v>
+        <v>595</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>592</v>
+        <v>595</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -12070,16 +12079,16 @@
         <v>171</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>593</v>
+        <v>596</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>595</v>
+        <v>598</v>
       </c>
       <c r="O74" t="s" s="2">
-        <v>596</v>
+        <v>599</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>84</v>
@@ -12108,7 +12117,7 @@
       </c>
       <c r="Y74" s="2"/>
       <c r="Z74" t="s" s="2">
-        <v>597</v>
+        <v>600</v>
       </c>
       <c r="AA74" t="s" s="2">
         <v>84</v>
@@ -12126,7 +12135,7 @@
         <v>84</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>592</v>
+        <v>595</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>82</v>
@@ -12141,7 +12150,7 @@
         <v>106</v>
       </c>
       <c r="AK74" t="s" s="2">
-        <v>598</v>
+        <v>601</v>
       </c>
       <c r="AL74" t="s" s="2">
         <v>84</v>
@@ -12153,10 +12162,10 @@
         <v>84</v>
       </c>
       <c r="AO74" t="s" s="2">
-        <v>599</v>
+        <v>602</v>
       </c>
       <c r="AP74" t="s" s="2">
-        <v>600</v>
+        <v>603</v>
       </c>
       <c r="AQ74" t="s" s="2">
         <v>84</v>
@@ -12167,10 +12176,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>601</v>
+        <v>604</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>601</v>
+        <v>604</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -12193,16 +12202,16 @@
         <v>84</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>602</v>
+        <v>605</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>603</v>
+        <v>606</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>604</v>
+        <v>607</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>605</v>
+        <v>608</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -12252,7 +12261,7 @@
         <v>84</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>601</v>
+        <v>604</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>82</v>
@@ -12276,27 +12285,27 @@
         <v>84</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="AO75" t="s" s="2">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="AP75" t="s" s="2">
-        <v>608</v>
+        <v>611</v>
       </c>
       <c r="AQ75" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR75" t="s" s="2">
-        <v>609</v>
+        <v>612</v>
       </c>
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -12319,16 +12328,16 @@
         <v>84</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>611</v>
+        <v>614</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>612</v>
+        <v>615</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>613</v>
+        <v>616</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>614</v>
+        <v>617</v>
       </c>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
@@ -12378,7 +12387,7 @@
         <v>84</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>82</v>
@@ -12402,27 +12411,27 @@
         <v>84</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>615</v>
+        <v>618</v>
       </c>
       <c r="AO76" t="s" s="2">
-        <v>616</v>
+        <v>619</v>
       </c>
       <c r="AP76" t="s" s="2">
-        <v>617</v>
+        <v>620</v>
       </c>
       <c r="AQ76" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR76" t="s" s="2">
-        <v>618</v>
+        <v>621</v>
       </c>
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>619</v>
+        <v>622</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>619</v>
+        <v>622</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -12445,19 +12454,19 @@
         <v>84</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>620</v>
+        <v>623</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>621</v>
+        <v>624</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>622</v>
+        <v>625</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>623</v>
+        <v>626</v>
       </c>
       <c r="O77" t="s" s="2">
-        <v>624</v>
+        <v>627</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>84</v>
@@ -12506,7 +12515,7 @@
         <v>84</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>619</v>
+        <v>622</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>82</v>
@@ -12518,7 +12527,7 @@
         <v>84</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>625</v>
+        <v>628</v>
       </c>
       <c r="AK77" t="s" s="2">
         <v>84</v>
@@ -12533,10 +12542,10 @@
         <v>84</v>
       </c>
       <c r="AO77" t="s" s="2">
-        <v>626</v>
+        <v>629</v>
       </c>
       <c r="AP77" t="s" s="2">
-        <v>627</v>
+        <v>630</v>
       </c>
       <c r="AQ77" t="s" s="2">
         <v>84</v>
@@ -12547,10 +12556,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -12671,10 +12680,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>629</v>
+        <v>632</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>629</v>
+        <v>632</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -12797,14 +12806,14 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>630</v>
+        <v>633</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>630</v>
+        <v>633</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
-        <v>631</v>
+        <v>634</v>
       </c>
       <c r="E80" s="2"/>
       <c r="F80" t="s" s="2">
@@ -12826,10 +12835,10 @@
         <v>139</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="N80" t="s" s="2">
         <v>183</v>
@@ -12884,7 +12893,7 @@
         <v>84</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>634</v>
+        <v>637</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>82</v>
@@ -12925,10 +12934,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>635</v>
+        <v>638</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>635</v>
+        <v>638</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12951,13 +12960,13 @@
         <v>84</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>636</v>
+        <v>639</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>637</v>
+        <v>640</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>638</v>
+        <v>641</v>
       </c>
       <c r="N81" s="2"/>
       <c r="O81" s="2"/>
@@ -13008,7 +13017,7 @@
         <v>84</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>635</v>
+        <v>638</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>82</v>
@@ -13017,7 +13026,7 @@
         <v>94</v>
       </c>
       <c r="AI81" t="s" s="2">
-        <v>639</v>
+        <v>642</v>
       </c>
       <c r="AJ81" t="s" s="2">
         <v>106</v>
@@ -13035,10 +13044,10 @@
         <v>84</v>
       </c>
       <c r="AO81" t="s" s="2">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="AP81" t="s" s="2">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="AQ81" t="s" s="2">
         <v>84</v>
@@ -13049,10 +13058,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>642</v>
+        <v>645</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>642</v>
+        <v>645</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -13075,13 +13084,13 @@
         <v>84</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>636</v>
+        <v>639</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>643</v>
+        <v>646</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>644</v>
+        <v>647</v>
       </c>
       <c r="N82" s="2"/>
       <c r="O82" s="2"/>
@@ -13132,16 +13141,16 @@
         <v>84</v>
       </c>
       <c r="AF82" t="s" s="2">
+        <v>645</v>
+      </c>
+      <c r="AG82" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH82" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI82" t="s" s="2">
         <v>642</v>
-      </c>
-      <c r="AG82" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH82" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AI82" t="s" s="2">
-        <v>639</v>
       </c>
       <c r="AJ82" t="s" s="2">
         <v>106</v>
@@ -13159,10 +13168,10 @@
         <v>84</v>
       </c>
       <c r="AO82" t="s" s="2">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="AP82" t="s" s="2">
-        <v>645</v>
+        <v>648</v>
       </c>
       <c r="AQ82" t="s" s="2">
         <v>84</v>
@@ -13173,10 +13182,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>646</v>
+        <v>649</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>646</v>
+        <v>649</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -13202,16 +13211,16 @@
         <v>171</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>647</v>
+        <v>650</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>648</v>
+        <v>651</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>649</v>
+        <v>652</v>
       </c>
       <c r="O83" t="s" s="2">
-        <v>650</v>
+        <v>653</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>84</v>
@@ -13239,10 +13248,10 @@
         <v>118</v>
       </c>
       <c r="Y83" t="s" s="2">
-        <v>651</v>
+        <v>654</v>
       </c>
       <c r="Z83" t="s" s="2">
-        <v>652</v>
+        <v>655</v>
       </c>
       <c r="AA83" t="s" s="2">
         <v>84</v>
@@ -13260,7 +13269,7 @@
         <v>84</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>646</v>
+        <v>649</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>82</v>
@@ -13284,13 +13293,13 @@
         <v>84</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>653</v>
+        <v>656</v>
       </c>
       <c r="AO83" t="s" s="2">
-        <v>654</v>
+        <v>657</v>
       </c>
       <c r="AP83" t="s" s="2">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="AQ83" t="s" s="2">
         <v>84</v>
@@ -13301,10 +13310,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>655</v>
+        <v>658</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>655</v>
+        <v>658</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -13330,16 +13339,16 @@
         <v>171</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>656</v>
+        <v>659</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>657</v>
+        <v>660</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>658</v>
+        <v>661</v>
       </c>
       <c r="O84" t="s" s="2">
-        <v>659</v>
+        <v>662</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>84</v>
@@ -13364,13 +13373,13 @@
         <v>84</v>
       </c>
       <c r="X84" t="s" s="2">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="Y84" t="s" s="2">
-        <v>660</v>
+        <v>663</v>
       </c>
       <c r="Z84" t="s" s="2">
-        <v>661</v>
+        <v>664</v>
       </c>
       <c r="AA84" t="s" s="2">
         <v>84</v>
@@ -13388,7 +13397,7 @@
         <v>84</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>655</v>
+        <v>658</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>82</v>
@@ -13412,13 +13421,13 @@
         <v>84</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>653</v>
+        <v>656</v>
       </c>
       <c r="AO84" t="s" s="2">
-        <v>654</v>
+        <v>657</v>
       </c>
       <c r="AP84" t="s" s="2">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="AQ84" t="s" s="2">
         <v>84</v>
@@ -13429,10 +13438,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>662</v>
+        <v>665</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>662</v>
+        <v>665</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -13455,17 +13464,17 @@
         <v>84</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>663</v>
+        <v>666</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>664</v>
+        <v>667</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>665</v>
+        <v>668</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" t="s" s="2">
-        <v>666</v>
+        <v>669</v>
       </c>
       <c r="P85" t="s" s="2">
         <v>84</v>
@@ -13514,7 +13523,7 @@
         <v>84</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>662</v>
+        <v>665</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>82</v>
@@ -13544,7 +13553,7 @@
         <v>84</v>
       </c>
       <c r="AP85" t="s" s="2">
-        <v>667</v>
+        <v>670</v>
       </c>
       <c r="AQ85" t="s" s="2">
         <v>84</v>
@@ -13555,10 +13564,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>668</v>
+        <v>671</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>668</v>
+        <v>671</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -13584,10 +13593,10 @@
         <v>196</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>669</v>
+        <v>672</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>670</v>
+        <v>673</v>
       </c>
       <c r="N86" s="2"/>
       <c r="O86" s="2"/>
@@ -13638,7 +13647,7 @@
         <v>84</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>668</v>
+        <v>671</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>82</v>
@@ -13665,10 +13674,10 @@
         <v>84</v>
       </c>
       <c r="AO86" t="s" s="2">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="AP86" t="s" s="2">
-        <v>671</v>
+        <v>674</v>
       </c>
       <c r="AQ86" t="s" s="2">
         <v>84</v>
@@ -13679,10 +13688,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>672</v>
+        <v>675</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>672</v>
+        <v>675</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -13705,16 +13714,16 @@
         <v>95</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>673</v>
+        <v>676</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>674</v>
+        <v>677</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>675</v>
+        <v>678</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
@@ -13764,7 +13773,7 @@
         <v>84</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>672</v>
+        <v>675</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>82</v>
@@ -13791,10 +13800,10 @@
         <v>84</v>
       </c>
       <c r="AO87" t="s" s="2">
-        <v>677</v>
+        <v>680</v>
       </c>
       <c r="AP87" t="s" s="2">
-        <v>678</v>
+        <v>681</v>
       </c>
       <c r="AQ87" t="s" s="2">
         <v>84</v>
@@ -13805,10 +13814,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -13831,16 +13840,16 @@
         <v>95</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>680</v>
+        <v>683</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>681</v>
+        <v>684</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>682</v>
+        <v>685</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>683</v>
+        <v>686</v>
       </c>
       <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
@@ -13890,7 +13899,7 @@
         <v>84</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>82</v>
@@ -13917,10 +13926,10 @@
         <v>84</v>
       </c>
       <c r="AO88" t="s" s="2">
-        <v>677</v>
+        <v>680</v>
       </c>
       <c r="AP88" t="s" s="2">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="AQ88" t="s" s="2">
         <v>84</v>
@@ -13931,10 +13940,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>685</v>
+        <v>688</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>685</v>
+        <v>688</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13942,7 +13951,7 @@
       </c>
       <c r="E89" s="2"/>
       <c r="F89" t="s" s="2">
-        <v>686</v>
+        <v>689</v>
       </c>
       <c r="G89" t="s" s="2">
         <v>83</v>
@@ -13957,19 +13966,19 @@
         <v>95</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>620</v>
+        <v>623</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>687</v>
+        <v>690</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>688</v>
+        <v>691</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>689</v>
+        <v>692</v>
       </c>
       <c r="O89" t="s" s="2">
-        <v>690</v>
+        <v>693</v>
       </c>
       <c r="P89" t="s" s="2">
         <v>84</v>
@@ -14006,7 +14015,7 @@
         <v>84</v>
       </c>
       <c r="AB89" t="s" s="2">
-        <v>691</v>
+        <v>694</v>
       </c>
       <c r="AC89" s="2"/>
       <c r="AD89" t="s" s="2">
@@ -14016,7 +14025,7 @@
         <v>143</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>685</v>
+        <v>688</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>82</v>
@@ -14028,7 +14037,7 @@
         <v>84</v>
       </c>
       <c r="AJ89" t="s" s="2">
-        <v>692</v>
+        <v>695</v>
       </c>
       <c r="AK89" t="s" s="2">
         <v>84</v>
@@ -14043,10 +14052,10 @@
         <v>84</v>
       </c>
       <c r="AO89" t="s" s="2">
-        <v>693</v>
+        <v>696</v>
       </c>
       <c r="AP89" t="s" s="2">
-        <v>694</v>
+        <v>697</v>
       </c>
       <c r="AQ89" t="s" s="2">
         <v>84</v>
@@ -14057,10 +14066,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>695</v>
+        <v>698</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>695</v>
+        <v>698</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -14181,10 +14190,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>696</v>
+        <v>699</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>696</v>
+        <v>699</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -14307,14 +14316,14 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>697</v>
+        <v>700</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>697</v>
+        <v>700</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
-        <v>631</v>
+        <v>634</v>
       </c>
       <c r="E92" s="2"/>
       <c r="F92" t="s" s="2">
@@ -14336,10 +14345,10 @@
         <v>139</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="N92" t="s" s="2">
         <v>183</v>
@@ -14394,7 +14403,7 @@
         <v>84</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>634</v>
+        <v>637</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>82</v>
@@ -14435,10 +14444,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>698</v>
+        <v>701</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>698</v>
+        <v>701</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -14464,16 +14473,16 @@
         <v>171</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>699</v>
+        <v>702</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>700</v>
+        <v>703</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>701</v>
+        <v>704</v>
       </c>
       <c r="O93" t="s" s="2">
-        <v>702</v>
+        <v>705</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>84</v>
@@ -14522,7 +14531,7 @@
         <v>84</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>698</v>
+        <v>701</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>94</v>
@@ -14546,7 +14555,7 @@
         <v>84</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>703</v>
+        <v>706</v>
       </c>
       <c r="AO93" t="s" s="2">
         <v>379</v>
@@ -14563,10 +14572,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>704</v>
+        <v>707</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>704</v>
+        <v>707</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -14589,19 +14598,19 @@
         <v>95</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>705</v>
+        <v>708</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>706</v>
+        <v>709</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>707</v>
+        <v>710</v>
       </c>
       <c r="O94" t="s" s="2">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>84</v>
@@ -14629,16 +14638,16 @@
         <v>214</v>
       </c>
       <c r="Y94" t="s" s="2">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="Z94" t="s" s="2">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="AA94" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AB94" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="AC94" s="2"/>
       <c r="AD94" t="s" s="2">
@@ -14648,7 +14657,7 @@
         <v>143</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>704</v>
+        <v>707</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>82</v>
@@ -14657,7 +14666,7 @@
         <v>94</v>
       </c>
       <c r="AI94" t="s" s="2">
-        <v>708</v>
+        <v>711</v>
       </c>
       <c r="AJ94" t="s" s="2">
         <v>106</v>
@@ -14672,30 +14681,30 @@
         <v>84</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>709</v>
+        <v>712</v>
       </c>
       <c r="AO94" t="s" s="2">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="AP94" t="s" s="2">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="AQ94" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR94" t="s" s="2">
-        <v>468</v>
+        <v>471</v>
       </c>
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>710</v>
+        <v>713</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>704</v>
+        <v>707</v>
       </c>
       <c r="C95" t="s" s="2">
-        <v>711</v>
+        <v>714</v>
       </c>
       <c r="D95" t="s" s="2">
         <v>84</v>
@@ -14720,16 +14729,16 @@
         <v>171</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>705</v>
+        <v>708</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>706</v>
+        <v>709</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>707</v>
+        <v>710</v>
       </c>
       <c r="O95" t="s" s="2">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>84</v>
@@ -14757,10 +14766,10 @@
         <v>214</v>
       </c>
       <c r="Y95" t="s" s="2">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="Z95" t="s" s="2">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="AA95" t="s" s="2">
         <v>84</v>
@@ -14778,7 +14787,7 @@
         <v>84</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>704</v>
+        <v>707</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>82</v>
@@ -14787,7 +14796,7 @@
         <v>94</v>
       </c>
       <c r="AI95" t="s" s="2">
-        <v>708</v>
+        <v>711</v>
       </c>
       <c r="AJ95" t="s" s="2">
         <v>106</v>
@@ -14802,27 +14811,27 @@
         <v>84</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>709</v>
+        <v>712</v>
       </c>
       <c r="AO95" t="s" s="2">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="AP95" t="s" s="2">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="AQ95" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR95" t="s" s="2">
-        <v>468</v>
+        <v>471</v>
       </c>
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>712</v>
+        <v>715</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>713</v>
+        <v>716</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -14943,10 +14952,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>714</v>
+        <v>717</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>715</v>
+        <v>718</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -15069,10 +15078,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>716</v>
+        <v>719</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>717</v>
+        <v>720</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -15136,7 +15145,7 @@
       </c>
       <c r="Y98" s="2"/>
       <c r="Z98" t="s" s="2">
-        <v>718</v>
+        <v>721</v>
       </c>
       <c r="AA98" t="s" s="2">
         <v>84</v>
@@ -15169,7 +15178,7 @@
         <v>106</v>
       </c>
       <c r="AK98" t="s" s="2">
-        <v>719</v>
+        <v>722</v>
       </c>
       <c r="AL98" t="s" s="2">
         <v>84</v>
@@ -15195,10 +15204,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>720</v>
+        <v>723</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>721</v>
+        <v>724</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -15323,10 +15332,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>722</v>
+        <v>725</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>722</v>
+        <v>725</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -15352,16 +15361,16 @@
         <v>171</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>723</v>
+        <v>726</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>724</v>
+        <v>727</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>725</v>
+        <v>728</v>
       </c>
       <c r="O100" t="s" s="2">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="P100" t="s" s="2">
         <v>84</v>
@@ -15389,10 +15398,10 @@
         <v>214</v>
       </c>
       <c r="Y100" t="s" s="2">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="Z100" t="s" s="2">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="AA100" t="s" s="2">
         <v>84</v>
@@ -15410,7 +15419,7 @@
         <v>84</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>722</v>
+        <v>725</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>82</v>
@@ -15419,13 +15428,13 @@
         <v>94</v>
       </c>
       <c r="AI100" t="s" s="2">
-        <v>726</v>
+        <v>729</v>
       </c>
       <c r="AJ100" t="s" s="2">
         <v>106</v>
       </c>
       <c r="AK100" t="s" s="2">
-        <v>727</v>
+        <v>730</v>
       </c>
       <c r="AL100" t="s" s="2">
         <v>84</v>
@@ -15440,7 +15449,7 @@
         <v>137</v>
       </c>
       <c r="AP100" t="s" s="2">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="AQ100" t="s" s="2">
         <v>84</v>
@@ -15451,14 +15460,14 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>728</v>
+        <v>731</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>728</v>
+        <v>731</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="E101" s="2"/>
       <c r="F101" t="s" s="2">
@@ -15480,16 +15489,16 @@
         <v>171</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="O101" t="s" s="2">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="P101" t="s" s="2">
         <v>84</v>
@@ -15517,10 +15526,10 @@
         <v>214</v>
       </c>
       <c r="Y101" t="s" s="2">
-        <v>567</v>
+        <v>570</v>
       </c>
       <c r="Z101" t="s" s="2">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="AA101" t="s" s="2">
         <v>84</v>
@@ -15538,7 +15547,7 @@
         <v>84</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>728</v>
+        <v>731</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>82</v>
@@ -15562,27 +15571,27 @@
         <v>84</v>
       </c>
       <c r="AN101" t="s" s="2">
-        <v>569</v>
+        <v>572</v>
       </c>
       <c r="AO101" t="s" s="2">
-        <v>570</v>
+        <v>573</v>
       </c>
       <c r="AP101" t="s" s="2">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="AQ101" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR101" t="s" s="2">
-        <v>572</v>
+        <v>575</v>
       </c>
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>729</v>
+        <v>732</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>729</v>
+        <v>732</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -15608,16 +15617,16 @@
         <v>85</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>730</v>
+        <v>733</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>731</v>
+        <v>734</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>623</v>
+        <v>626</v>
       </c>
       <c r="O102" t="s" s="2">
-        <v>624</v>
+        <v>627</v>
       </c>
       <c r="P102" t="s" s="2">
         <v>84</v>
@@ -15666,7 +15675,7 @@
         <v>84</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>729</v>
+        <v>732</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>82</v>
@@ -15693,10 +15702,10 @@
         <v>84</v>
       </c>
       <c r="AO102" t="s" s="2">
-        <v>626</v>
+        <v>629</v>
       </c>
       <c r="AP102" t="s" s="2">
-        <v>627</v>
+        <v>630</v>
       </c>
       <c r="AQ102" t="s" s="2">
         <v>84</v>
@@ -15707,13 +15716,13 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>732</v>
+        <v>735</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>685</v>
+        <v>688</v>
       </c>
       <c r="C103" t="s" s="2">
-        <v>733</v>
+        <v>736</v>
       </c>
       <c r="D103" t="s" s="2">
         <v>84</v>
@@ -15735,19 +15744,19 @@
         <v>95</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>620</v>
+        <v>623</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>734</v>
+        <v>737</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>688</v>
+        <v>691</v>
       </c>
       <c r="N103" t="s" s="2">
-        <v>689</v>
+        <v>692</v>
       </c>
       <c r="O103" t="s" s="2">
-        <v>690</v>
+        <v>693</v>
       </c>
       <c r="P103" t="s" s="2">
         <v>84</v>
@@ -15796,7 +15805,7 @@
         <v>84</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>685</v>
+        <v>688</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>82</v>
@@ -15808,7 +15817,7 @@
         <v>84</v>
       </c>
       <c r="AJ103" t="s" s="2">
-        <v>692</v>
+        <v>695</v>
       </c>
       <c r="AK103" t="s" s="2">
         <v>84</v>
@@ -15823,10 +15832,10 @@
         <v>84</v>
       </c>
       <c r="AO103" t="s" s="2">
-        <v>693</v>
+        <v>696</v>
       </c>
       <c r="AP103" t="s" s="2">
-        <v>694</v>
+        <v>697</v>
       </c>
       <c r="AQ103" t="s" s="2">
         <v>84</v>
@@ -15837,10 +15846,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>735</v>
+        <v>738</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>695</v>
+        <v>698</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -15961,10 +15970,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>736</v>
+        <v>739</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>696</v>
+        <v>699</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -16087,14 +16096,14 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>737</v>
+        <v>740</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>697</v>
+        <v>700</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
-        <v>631</v>
+        <v>634</v>
       </c>
       <c r="E106" s="2"/>
       <c r="F106" t="s" s="2">
@@ -16116,10 +16125,10 @@
         <v>139</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="N106" t="s" s="2">
         <v>183</v>
@@ -16174,7 +16183,7 @@
         <v>84</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>634</v>
+        <v>637</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>82</v>
@@ -16215,10 +16224,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>738</v>
+        <v>741</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>698</v>
+        <v>701</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -16244,16 +16253,16 @@
         <v>171</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>739</v>
+        <v>742</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>700</v>
+        <v>703</v>
       </c>
       <c r="N107" t="s" s="2">
-        <v>701</v>
+        <v>704</v>
       </c>
       <c r="O107" t="s" s="2">
-        <v>702</v>
+        <v>705</v>
       </c>
       <c r="P107" t="s" s="2">
         <v>84</v>
@@ -16263,7 +16272,7 @@
         <v>84</v>
       </c>
       <c r="S107" t="s" s="2">
-        <v>740</v>
+        <v>743</v>
       </c>
       <c r="T107" t="s" s="2">
         <v>84</v>
@@ -16302,7 +16311,7 @@
         <v>84</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>698</v>
+        <v>701</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>94</v>
@@ -16326,7 +16335,7 @@
         <v>84</v>
       </c>
       <c r="AN107" t="s" s="2">
-        <v>703</v>
+        <v>706</v>
       </c>
       <c r="AO107" t="s" s="2">
         <v>379</v>
@@ -16343,10 +16352,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>741</v>
+        <v>744</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>704</v>
+        <v>707</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -16369,19 +16378,19 @@
         <v>95</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>705</v>
+        <v>708</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>706</v>
+        <v>709</v>
       </c>
       <c r="N108" t="s" s="2">
-        <v>707</v>
+        <v>710</v>
       </c>
       <c r="O108" t="s" s="2">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="P108" t="s" s="2">
         <v>84</v>
@@ -16409,10 +16418,10 @@
         <v>214</v>
       </c>
       <c r="Y108" t="s" s="2">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="Z108" t="s" s="2">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="AA108" t="s" s="2">
         <v>84</v>
@@ -16430,7 +16439,7 @@
         <v>84</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>704</v>
+        <v>707</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>82</v>
@@ -16439,7 +16448,7 @@
         <v>94</v>
       </c>
       <c r="AI108" t="s" s="2">
-        <v>708</v>
+        <v>711</v>
       </c>
       <c r="AJ108" t="s" s="2">
         <v>106</v>
@@ -16454,27 +16463,27 @@
         <v>84</v>
       </c>
       <c r="AN108" t="s" s="2">
-        <v>709</v>
+        <v>712</v>
       </c>
       <c r="AO108" t="s" s="2">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="AP108" t="s" s="2">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="AQ108" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR108" t="s" s="2">
-        <v>468</v>
+        <v>471</v>
       </c>
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>742</v>
+        <v>745</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>713</v>
+        <v>716</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -16595,10 +16604,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>743</v>
+        <v>746</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>715</v>
+        <v>718</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -16721,10 +16730,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>744</v>
+        <v>747</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>745</v>
+        <v>748</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -16747,19 +16756,19 @@
         <v>95</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="N111" t="s" s="2">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="O111" t="s" s="2">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="P111" t="s" s="2">
         <v>84</v>
@@ -16808,7 +16817,7 @@
         <v>84</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>82</v>
@@ -16823,10 +16832,10 @@
         <v>106</v>
       </c>
       <c r="AK111" t="s" s="2">
-        <v>746</v>
+        <v>749</v>
       </c>
       <c r="AL111" t="s" s="2">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="AM111" t="s" s="2">
         <v>84</v>
@@ -16835,10 +16844,10 @@
         <v>84</v>
       </c>
       <c r="AO111" t="s" s="2">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="AP111" t="s" s="2">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="AQ111" t="s" s="2">
         <v>84</v>
@@ -16849,10 +16858,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>747</v>
+        <v>750</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>748</v>
+        <v>751</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -16878,20 +16887,20 @@
         <v>114</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="N112" s="2"/>
       <c r="O112" t="s" s="2">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="P112" t="s" s="2">
         <v>84</v>
       </c>
       <c r="Q112" t="s" s="2">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="R112" t="s" s="2">
         <v>84</v>
@@ -16915,10 +16924,10 @@
         <v>174</v>
       </c>
       <c r="Y112" t="s" s="2">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="Z112" t="s" s="2">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="AA112" t="s" s="2">
         <v>84</v>
@@ -16936,7 +16945,7 @@
         <v>84</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>82</v>
@@ -16963,10 +16972,10 @@
         <v>84</v>
       </c>
       <c r="AO112" t="s" s="2">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="AP112" t="s" s="2">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="AQ112" t="s" s="2">
         <v>84</v>
@@ -16977,10 +16986,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>749</v>
+        <v>752</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>750</v>
+        <v>753</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -17006,14 +17015,14 @@
         <v>196</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="N113" s="2"/>
       <c r="O113" t="s" s="2">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="P113" t="s" s="2">
         <v>84</v>
@@ -17062,7 +17071,7 @@
         <v>84</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>82</v>
@@ -17089,10 +17098,10 @@
         <v>84</v>
       </c>
       <c r="AO113" t="s" s="2">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="AP113" t="s" s="2">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="AQ113" t="s" s="2">
         <v>84</v>
@@ -17103,10 +17112,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>751</v>
+        <v>754</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>752</v>
+        <v>755</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -17132,21 +17141,21 @@
         <v>108</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="N114" s="2"/>
       <c r="O114" t="s" s="2">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="P114" t="s" s="2">
         <v>84</v>
       </c>
       <c r="Q114" s="2"/>
       <c r="R114" t="s" s="2">
-        <v>753</v>
+        <v>756</v>
       </c>
       <c r="S114" t="s" s="2">
         <v>84</v>
@@ -17188,7 +17197,7 @@
         <v>84</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>82</v>
@@ -17197,7 +17206,7 @@
         <v>94</v>
       </c>
       <c r="AI114" t="s" s="2">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="AJ114" t="s" s="2">
         <v>106</v>
@@ -17215,10 +17224,10 @@
         <v>84</v>
       </c>
       <c r="AO114" t="s" s="2">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="AP114" t="s" s="2">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="AQ114" t="s" s="2">
         <v>84</v>
@@ -17229,10 +17238,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>754</v>
+        <v>757</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>755</v>
+        <v>758</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -17258,23 +17267,23 @@
         <v>114</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="N115" t="s" s="2">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="O115" t="s" s="2">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="P115" t="s" s="2">
         <v>84</v>
       </c>
       <c r="Q115" s="2"/>
       <c r="R115" t="s" s="2">
-        <v>756</v>
+        <v>759</v>
       </c>
       <c r="S115" t="s" s="2">
         <v>84</v>
@@ -17316,7 +17325,7 @@
         <v>84</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>82</v>
@@ -17343,10 +17352,10 @@
         <v>84</v>
       </c>
       <c r="AO115" t="s" s="2">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="AP115" t="s" s="2">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="AQ115" t="s" s="2">
         <v>84</v>
@@ -17357,10 +17366,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>757</v>
+        <v>760</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>722</v>
+        <v>725</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -17386,16 +17395,16 @@
         <v>171</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>723</v>
+        <v>726</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>724</v>
+        <v>727</v>
       </c>
       <c r="N116" t="s" s="2">
-        <v>725</v>
+        <v>728</v>
       </c>
       <c r="O116" t="s" s="2">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="P116" t="s" s="2">
         <v>84</v>
@@ -17423,10 +17432,10 @@
         <v>214</v>
       </c>
       <c r="Y116" t="s" s="2">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="Z116" t="s" s="2">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="AA116" t="s" s="2">
         <v>84</v>
@@ -17444,7 +17453,7 @@
         <v>84</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>722</v>
+        <v>725</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>82</v>
@@ -17453,7 +17462,7 @@
         <v>94</v>
       </c>
       <c r="AI116" t="s" s="2">
-        <v>726</v>
+        <v>729</v>
       </c>
       <c r="AJ116" t="s" s="2">
         <v>106</v>
@@ -17474,7 +17483,7 @@
         <v>137</v>
       </c>
       <c r="AP116" t="s" s="2">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="AQ116" t="s" s="2">
         <v>84</v>
@@ -17485,14 +17494,14 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>758</v>
+        <v>761</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>728</v>
+        <v>731</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="E117" s="2"/>
       <c r="F117" t="s" s="2">
@@ -17514,16 +17523,16 @@
         <v>171</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="N117" t="s" s="2">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="O117" t="s" s="2">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="P117" t="s" s="2">
         <v>84</v>
@@ -17551,10 +17560,10 @@
         <v>214</v>
       </c>
       <c r="Y117" t="s" s="2">
-        <v>567</v>
+        <v>570</v>
       </c>
       <c r="Z117" t="s" s="2">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="AA117" t="s" s="2">
         <v>84</v>
@@ -17572,7 +17581,7 @@
         <v>84</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>728</v>
+        <v>731</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>82</v>
@@ -17596,27 +17605,27 @@
         <v>84</v>
       </c>
       <c r="AN117" t="s" s="2">
-        <v>569</v>
+        <v>572</v>
       </c>
       <c r="AO117" t="s" s="2">
-        <v>570</v>
+        <v>573</v>
       </c>
       <c r="AP117" t="s" s="2">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="AQ117" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR117" t="s" s="2">
-        <v>572</v>
+        <v>575</v>
       </c>
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>759</v>
+        <v>762</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>729</v>
+        <v>732</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -17642,16 +17651,16 @@
         <v>85</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>730</v>
+        <v>733</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>731</v>
+        <v>734</v>
       </c>
       <c r="N118" t="s" s="2">
-        <v>623</v>
+        <v>626</v>
       </c>
       <c r="O118" t="s" s="2">
-        <v>624</v>
+        <v>627</v>
       </c>
       <c r="P118" t="s" s="2">
         <v>84</v>
@@ -17700,7 +17709,7 @@
         <v>84</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>729</v>
+        <v>732</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>82</v>
@@ -17727,10 +17736,10 @@
         <v>84</v>
       </c>
       <c r="AO118" t="s" s="2">
-        <v>626</v>
+        <v>629</v>
       </c>
       <c r="AP118" t="s" s="2">
-        <v>627</v>
+        <v>630</v>
       </c>
       <c r="AQ118" t="s" s="2">
         <v>84</v>
@@ -17741,13 +17750,13 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>760</v>
+        <v>763</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>685</v>
+        <v>688</v>
       </c>
       <c r="C119" t="s" s="2">
-        <v>761</v>
+        <v>764</v>
       </c>
       <c r="D119" t="s" s="2">
         <v>84</v>
@@ -17769,19 +17778,19 @@
         <v>95</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>620</v>
+        <v>623</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>762</v>
+        <v>765</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>688</v>
+        <v>691</v>
       </c>
       <c r="N119" t="s" s="2">
-        <v>689</v>
+        <v>692</v>
       </c>
       <c r="O119" t="s" s="2">
-        <v>690</v>
+        <v>693</v>
       </c>
       <c r="P119" t="s" s="2">
         <v>84</v>
@@ -17830,7 +17839,7 @@
         <v>84</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>685</v>
+        <v>688</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>82</v>
@@ -17842,7 +17851,7 @@
         <v>84</v>
       </c>
       <c r="AJ119" t="s" s="2">
-        <v>692</v>
+        <v>695</v>
       </c>
       <c r="AK119" t="s" s="2">
         <v>84</v>
@@ -17857,10 +17866,10 @@
         <v>84</v>
       </c>
       <c r="AO119" t="s" s="2">
-        <v>693</v>
+        <v>696</v>
       </c>
       <c r="AP119" t="s" s="2">
-        <v>694</v>
+        <v>697</v>
       </c>
       <c r="AQ119" t="s" s="2">
         <v>84</v>
@@ -17871,10 +17880,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>763</v>
+        <v>766</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>695</v>
+        <v>698</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -17995,10 +18004,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>764</v>
+        <v>767</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>696</v>
+        <v>699</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -18121,14 +18130,14 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>765</v>
+        <v>768</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>697</v>
+        <v>700</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
-        <v>631</v>
+        <v>634</v>
       </c>
       <c r="E122" s="2"/>
       <c r="F122" t="s" s="2">
@@ -18150,10 +18159,10 @@
         <v>139</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="N122" t="s" s="2">
         <v>183</v>
@@ -18208,7 +18217,7 @@
         <v>84</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>634</v>
+        <v>637</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>82</v>
@@ -18249,10 +18258,10 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>766</v>
+        <v>769</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>698</v>
+        <v>701</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -18278,16 +18287,16 @@
         <v>171</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>767</v>
+        <v>770</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>700</v>
+        <v>703</v>
       </c>
       <c r="N123" t="s" s="2">
-        <v>701</v>
+        <v>704</v>
       </c>
       <c r="O123" t="s" s="2">
-        <v>702</v>
+        <v>705</v>
       </c>
       <c r="P123" t="s" s="2">
         <v>84</v>
@@ -18297,7 +18306,7 @@
         <v>84</v>
       </c>
       <c r="S123" t="s" s="2">
-        <v>768</v>
+        <v>771</v>
       </c>
       <c r="T123" t="s" s="2">
         <v>84</v>
@@ -18336,7 +18345,7 @@
         <v>84</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>698</v>
+        <v>701</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>94</v>
@@ -18360,7 +18369,7 @@
         <v>84</v>
       </c>
       <c r="AN123" t="s" s="2">
-        <v>703</v>
+        <v>706</v>
       </c>
       <c r="AO123" t="s" s="2">
         <v>379</v>
@@ -18377,10 +18386,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>769</v>
+        <v>772</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>704</v>
+        <v>707</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -18403,19 +18412,19 @@
         <v>95</v>
       </c>
       <c r="K124" t="s" s="2">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>705</v>
+        <v>708</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>706</v>
+        <v>709</v>
       </c>
       <c r="N124" t="s" s="2">
-        <v>707</v>
+        <v>710</v>
       </c>
       <c r="O124" t="s" s="2">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="P124" t="s" s="2">
         <v>84</v>
@@ -18443,10 +18452,10 @@
         <v>214</v>
       </c>
       <c r="Y124" t="s" s="2">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="Z124" t="s" s="2">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="AA124" t="s" s="2">
         <v>84</v>
@@ -18464,7 +18473,7 @@
         <v>84</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>704</v>
+        <v>707</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>82</v>
@@ -18473,7 +18482,7 @@
         <v>94</v>
       </c>
       <c r="AI124" t="s" s="2">
-        <v>708</v>
+        <v>711</v>
       </c>
       <c r="AJ124" t="s" s="2">
         <v>106</v>
@@ -18488,27 +18497,27 @@
         <v>84</v>
       </c>
       <c r="AN124" t="s" s="2">
-        <v>709</v>
+        <v>712</v>
       </c>
       <c r="AO124" t="s" s="2">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="AP124" t="s" s="2">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="AQ124" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR124" t="s" s="2">
-        <v>468</v>
+        <v>471</v>
       </c>
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>770</v>
+        <v>773</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>713</v>
+        <v>716</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -18629,10 +18638,10 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>771</v>
+        <v>774</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>715</v>
+        <v>718</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -18755,10 +18764,10 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>772</v>
+        <v>775</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>745</v>
+        <v>748</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -18781,19 +18790,19 @@
         <v>95</v>
       </c>
       <c r="K127" t="s" s="2">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="N127" t="s" s="2">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="O127" t="s" s="2">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="P127" t="s" s="2">
         <v>84</v>
@@ -18842,7 +18851,7 @@
         <v>84</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>82</v>
@@ -18857,10 +18866,10 @@
         <v>106</v>
       </c>
       <c r="AK127" t="s" s="2">
-        <v>773</v>
+        <v>776</v>
       </c>
       <c r="AL127" t="s" s="2">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="AM127" t="s" s="2">
         <v>84</v>
@@ -18869,10 +18878,10 @@
         <v>84</v>
       </c>
       <c r="AO127" t="s" s="2">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="AP127" t="s" s="2">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="AQ127" t="s" s="2">
         <v>84</v>
@@ -18883,10 +18892,10 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>774</v>
+        <v>777</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>748</v>
+        <v>751</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -18912,20 +18921,20 @@
         <v>114</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="N128" s="2"/>
       <c r="O128" t="s" s="2">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="P128" t="s" s="2">
         <v>84</v>
       </c>
       <c r="Q128" t="s" s="2">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="R128" t="s" s="2">
         <v>84</v>
@@ -18949,10 +18958,10 @@
         <v>174</v>
       </c>
       <c r="Y128" t="s" s="2">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="Z128" t="s" s="2">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="AA128" t="s" s="2">
         <v>84</v>
@@ -18970,7 +18979,7 @@
         <v>84</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>82</v>
@@ -18997,10 +19006,10 @@
         <v>84</v>
       </c>
       <c r="AO128" t="s" s="2">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="AP128" t="s" s="2">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="AQ128" t="s" s="2">
         <v>84</v>
@@ -19011,10 +19020,10 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>775</v>
+        <v>778</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>750</v>
+        <v>753</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -19040,14 +19049,14 @@
         <v>196</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="N129" s="2"/>
       <c r="O129" t="s" s="2">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="P129" t="s" s="2">
         <v>84</v>
@@ -19096,7 +19105,7 @@
         <v>84</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>82</v>
@@ -19123,10 +19132,10 @@
         <v>84</v>
       </c>
       <c r="AO129" t="s" s="2">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="AP129" t="s" s="2">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="AQ129" t="s" s="2">
         <v>84</v>
@@ -19137,10 +19146,10 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>776</v>
+        <v>779</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>752</v>
+        <v>755</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -19166,21 +19175,21 @@
         <v>108</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="N130" s="2"/>
       <c r="O130" t="s" s="2">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="P130" t="s" s="2">
         <v>84</v>
       </c>
       <c r="Q130" s="2"/>
       <c r="R130" t="s" s="2">
-        <v>753</v>
+        <v>756</v>
       </c>
       <c r="S130" t="s" s="2">
         <v>84</v>
@@ -19222,7 +19231,7 @@
         <v>84</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>82</v>
@@ -19231,7 +19240,7 @@
         <v>94</v>
       </c>
       <c r="AI130" t="s" s="2">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="AJ130" t="s" s="2">
         <v>106</v>
@@ -19249,10 +19258,10 @@
         <v>84</v>
       </c>
       <c r="AO130" t="s" s="2">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="AP130" t="s" s="2">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="AQ130" t="s" s="2">
         <v>84</v>
@@ -19263,10 +19272,10 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>777</v>
+        <v>780</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>755</v>
+        <v>758</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -19292,23 +19301,23 @@
         <v>114</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="N131" t="s" s="2">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="O131" t="s" s="2">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="P131" t="s" s="2">
         <v>84</v>
       </c>
       <c r="Q131" s="2"/>
       <c r="R131" t="s" s="2">
-        <v>756</v>
+        <v>759</v>
       </c>
       <c r="S131" t="s" s="2">
         <v>84</v>
@@ -19350,7 +19359,7 @@
         <v>84</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>82</v>
@@ -19377,10 +19386,10 @@
         <v>84</v>
       </c>
       <c r="AO131" t="s" s="2">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="AP131" t="s" s="2">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="AQ131" t="s" s="2">
         <v>84</v>
@@ -19391,10 +19400,10 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>778</v>
+        <v>781</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>722</v>
+        <v>725</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -19420,16 +19429,16 @@
         <v>171</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>723</v>
+        <v>726</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>724</v>
+        <v>727</v>
       </c>
       <c r="N132" t="s" s="2">
-        <v>725</v>
+        <v>728</v>
       </c>
       <c r="O132" t="s" s="2">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="P132" t="s" s="2">
         <v>84</v>
@@ -19457,10 +19466,10 @@
         <v>214</v>
       </c>
       <c r="Y132" t="s" s="2">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="Z132" t="s" s="2">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="AA132" t="s" s="2">
         <v>84</v>
@@ -19478,7 +19487,7 @@
         <v>84</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>722</v>
+        <v>725</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>82</v>
@@ -19487,7 +19496,7 @@
         <v>94</v>
       </c>
       <c r="AI132" t="s" s="2">
-        <v>726</v>
+        <v>729</v>
       </c>
       <c r="AJ132" t="s" s="2">
         <v>106</v>
@@ -19508,7 +19517,7 @@
         <v>137</v>
       </c>
       <c r="AP132" t="s" s="2">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="AQ132" t="s" s="2">
         <v>84</v>
@@ -19519,14 +19528,14 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>779</v>
+        <v>782</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>728</v>
+        <v>731</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="E133" s="2"/>
       <c r="F133" t="s" s="2">
@@ -19548,16 +19557,16 @@
         <v>171</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="N133" t="s" s="2">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="O133" t="s" s="2">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="P133" t="s" s="2">
         <v>84</v>
@@ -19585,10 +19594,10 @@
         <v>214</v>
       </c>
       <c r="Y133" t="s" s="2">
-        <v>567</v>
+        <v>570</v>
       </c>
       <c r="Z133" t="s" s="2">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="AA133" t="s" s="2">
         <v>84</v>
@@ -19606,7 +19615,7 @@
         <v>84</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>728</v>
+        <v>731</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>82</v>
@@ -19630,27 +19639,27 @@
         <v>84</v>
       </c>
       <c r="AN133" t="s" s="2">
-        <v>569</v>
+        <v>572</v>
       </c>
       <c r="AO133" t="s" s="2">
-        <v>570</v>
+        <v>573</v>
       </c>
       <c r="AP133" t="s" s="2">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="AQ133" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR133" t="s" s="2">
-        <v>572</v>
+        <v>575</v>
       </c>
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>780</v>
+        <v>783</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>729</v>
+        <v>732</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -19676,16 +19685,16 @@
         <v>85</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>730</v>
+        <v>733</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>731</v>
+        <v>734</v>
       </c>
       <c r="N134" t="s" s="2">
-        <v>623</v>
+        <v>626</v>
       </c>
       <c r="O134" t="s" s="2">
-        <v>624</v>
+        <v>627</v>
       </c>
       <c r="P134" t="s" s="2">
         <v>84</v>
@@ -19734,7 +19743,7 @@
         <v>84</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>729</v>
+        <v>732</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>82</v>
@@ -19761,10 +19770,10 @@
         <v>84</v>
       </c>
       <c r="AO134" t="s" s="2">
-        <v>626</v>
+        <v>629</v>
       </c>
       <c r="AP134" t="s" s="2">
-        <v>627</v>
+        <v>630</v>
       </c>
       <c r="AQ134" t="s" s="2">
         <v>84</v>

--- a/docs/StructureDefinition-VitalSignsBPObservation.xlsx
+++ b/docs/StructureDefinition-VitalSignsBPObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.47.0</t>
+    <t>0.48.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-04T09:18:00+00:00</t>
+    <t>2024-05-06T08:00:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsBPObservation.xlsx
+++ b/docs/StructureDefinition-VitalSignsBPObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.48.0</t>
+    <t>0.49.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-06T08:00:03+00:00</t>
+    <t>2024-05-06T11:38:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsBPObservation.xlsx
+++ b/docs/StructureDefinition-VitalSignsBPObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.49.0</t>
+    <t>0.50.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-06T11:38:53+00:00</t>
+    <t>2024-05-08T06:31:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsBPObservation.xlsx
+++ b/docs/StructureDefinition-VitalSignsBPObservation.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AR$134</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AR$171</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5430" uniqueCount="784">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6933" uniqueCount="828">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.50.0</t>
+    <t>0.51.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-08T06:31:45+00:00</t>
+    <t>2024-05-11T08:27:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -2245,42 +2245,6 @@
     <t>363714003 |Interprets| &lt; 441742003 |Evaluation finding|</t>
   </si>
   <si>
-    <t>Observation.component.value[x]:valueCodeableConcept</t>
-  </si>
-  <si>
-    <t>valueCodeableConcept</t>
-  </si>
-  <si>
-    <t>Observation.component.value[x]:valueCodeableConcept.id</t>
-  </si>
-  <si>
-    <t>Observation.component.value[x].id</t>
-  </si>
-  <si>
-    <t>Observation.component.value[x]:valueCodeableConcept.extension</t>
-  </si>
-  <si>
-    <t>Observation.component.value[x].extension</t>
-  </si>
-  <si>
-    <t>Observation.component.value[x]:valueCodeableConcept.coding</t>
-  </si>
-  <si>
-    <t>Observation.component.value[x].coding</t>
-  </si>
-  <si>
-    <t>http://va.gov/fhir/ValueSet/VSVFVitalsCuffSize</t>
-  </si>
-  <si>
-    <t>1805: terminologyMaps using VF_VitalsCuffSize on GMRV VITAL MEASUREMENT - QUALIFIER &gt; GMRV VITAL QUALIFIER - VUID (120.5-5 &gt; 120.52-99.99)</t>
-  </si>
-  <si>
-    <t>Observation.component.value[x]:valueCodeableConcept.text</t>
-  </si>
-  <si>
-    <t>Observation.component.value[x].text</t>
-  </si>
-  <si>
     <t>Observation.component.dataAbsentReason</t>
   </si>
   <si>
@@ -2351,7 +2315,13 @@
     <t>Observation.component:systolic.value[x].id</t>
   </si>
   <si>
+    <t>Observation.component.value[x].id</t>
+  </si>
+  <si>
     <t>Observation.component:systolic.value[x].extension</t>
+  </si>
+  <si>
+    <t>Observation.component.value[x].extension</t>
   </si>
   <si>
     <t>Observation.component:systolic.value[x].value</t>
@@ -2468,6 +2438,168 @@
   </si>
   <si>
     <t>Observation.component:diastolic.referenceRange</t>
+  </si>
+  <si>
+    <t>Observation.component:va-pre-condition</t>
+  </si>
+  <si>
+    <t>va-pre-condition</t>
+  </si>
+  <si>
+    <t>Observation.component:va-pre-condition.id</t>
+  </si>
+  <si>
+    <t>Observation.component:va-pre-condition.extension</t>
+  </si>
+  <si>
+    <t>Observation.component:va-pre-condition.modifierExtension</t>
+  </si>
+  <si>
+    <t>Observation.component:va-pre-condition.code</t>
+  </si>
+  <si>
+    <t>Observation.component:va-pre-condition.value[x]</t>
+  </si>
+  <si>
+    <t>Observation.component:va-pre-condition.value[x]:valueCodeableConcept</t>
+  </si>
+  <si>
+    <t>valueCodeableConcept</t>
+  </si>
+  <si>
+    <t>Observation.component:va-pre-condition.value[x]:valueCodeableConcept.id</t>
+  </si>
+  <si>
+    <t>Observation.component:va-pre-condition.value[x]:valueCodeableConcept.extension</t>
+  </si>
+  <si>
+    <t>Observation.component:va-pre-condition.value[x]:valueCodeableConcept.coding</t>
+  </si>
+  <si>
+    <t>Observation.component.value[x].coding</t>
+  </si>
+  <si>
+    <t>http://va.gov/fhir/ValueSet/VSVFVitalsPrecondition</t>
+  </si>
+  <si>
+    <t>1802: terminologyMaps using VF_VitalsPrecondition on GMRV VITAL MEASUREMENT - QUALIFIER &gt; GMRV VITAL QUALIFIER - VUID (120.5-5 &gt; 120.52-99.99)</t>
+  </si>
+  <si>
+    <t>Observation.component:va-pre-condition.value[x]:valueCodeableConcept.text</t>
+  </si>
+  <si>
+    <t>Observation.component.value[x].text</t>
+  </si>
+  <si>
+    <t>Observation.component:va-pre-condition.dataAbsentReason</t>
+  </si>
+  <si>
+    <t>Observation.component:va-pre-condition.interpretation</t>
+  </si>
+  <si>
+    <t>Observation.component:va-pre-condition.referenceRange</t>
+  </si>
+  <si>
+    <t>Observation.component:va-pre-condition-device</t>
+  </si>
+  <si>
+    <t>va-pre-condition-device</t>
+  </si>
+  <si>
+    <t>Observation.component:va-pre-condition-device.id</t>
+  </si>
+  <si>
+    <t>Observation.component:va-pre-condition-device.extension</t>
+  </si>
+  <si>
+    <t>Observation.component:va-pre-condition-device.modifierExtension</t>
+  </si>
+  <si>
+    <t>Observation.component:va-pre-condition-device.code</t>
+  </si>
+  <si>
+    <t>Observation.component:va-pre-condition-device.value[x]</t>
+  </si>
+  <si>
+    <t>Observation.component:va-pre-condition-device.value[x]:valueCodeableConcept</t>
+  </si>
+  <si>
+    <t>Observation.component:va-pre-condition-device.value[x]:valueCodeableConcept.id</t>
+  </si>
+  <si>
+    <t>Observation.component:va-pre-condition-device.value[x]:valueCodeableConcept.extension</t>
+  </si>
+  <si>
+    <t>Observation.component:va-pre-condition-device.value[x]:valueCodeableConcept.coding</t>
+  </si>
+  <si>
+    <t>http://va.gov/fhir/ValueSet/VSVFVitalsQualifyingDevice</t>
+  </si>
+  <si>
+    <t>1803: terminologyMaps using VF_VitalsQualifyingDevice on GMRV VITAL MEASUREMENT - QUALIFIER &gt; GMRV VITAL QUALIFIER - VUID (120.5-5 &gt; 120.52-99.99)</t>
+  </si>
+  <si>
+    <t>Observation.component:va-pre-condition-device.value[x]:valueCodeableConcept.text</t>
+  </si>
+  <si>
+    <t>Observation.component:va-pre-condition-device.dataAbsentReason</t>
+  </si>
+  <si>
+    <t>Observation.component:va-pre-condition-device.interpretation</t>
+  </si>
+  <si>
+    <t>Observation.component:va-pre-condition-device.referenceRange</t>
+  </si>
+  <si>
+    <t>Observation.component:va-cuff-size</t>
+  </si>
+  <si>
+    <t>va-cuff-size</t>
+  </si>
+  <si>
+    <t>Observation.component:va-cuff-size.id</t>
+  </si>
+  <si>
+    <t>Observation.component:va-cuff-size.extension</t>
+  </si>
+  <si>
+    <t>Observation.component:va-cuff-size.modifierExtension</t>
+  </si>
+  <si>
+    <t>Observation.component:va-cuff-size.code</t>
+  </si>
+  <si>
+    <t>Observation.component:va-cuff-size.value[x]</t>
+  </si>
+  <si>
+    <t>Observation.component:va-cuff-size.value[x]:valueCodeableConcept</t>
+  </si>
+  <si>
+    <t>Observation.component:va-cuff-size.value[x]:valueCodeableConcept.id</t>
+  </si>
+  <si>
+    <t>Observation.component:va-cuff-size.value[x]:valueCodeableConcept.extension</t>
+  </si>
+  <si>
+    <t>Observation.component:va-cuff-size.value[x]:valueCodeableConcept.coding</t>
+  </si>
+  <si>
+    <t>http://va.gov/fhir/ValueSet/VSVFVitalsCuffSize</t>
+  </si>
+  <si>
+    <t>1805: terminologyMaps using VF_VitalsCuffSize on GMRV VITAL MEASUREMENT - QUALIFIER &gt; GMRV VITAL QUALIFIER - VUID (120.5-5 &gt; 120.52-99.99)</t>
+  </si>
+  <si>
+    <t>Observation.component:va-cuff-size.value[x]:valueCodeableConcept.text</t>
+  </si>
+  <si>
+    <t>Observation.component:va-cuff-size.dataAbsentReason</t>
+  </si>
+  <si>
+    <t>Observation.component:va-cuff-size.interpretation</t>
+  </si>
+  <si>
+    <t>Observation.component:va-cuff-size.referenceRange</t>
   </si>
 </sst>
 </file>
@@ -2784,7 +2916,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AR134"/>
+  <dimension ref="A1:AR171"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="91.8671875" customWidth="true" bestFit="true"/>
@@ -2812,7 +2944,7 @@
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="98.375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="50.83984375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="51.3125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
@@ -2822,7 +2954,7 @@
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="144.703125" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="148.453125" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="98.75" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="29.69921875" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="247.40625" customWidth="true" bestFit="true"/>
@@ -14647,14 +14779,16 @@
         <v>84</v>
       </c>
       <c r="AB94" t="s" s="2">
-        <v>426</v>
-      </c>
-      <c r="AC94" s="2"/>
+        <v>84</v>
+      </c>
+      <c r="AC94" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="AD94" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE94" t="s" s="2">
-        <v>143</v>
+        <v>84</v>
       </c>
       <c r="AF94" t="s" s="2">
         <v>707</v>
@@ -14701,11 +14835,9 @@
         <v>713</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>707</v>
-      </c>
-      <c r="C95" t="s" s="2">
-        <v>714</v>
-      </c>
+        <v>713</v>
+      </c>
+      <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
         <v>84</v>
       </c>
@@ -14723,22 +14855,22 @@
         <v>84</v>
       </c>
       <c r="J95" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K95" t="s" s="2">
         <v>171</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>708</v>
+        <v>714</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>709</v>
+        <v>715</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>710</v>
+        <v>716</v>
       </c>
       <c r="O95" t="s" s="2">
-        <v>464</v>
+        <v>558</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>84</v>
@@ -14766,10 +14898,10 @@
         <v>214</v>
       </c>
       <c r="Y95" t="s" s="2">
-        <v>465</v>
+        <v>559</v>
       </c>
       <c r="Z95" t="s" s="2">
-        <v>466</v>
+        <v>560</v>
       </c>
       <c r="AA95" t="s" s="2">
         <v>84</v>
@@ -14787,7 +14919,7 @@
         <v>84</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>707</v>
+        <v>713</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>82</v>
@@ -14796,13 +14928,13 @@
         <v>94</v>
       </c>
       <c r="AI95" t="s" s="2">
-        <v>711</v>
+        <v>717</v>
       </c>
       <c r="AJ95" t="s" s="2">
         <v>106</v>
       </c>
       <c r="AK95" t="s" s="2">
-        <v>84</v>
+        <v>718</v>
       </c>
       <c r="AL95" t="s" s="2">
         <v>84</v>
@@ -14811,38 +14943,38 @@
         <v>84</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>712</v>
+        <v>84</v>
       </c>
       <c r="AO95" t="s" s="2">
-        <v>469</v>
+        <v>137</v>
       </c>
       <c r="AP95" t="s" s="2">
-        <v>470</v>
+        <v>563</v>
       </c>
       <c r="AQ95" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR95" t="s" s="2">
-        <v>471</v>
+        <v>84</v>
       </c>
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>716</v>
+        <v>719</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
-        <v>84</v>
+        <v>565</v>
       </c>
       <c r="E96" s="2"/>
       <c r="F96" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G96" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H96" t="s" s="2">
         <v>84</v>
@@ -14854,16 +14986,20 @@
         <v>84</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>196</v>
+        <v>171</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>153</v>
+        <v>566</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>154</v>
-      </c>
-      <c r="N96" s="2"/>
-      <c r="O96" s="2"/>
+        <v>567</v>
+      </c>
+      <c r="N96" t="s" s="2">
+        <v>568</v>
+      </c>
+      <c r="O96" t="s" s="2">
+        <v>569</v>
+      </c>
       <c r="P96" t="s" s="2">
         <v>84</v>
       </c>
@@ -14887,13 +15023,13 @@
         <v>84</v>
       </c>
       <c r="X96" t="s" s="2">
-        <v>84</v>
+        <v>214</v>
       </c>
       <c r="Y96" t="s" s="2">
-        <v>84</v>
+        <v>570</v>
       </c>
       <c r="Z96" t="s" s="2">
-        <v>84</v>
+        <v>571</v>
       </c>
       <c r="AA96" t="s" s="2">
         <v>84</v>
@@ -14911,19 +15047,19 @@
         <v>84</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>155</v>
+        <v>719</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH96" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI96" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ96" t="s" s="2">
-        <v>84</v>
+        <v>106</v>
       </c>
       <c r="AK96" t="s" s="2">
         <v>84</v>
@@ -14935,31 +15071,31 @@
         <v>84</v>
       </c>
       <c r="AN96" t="s" s="2">
-        <v>84</v>
+        <v>572</v>
       </c>
       <c r="AO96" t="s" s="2">
-        <v>84</v>
+        <v>573</v>
       </c>
       <c r="AP96" t="s" s="2">
-        <v>157</v>
+        <v>574</v>
       </c>
       <c r="AQ96" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR96" t="s" s="2">
-        <v>84</v>
+        <v>575</v>
       </c>
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>717</v>
+        <v>720</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>718</v>
+        <v>720</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
-        <v>180</v>
+        <v>84</v>
       </c>
       <c r="E97" s="2"/>
       <c r="F97" t="s" s="2">
@@ -14978,18 +15114,20 @@
         <v>84</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>139</v>
+        <v>85</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>198</v>
+        <v>721</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>199</v>
+        <v>722</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="O97" s="2"/>
+        <v>626</v>
+      </c>
+      <c r="O97" t="s" s="2">
+        <v>627</v>
+      </c>
       <c r="P97" t="s" s="2">
         <v>84</v>
       </c>
@@ -15025,19 +15163,19 @@
         <v>84</v>
       </c>
       <c r="AB97" t="s" s="2">
-        <v>142</v>
+        <v>84</v>
       </c>
       <c r="AC97" t="s" s="2">
-        <v>160</v>
+        <v>84</v>
       </c>
       <c r="AD97" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE97" t="s" s="2">
-        <v>143</v>
+        <v>84</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>161</v>
+        <v>720</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>82</v>
@@ -15049,7 +15187,7 @@
         <v>84</v>
       </c>
       <c r="AJ97" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK97" t="s" s="2">
         <v>84</v>
@@ -15064,10 +15202,10 @@
         <v>84</v>
       </c>
       <c r="AO97" t="s" s="2">
-        <v>84</v>
+        <v>629</v>
       </c>
       <c r="AP97" t="s" s="2">
-        <v>157</v>
+        <v>630</v>
       </c>
       <c r="AQ97" t="s" s="2">
         <v>84</v>
@@ -15078,21 +15216,23 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>719</v>
+        <v>723</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>720</v>
-      </c>
-      <c r="C98" s="2"/>
+        <v>688</v>
+      </c>
+      <c r="C98" t="s" s="2">
+        <v>724</v>
+      </c>
       <c r="D98" t="s" s="2">
         <v>84</v>
       </c>
       <c r="E98" s="2"/>
       <c r="F98" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="G98" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H98" t="s" s="2">
         <v>95</v>
@@ -15104,19 +15244,19 @@
         <v>95</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>302</v>
+        <v>623</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>303</v>
+        <v>725</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>304</v>
+        <v>691</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>305</v>
+        <v>692</v>
       </c>
       <c r="O98" t="s" s="2">
-        <v>306</v>
+        <v>693</v>
       </c>
       <c r="P98" t="s" s="2">
         <v>84</v>
@@ -15141,11 +15281,13 @@
         <v>84</v>
       </c>
       <c r="X98" t="s" s="2">
-        <v>174</v>
-      </c>
-      <c r="Y98" s="2"/>
+        <v>84</v>
+      </c>
+      <c r="Y98" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="Z98" t="s" s="2">
-        <v>721</v>
+        <v>84</v>
       </c>
       <c r="AA98" t="s" s="2">
         <v>84</v>
@@ -15163,7 +15305,7 @@
         <v>84</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>307</v>
+        <v>688</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>82</v>
@@ -15175,10 +15317,10 @@
         <v>84</v>
       </c>
       <c r="AJ98" t="s" s="2">
-        <v>106</v>
+        <v>695</v>
       </c>
       <c r="AK98" t="s" s="2">
-        <v>722</v>
+        <v>84</v>
       </c>
       <c r="AL98" t="s" s="2">
         <v>84</v>
@@ -15190,10 +15332,10 @@
         <v>84</v>
       </c>
       <c r="AO98" t="s" s="2">
-        <v>308</v>
+        <v>696</v>
       </c>
       <c r="AP98" t="s" s="2">
-        <v>309</v>
+        <v>697</v>
       </c>
       <c r="AQ98" t="s" s="2">
         <v>84</v>
@@ -15204,10 +15346,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>723</v>
+        <v>726</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>724</v>
+        <v>698</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -15227,23 +15369,19 @@
         <v>84</v>
       </c>
       <c r="J99" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K99" t="s" s="2">
         <v>196</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>361</v>
+        <v>153</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>362</v>
-      </c>
-      <c r="N99" t="s" s="2">
-        <v>363</v>
-      </c>
-      <c r="O99" t="s" s="2">
-        <v>364</v>
-      </c>
+        <v>154</v>
+      </c>
+      <c r="N99" s="2"/>
+      <c r="O99" s="2"/>
       <c r="P99" t="s" s="2">
         <v>84</v>
       </c>
@@ -15291,7 +15429,7 @@
         <v>84</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>365</v>
+        <v>155</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>82</v>
@@ -15303,7 +15441,7 @@
         <v>84</v>
       </c>
       <c r="AJ99" t="s" s="2">
-        <v>106</v>
+        <v>84</v>
       </c>
       <c r="AK99" t="s" s="2">
         <v>84</v>
@@ -15318,10 +15456,10 @@
         <v>84</v>
       </c>
       <c r="AO99" t="s" s="2">
-        <v>366</v>
+        <v>84</v>
       </c>
       <c r="AP99" t="s" s="2">
-        <v>367</v>
+        <v>157</v>
       </c>
       <c r="AQ99" t="s" s="2">
         <v>84</v>
@@ -15332,24 +15470,24 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>725</v>
+        <v>727</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>725</v>
+        <v>699</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
-        <v>84</v>
+        <v>180</v>
       </c>
       <c r="E100" s="2"/>
       <c r="F100" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G100" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H100" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="I100" t="s" s="2">
         <v>84</v>
@@ -15358,20 +15496,18 @@
         <v>84</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>171</v>
+        <v>139</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>726</v>
+        <v>198</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>727</v>
+        <v>199</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>728</v>
-      </c>
-      <c r="O100" t="s" s="2">
-        <v>558</v>
-      </c>
+        <v>183</v>
+      </c>
+      <c r="O100" s="2"/>
       <c r="P100" t="s" s="2">
         <v>84</v>
       </c>
@@ -15395,13 +15531,13 @@
         <v>84</v>
       </c>
       <c r="X100" t="s" s="2">
-        <v>214</v>
+        <v>84</v>
       </c>
       <c r="Y100" t="s" s="2">
-        <v>559</v>
+        <v>84</v>
       </c>
       <c r="Z100" t="s" s="2">
-        <v>560</v>
+        <v>84</v>
       </c>
       <c r="AA100" t="s" s="2">
         <v>84</v>
@@ -15419,22 +15555,22 @@
         <v>84</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>725</v>
+        <v>161</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH100" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI100" t="s" s="2">
-        <v>729</v>
+        <v>84</v>
       </c>
       <c r="AJ100" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK100" t="s" s="2">
-        <v>730</v>
+        <v>84</v>
       </c>
       <c r="AL100" t="s" s="2">
         <v>84</v>
@@ -15446,10 +15582,10 @@
         <v>84</v>
       </c>
       <c r="AO100" t="s" s="2">
-        <v>137</v>
+        <v>84</v>
       </c>
       <c r="AP100" t="s" s="2">
-        <v>563</v>
+        <v>157</v>
       </c>
       <c r="AQ100" t="s" s="2">
         <v>84</v>
@@ -15460,14 +15596,14 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>731</v>
+        <v>728</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>731</v>
+        <v>700</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
-        <v>565</v>
+        <v>634</v>
       </c>
       <c r="E101" s="2"/>
       <c r="F101" t="s" s="2">
@@ -15480,25 +15616,25 @@
         <v>84</v>
       </c>
       <c r="I101" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="J101" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>171</v>
+        <v>139</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>566</v>
+        <v>635</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>567</v>
+        <v>636</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>568</v>
+        <v>183</v>
       </c>
       <c r="O101" t="s" s="2">
-        <v>569</v>
+        <v>184</v>
       </c>
       <c r="P101" t="s" s="2">
         <v>84</v>
@@ -15523,13 +15659,13 @@
         <v>84</v>
       </c>
       <c r="X101" t="s" s="2">
-        <v>214</v>
+        <v>84</v>
       </c>
       <c r="Y101" t="s" s="2">
-        <v>570</v>
+        <v>84</v>
       </c>
       <c r="Z101" t="s" s="2">
-        <v>571</v>
+        <v>84</v>
       </c>
       <c r="AA101" t="s" s="2">
         <v>84</v>
@@ -15547,7 +15683,7 @@
         <v>84</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>731</v>
+        <v>637</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>82</v>
@@ -15559,7 +15695,7 @@
         <v>84</v>
       </c>
       <c r="AJ101" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK101" t="s" s="2">
         <v>84</v>
@@ -15571,27 +15707,27 @@
         <v>84</v>
       </c>
       <c r="AN101" t="s" s="2">
-        <v>572</v>
+        <v>84</v>
       </c>
       <c r="AO101" t="s" s="2">
-        <v>573</v>
+        <v>84</v>
       </c>
       <c r="AP101" t="s" s="2">
-        <v>574</v>
+        <v>137</v>
       </c>
       <c r="AQ101" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR101" t="s" s="2">
-        <v>575</v>
+        <v>84</v>
       </c>
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>732</v>
+        <v>729</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>732</v>
+        <v>701</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -15599,34 +15735,34 @@
       </c>
       <c r="E102" s="2"/>
       <c r="F102" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="G102" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H102" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I102" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J102" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>85</v>
+        <v>171</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>733</v>
+        <v>730</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>734</v>
+        <v>703</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>626</v>
+        <v>704</v>
       </c>
       <c r="O102" t="s" s="2">
-        <v>627</v>
+        <v>705</v>
       </c>
       <c r="P102" t="s" s="2">
         <v>84</v>
@@ -15636,7 +15772,7 @@
         <v>84</v>
       </c>
       <c r="S102" t="s" s="2">
-        <v>84</v>
+        <v>731</v>
       </c>
       <c r="T102" t="s" s="2">
         <v>84</v>
@@ -15651,13 +15787,13 @@
         <v>84</v>
       </c>
       <c r="X102" t="s" s="2">
-        <v>84</v>
+        <v>214</v>
       </c>
       <c r="Y102" t="s" s="2">
-        <v>84</v>
+        <v>375</v>
       </c>
       <c r="Z102" t="s" s="2">
-        <v>84</v>
+        <v>376</v>
       </c>
       <c r="AA102" t="s" s="2">
         <v>84</v>
@@ -15675,13 +15811,13 @@
         <v>84</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>732</v>
+        <v>701</v>
       </c>
       <c r="AG102" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AH102" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI102" t="s" s="2">
         <v>84</v>
@@ -15699,16 +15835,16 @@
         <v>84</v>
       </c>
       <c r="AN102" t="s" s="2">
-        <v>84</v>
+        <v>706</v>
       </c>
       <c r="AO102" t="s" s="2">
-        <v>629</v>
+        <v>379</v>
       </c>
       <c r="AP102" t="s" s="2">
-        <v>630</v>
+        <v>380</v>
       </c>
       <c r="AQ102" t="s" s="2">
-        <v>84</v>
+        <v>381</v>
       </c>
       <c r="AR102" t="s" s="2">
         <v>84</v>
@@ -15716,20 +15852,18 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>735</v>
+        <v>732</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>688</v>
-      </c>
-      <c r="C103" t="s" s="2">
-        <v>736</v>
-      </c>
+        <v>707</v>
+      </c>
+      <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
         <v>84</v>
       </c>
       <c r="E103" s="2"/>
       <c r="F103" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="G103" t="s" s="2">
         <v>94</v>
@@ -15744,19 +15878,19 @@
         <v>95</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>623</v>
+        <v>474</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>737</v>
+        <v>708</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>691</v>
+        <v>709</v>
       </c>
       <c r="N103" t="s" s="2">
-        <v>692</v>
+        <v>710</v>
       </c>
       <c r="O103" t="s" s="2">
-        <v>693</v>
+        <v>464</v>
       </c>
       <c r="P103" t="s" s="2">
         <v>84</v>
@@ -15781,13 +15915,13 @@
         <v>84</v>
       </c>
       <c r="X103" t="s" s="2">
-        <v>84</v>
+        <v>214</v>
       </c>
       <c r="Y103" t="s" s="2">
-        <v>84</v>
+        <v>465</v>
       </c>
       <c r="Z103" t="s" s="2">
-        <v>84</v>
+        <v>466</v>
       </c>
       <c r="AA103" t="s" s="2">
         <v>84</v>
@@ -15805,19 +15939,19 @@
         <v>84</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>688</v>
+        <v>707</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH103" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI103" t="s" s="2">
-        <v>84</v>
+        <v>711</v>
       </c>
       <c r="AJ103" t="s" s="2">
-        <v>695</v>
+        <v>106</v>
       </c>
       <c r="AK103" t="s" s="2">
         <v>84</v>
@@ -15829,27 +15963,27 @@
         <v>84</v>
       </c>
       <c r="AN103" t="s" s="2">
-        <v>84</v>
+        <v>712</v>
       </c>
       <c r="AO103" t="s" s="2">
-        <v>696</v>
+        <v>469</v>
       </c>
       <c r="AP103" t="s" s="2">
-        <v>697</v>
+        <v>470</v>
       </c>
       <c r="AQ103" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR103" t="s" s="2">
-        <v>84</v>
+        <v>471</v>
       </c>
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>738</v>
+        <v>733</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>698</v>
+        <v>734</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -15970,10 +16104,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>739</v>
+        <v>735</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>699</v>
+        <v>736</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -16043,16 +16177,16 @@
         <v>84</v>
       </c>
       <c r="AB105" t="s" s="2">
-        <v>84</v>
+        <v>142</v>
       </c>
       <c r="AC105" t="s" s="2">
-        <v>84</v>
+        <v>160</v>
       </c>
       <c r="AD105" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE105" t="s" s="2">
-        <v>84</v>
+        <v>143</v>
       </c>
       <c r="AF105" t="s" s="2">
         <v>161</v>
@@ -16096,45 +16230,45 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>740</v>
+        <v>737</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>700</v>
+        <v>738</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
-        <v>634</v>
+        <v>84</v>
       </c>
       <c r="E106" s="2"/>
       <c r="F106" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="G106" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H106" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I106" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="J106" t="s" s="2">
         <v>95</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>139</v>
+        <v>481</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>635</v>
+        <v>482</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>636</v>
+        <v>483</v>
       </c>
       <c r="N106" t="s" s="2">
-        <v>183</v>
+        <v>484</v>
       </c>
       <c r="O106" t="s" s="2">
-        <v>184</v>
+        <v>485</v>
       </c>
       <c r="P106" t="s" s="2">
         <v>84</v>
@@ -16183,25 +16317,25 @@
         <v>84</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>637</v>
+        <v>486</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH106" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI106" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ106" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK106" t="s" s="2">
-        <v>84</v>
+        <v>739</v>
       </c>
       <c r="AL106" t="s" s="2">
-        <v>84</v>
+        <v>488</v>
       </c>
       <c r="AM106" t="s" s="2">
         <v>84</v>
@@ -16210,10 +16344,10 @@
         <v>84</v>
       </c>
       <c r="AO106" t="s" s="2">
-        <v>84</v>
+        <v>489</v>
       </c>
       <c r="AP106" t="s" s="2">
-        <v>137</v>
+        <v>490</v>
       </c>
       <c r="AQ106" t="s" s="2">
         <v>84</v>
@@ -16224,10 +16358,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
+        <v>740</v>
+      </c>
+      <c r="B107" t="s" s="2">
         <v>741</v>
-      </c>
-      <c r="B107" t="s" s="2">
-        <v>701</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -16235,44 +16369,44 @@
       </c>
       <c r="E107" s="2"/>
       <c r="F107" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="G107" t="s" s="2">
         <v>94</v>
       </c>
       <c r="H107" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I107" t="s" s="2">
         <v>95</v>
-      </c>
-      <c r="I107" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="J107" t="s" s="2">
         <v>95</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>171</v>
+        <v>114</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>742</v>
+        <v>493</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>703</v>
-      </c>
-      <c r="N107" t="s" s="2">
-        <v>704</v>
-      </c>
+        <v>494</v>
+      </c>
+      <c r="N107" s="2"/>
       <c r="O107" t="s" s="2">
-        <v>705</v>
+        <v>495</v>
       </c>
       <c r="P107" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="Q107" s="2"/>
+      <c r="Q107" t="s" s="2">
+        <v>496</v>
+      </c>
       <c r="R107" t="s" s="2">
         <v>84</v>
       </c>
       <c r="S107" t="s" s="2">
-        <v>743</v>
+        <v>84</v>
       </c>
       <c r="T107" t="s" s="2">
         <v>84</v>
@@ -16287,13 +16421,13 @@
         <v>84</v>
       </c>
       <c r="X107" t="s" s="2">
-        <v>214</v>
+        <v>174</v>
       </c>
       <c r="Y107" t="s" s="2">
-        <v>375</v>
+        <v>497</v>
       </c>
       <c r="Z107" t="s" s="2">
-        <v>376</v>
+        <v>498</v>
       </c>
       <c r="AA107" t="s" s="2">
         <v>84</v>
@@ -16311,10 +16445,10 @@
         <v>84</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>701</v>
+        <v>499</v>
       </c>
       <c r="AG107" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AH107" t="s" s="2">
         <v>94</v>
@@ -16335,16 +16469,16 @@
         <v>84</v>
       </c>
       <c r="AN107" t="s" s="2">
-        <v>706</v>
+        <v>84</v>
       </c>
       <c r="AO107" t="s" s="2">
-        <v>379</v>
+        <v>500</v>
       </c>
       <c r="AP107" t="s" s="2">
-        <v>380</v>
+        <v>501</v>
       </c>
       <c r="AQ107" t="s" s="2">
-        <v>381</v>
+        <v>84</v>
       </c>
       <c r="AR107" t="s" s="2">
         <v>84</v>
@@ -16352,10 +16486,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>744</v>
+        <v>742</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>707</v>
+        <v>743</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -16363,7 +16497,7 @@
       </c>
       <c r="E108" s="2"/>
       <c r="F108" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="G108" t="s" s="2">
         <v>94</v>
@@ -16378,19 +16512,17 @@
         <v>95</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>474</v>
+        <v>196</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>708</v>
+        <v>504</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>709</v>
-      </c>
-      <c r="N108" t="s" s="2">
-        <v>710</v>
-      </c>
+        <v>505</v>
+      </c>
+      <c r="N108" s="2"/>
       <c r="O108" t="s" s="2">
-        <v>464</v>
+        <v>506</v>
       </c>
       <c r="P108" t="s" s="2">
         <v>84</v>
@@ -16415,13 +16547,13 @@
         <v>84</v>
       </c>
       <c r="X108" t="s" s="2">
-        <v>214</v>
+        <v>84</v>
       </c>
       <c r="Y108" t="s" s="2">
-        <v>465</v>
+        <v>84</v>
       </c>
       <c r="Z108" t="s" s="2">
-        <v>466</v>
+        <v>84</v>
       </c>
       <c r="AA108" t="s" s="2">
         <v>84</v>
@@ -16439,7 +16571,7 @@
         <v>84</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>707</v>
+        <v>507</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>82</v>
@@ -16448,7 +16580,7 @@
         <v>94</v>
       </c>
       <c r="AI108" t="s" s="2">
-        <v>711</v>
+        <v>84</v>
       </c>
       <c r="AJ108" t="s" s="2">
         <v>106</v>
@@ -16463,27 +16595,27 @@
         <v>84</v>
       </c>
       <c r="AN108" t="s" s="2">
-        <v>712</v>
+        <v>84</v>
       </c>
       <c r="AO108" t="s" s="2">
-        <v>469</v>
+        <v>508</v>
       </c>
       <c r="AP108" t="s" s="2">
-        <v>470</v>
+        <v>509</v>
       </c>
       <c r="AQ108" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR108" t="s" s="2">
-        <v>471</v>
+        <v>84</v>
       </c>
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
+        <v>744</v>
+      </c>
+      <c r="B109" t="s" s="2">
         <v>745</v>
-      </c>
-      <c r="B109" t="s" s="2">
-        <v>716</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -16491,37 +16623,39 @@
       </c>
       <c r="E109" s="2"/>
       <c r="F109" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="G109" t="s" s="2">
         <v>94</v>
       </c>
       <c r="H109" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I109" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J109" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>196</v>
+        <v>108</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>153</v>
+        <v>512</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>154</v>
+        <v>513</v>
       </c>
       <c r="N109" s="2"/>
-      <c r="O109" s="2"/>
+      <c r="O109" t="s" s="2">
+        <v>514</v>
+      </c>
       <c r="P109" t="s" s="2">
         <v>84</v>
       </c>
       <c r="Q109" s="2"/>
       <c r="R109" t="s" s="2">
-        <v>84</v>
+        <v>746</v>
       </c>
       <c r="S109" t="s" s="2">
         <v>84</v>
@@ -16563,7 +16697,7 @@
         <v>84</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>155</v>
+        <v>515</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>82</v>
@@ -16572,10 +16706,10 @@
         <v>94</v>
       </c>
       <c r="AI109" t="s" s="2">
-        <v>84</v>
+        <v>516</v>
       </c>
       <c r="AJ109" t="s" s="2">
-        <v>84</v>
+        <v>106</v>
       </c>
       <c r="AK109" t="s" s="2">
         <v>84</v>
@@ -16590,10 +16724,10 @@
         <v>84</v>
       </c>
       <c r="AO109" t="s" s="2">
-        <v>84</v>
+        <v>508</v>
       </c>
       <c r="AP109" t="s" s="2">
-        <v>157</v>
+        <v>517</v>
       </c>
       <c r="AQ109" t="s" s="2">
         <v>84</v>
@@ -16604,50 +16738,52 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>718</v>
+        <v>748</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
-        <v>180</v>
+        <v>84</v>
       </c>
       <c r="E110" s="2"/>
       <c r="F110" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="G110" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H110" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I110" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J110" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>139</v>
+        <v>114</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>198</v>
+        <v>520</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>199</v>
+        <v>521</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="O110" s="2"/>
+        <v>522</v>
+      </c>
+      <c r="O110" t="s" s="2">
+        <v>523</v>
+      </c>
       <c r="P110" t="s" s="2">
         <v>84</v>
       </c>
       <c r="Q110" s="2"/>
       <c r="R110" t="s" s="2">
-        <v>84</v>
+        <v>749</v>
       </c>
       <c r="S110" t="s" s="2">
         <v>84</v>
@@ -16677,31 +16813,31 @@
         <v>84</v>
       </c>
       <c r="AB110" t="s" s="2">
-        <v>142</v>
+        <v>84</v>
       </c>
       <c r="AC110" t="s" s="2">
-        <v>160</v>
+        <v>84</v>
       </c>
       <c r="AD110" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE110" t="s" s="2">
-        <v>143</v>
+        <v>84</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>161</v>
+        <v>524</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH110" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI110" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ110" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK110" t="s" s="2">
         <v>84</v>
@@ -16716,10 +16852,10 @@
         <v>84</v>
       </c>
       <c r="AO110" t="s" s="2">
-        <v>84</v>
+        <v>508</v>
       </c>
       <c r="AP110" t="s" s="2">
-        <v>157</v>
+        <v>526</v>
       </c>
       <c r="AQ110" t="s" s="2">
         <v>84</v>
@@ -16730,10 +16866,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>747</v>
+        <v>750</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>748</v>
+        <v>713</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -16741,7 +16877,7 @@
       </c>
       <c r="E111" s="2"/>
       <c r="F111" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="G111" t="s" s="2">
         <v>94</v>
@@ -16753,22 +16889,22 @@
         <v>84</v>
       </c>
       <c r="J111" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>481</v>
+        <v>171</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>482</v>
+        <v>714</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>483</v>
+        <v>715</v>
       </c>
       <c r="N111" t="s" s="2">
-        <v>484</v>
+        <v>716</v>
       </c>
       <c r="O111" t="s" s="2">
-        <v>485</v>
+        <v>558</v>
       </c>
       <c r="P111" t="s" s="2">
         <v>84</v>
@@ -16793,13 +16929,13 @@
         <v>84</v>
       </c>
       <c r="X111" t="s" s="2">
-        <v>84</v>
+        <v>214</v>
       </c>
       <c r="Y111" t="s" s="2">
-        <v>84</v>
+        <v>559</v>
       </c>
       <c r="Z111" t="s" s="2">
-        <v>84</v>
+        <v>560</v>
       </c>
       <c r="AA111" t="s" s="2">
         <v>84</v>
@@ -16817,7 +16953,7 @@
         <v>84</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>486</v>
+        <v>713</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>82</v>
@@ -16826,16 +16962,16 @@
         <v>94</v>
       </c>
       <c r="AI111" t="s" s="2">
-        <v>84</v>
+        <v>717</v>
       </c>
       <c r="AJ111" t="s" s="2">
         <v>106</v>
       </c>
       <c r="AK111" t="s" s="2">
-        <v>749</v>
+        <v>84</v>
       </c>
       <c r="AL111" t="s" s="2">
-        <v>488</v>
+        <v>84</v>
       </c>
       <c r="AM111" t="s" s="2">
         <v>84</v>
@@ -16844,10 +16980,10 @@
         <v>84</v>
       </c>
       <c r="AO111" t="s" s="2">
-        <v>489</v>
+        <v>137</v>
       </c>
       <c r="AP111" t="s" s="2">
-        <v>490</v>
+        <v>563</v>
       </c>
       <c r="AQ111" t="s" s="2">
         <v>84</v>
@@ -16858,50 +16994,50 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>751</v>
+        <v>719</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
-        <v>84</v>
+        <v>565</v>
       </c>
       <c r="E112" s="2"/>
       <c r="F112" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G112" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H112" t="s" s="2">
         <v>84</v>
       </c>
       <c r="I112" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="J112" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>114</v>
+        <v>171</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>493</v>
+        <v>566</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>494</v>
-      </c>
-      <c r="N112" s="2"/>
+        <v>567</v>
+      </c>
+      <c r="N112" t="s" s="2">
+        <v>568</v>
+      </c>
       <c r="O112" t="s" s="2">
-        <v>495</v>
+        <v>569</v>
       </c>
       <c r="P112" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="Q112" t="s" s="2">
-        <v>496</v>
-      </c>
+      <c r="Q112" s="2"/>
       <c r="R112" t="s" s="2">
         <v>84</v>
       </c>
@@ -16921,13 +17057,13 @@
         <v>84</v>
       </c>
       <c r="X112" t="s" s="2">
-        <v>174</v>
+        <v>214</v>
       </c>
       <c r="Y112" t="s" s="2">
-        <v>497</v>
+        <v>570</v>
       </c>
       <c r="Z112" t="s" s="2">
-        <v>498</v>
+        <v>571</v>
       </c>
       <c r="AA112" t="s" s="2">
         <v>84</v>
@@ -16945,13 +17081,13 @@
         <v>84</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>499</v>
+        <v>719</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH112" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI112" t="s" s="2">
         <v>84</v>
@@ -16969,19 +17105,19 @@
         <v>84</v>
       </c>
       <c r="AN112" t="s" s="2">
-        <v>84</v>
+        <v>572</v>
       </c>
       <c r="AO112" t="s" s="2">
-        <v>500</v>
+        <v>573</v>
       </c>
       <c r="AP112" t="s" s="2">
-        <v>501</v>
+        <v>574</v>
       </c>
       <c r="AQ112" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR112" t="s" s="2">
-        <v>84</v>
+        <v>575</v>
       </c>
     </row>
     <row r="113" hidden="true">
@@ -16989,7 +17125,7 @@
         <v>752</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>753</v>
+        <v>720</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -16997,32 +17133,34 @@
       </c>
       <c r="E113" s="2"/>
       <c r="F113" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="G113" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H113" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="I113" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J113" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>196</v>
+        <v>85</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>504</v>
+        <v>721</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>505</v>
-      </c>
-      <c r="N113" s="2"/>
+        <v>722</v>
+      </c>
+      <c r="N113" t="s" s="2">
+        <v>626</v>
+      </c>
       <c r="O113" t="s" s="2">
-        <v>506</v>
+        <v>627</v>
       </c>
       <c r="P113" t="s" s="2">
         <v>84</v>
@@ -17071,13 +17209,13 @@
         <v>84</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>507</v>
+        <v>720</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH113" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI113" t="s" s="2">
         <v>84</v>
@@ -17098,10 +17236,10 @@
         <v>84</v>
       </c>
       <c r="AO113" t="s" s="2">
-        <v>508</v>
+        <v>629</v>
       </c>
       <c r="AP113" t="s" s="2">
-        <v>509</v>
+        <v>630</v>
       </c>
       <c r="AQ113" t="s" s="2">
         <v>84</v>
@@ -17112,12 +17250,14 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
+        <v>753</v>
+      </c>
+      <c r="B114" t="s" s="2">
+        <v>688</v>
+      </c>
+      <c r="C114" t="s" s="2">
         <v>754</v>
       </c>
-      <c r="B114" t="s" s="2">
-        <v>755</v>
-      </c>
-      <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
         <v>84</v>
       </c>
@@ -17138,24 +17278,26 @@
         <v>95</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>108</v>
+        <v>623</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>512</v>
+        <v>755</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>513</v>
-      </c>
-      <c r="N114" s="2"/>
+        <v>691</v>
+      </c>
+      <c r="N114" t="s" s="2">
+        <v>692</v>
+      </c>
       <c r="O114" t="s" s="2">
-        <v>514</v>
+        <v>693</v>
       </c>
       <c r="P114" t="s" s="2">
         <v>84</v>
       </c>
       <c r="Q114" s="2"/>
       <c r="R114" t="s" s="2">
-        <v>756</v>
+        <v>84</v>
       </c>
       <c r="S114" t="s" s="2">
         <v>84</v>
@@ -17197,19 +17339,19 @@
         <v>84</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>515</v>
+        <v>688</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH114" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI114" t="s" s="2">
-        <v>516</v>
+        <v>84</v>
       </c>
       <c r="AJ114" t="s" s="2">
-        <v>106</v>
+        <v>695</v>
       </c>
       <c r="AK114" t="s" s="2">
         <v>84</v>
@@ -17224,10 +17366,10 @@
         <v>84</v>
       </c>
       <c r="AO114" t="s" s="2">
-        <v>508</v>
+        <v>696</v>
       </c>
       <c r="AP114" t="s" s="2">
-        <v>517</v>
+        <v>697</v>
       </c>
       <c r="AQ114" t="s" s="2">
         <v>84</v>
@@ -17238,10 +17380,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>758</v>
+        <v>698</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -17249,41 +17391,37 @@
       </c>
       <c r="E115" s="2"/>
       <c r="F115" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="G115" t="s" s="2">
         <v>94</v>
       </c>
       <c r="H115" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="I115" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J115" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>114</v>
+        <v>196</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>520</v>
+        <v>153</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>521</v>
-      </c>
-      <c r="N115" t="s" s="2">
-        <v>522</v>
-      </c>
-      <c r="O115" t="s" s="2">
-        <v>523</v>
-      </c>
+        <v>154</v>
+      </c>
+      <c r="N115" s="2"/>
+      <c r="O115" s="2"/>
       <c r="P115" t="s" s="2">
         <v>84</v>
       </c>
       <c r="Q115" s="2"/>
       <c r="R115" t="s" s="2">
-        <v>759</v>
+        <v>84</v>
       </c>
       <c r="S115" t="s" s="2">
         <v>84</v>
@@ -17325,7 +17463,7 @@
         <v>84</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>524</v>
+        <v>155</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>82</v>
@@ -17337,7 +17475,7 @@
         <v>84</v>
       </c>
       <c r="AJ115" t="s" s="2">
-        <v>106</v>
+        <v>84</v>
       </c>
       <c r="AK115" t="s" s="2">
         <v>84</v>
@@ -17352,10 +17490,10 @@
         <v>84</v>
       </c>
       <c r="AO115" t="s" s="2">
-        <v>508</v>
+        <v>84</v>
       </c>
       <c r="AP115" t="s" s="2">
-        <v>526</v>
+        <v>157</v>
       </c>
       <c r="AQ115" t="s" s="2">
         <v>84</v>
@@ -17366,24 +17504,24 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>760</v>
+        <v>757</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>725</v>
+        <v>699</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
-        <v>84</v>
+        <v>180</v>
       </c>
       <c r="E116" s="2"/>
       <c r="F116" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G116" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H116" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="I116" t="s" s="2">
         <v>84</v>
@@ -17392,20 +17530,18 @@
         <v>84</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>171</v>
+        <v>139</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>726</v>
+        <v>198</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>727</v>
+        <v>199</v>
       </c>
       <c r="N116" t="s" s="2">
-        <v>728</v>
-      </c>
-      <c r="O116" t="s" s="2">
-        <v>558</v>
-      </c>
+        <v>183</v>
+      </c>
+      <c r="O116" s="2"/>
       <c r="P116" t="s" s="2">
         <v>84</v>
       </c>
@@ -17429,13 +17565,13 @@
         <v>84</v>
       </c>
       <c r="X116" t="s" s="2">
-        <v>214</v>
+        <v>84</v>
       </c>
       <c r="Y116" t="s" s="2">
-        <v>559</v>
+        <v>84</v>
       </c>
       <c r="Z116" t="s" s="2">
-        <v>560</v>
+        <v>84</v>
       </c>
       <c r="AA116" t="s" s="2">
         <v>84</v>
@@ -17453,19 +17589,19 @@
         <v>84</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>725</v>
+        <v>161</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH116" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI116" t="s" s="2">
-        <v>729</v>
+        <v>84</v>
       </c>
       <c r="AJ116" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK116" t="s" s="2">
         <v>84</v>
@@ -17480,10 +17616,10 @@
         <v>84</v>
       </c>
       <c r="AO116" t="s" s="2">
-        <v>137</v>
+        <v>84</v>
       </c>
       <c r="AP116" t="s" s="2">
-        <v>563</v>
+        <v>157</v>
       </c>
       <c r="AQ116" t="s" s="2">
         <v>84</v>
@@ -17494,14 +17630,14 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>761</v>
+        <v>758</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>731</v>
+        <v>700</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
-        <v>565</v>
+        <v>634</v>
       </c>
       <c r="E117" s="2"/>
       <c r="F117" t="s" s="2">
@@ -17514,25 +17650,25 @@
         <v>84</v>
       </c>
       <c r="I117" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="J117" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>171</v>
+        <v>139</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>566</v>
+        <v>635</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>567</v>
+        <v>636</v>
       </c>
       <c r="N117" t="s" s="2">
-        <v>568</v>
+        <v>183</v>
       </c>
       <c r="O117" t="s" s="2">
-        <v>569</v>
+        <v>184</v>
       </c>
       <c r="P117" t="s" s="2">
         <v>84</v>
@@ -17557,13 +17693,13 @@
         <v>84</v>
       </c>
       <c r="X117" t="s" s="2">
-        <v>214</v>
+        <v>84</v>
       </c>
       <c r="Y117" t="s" s="2">
-        <v>570</v>
+        <v>84</v>
       </c>
       <c r="Z117" t="s" s="2">
-        <v>571</v>
+        <v>84</v>
       </c>
       <c r="AA117" t="s" s="2">
         <v>84</v>
@@ -17581,7 +17717,7 @@
         <v>84</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>731</v>
+        <v>637</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>82</v>
@@ -17593,7 +17729,7 @@
         <v>84</v>
       </c>
       <c r="AJ117" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK117" t="s" s="2">
         <v>84</v>
@@ -17605,27 +17741,27 @@
         <v>84</v>
       </c>
       <c r="AN117" t="s" s="2">
-        <v>572</v>
+        <v>84</v>
       </c>
       <c r="AO117" t="s" s="2">
-        <v>573</v>
+        <v>84</v>
       </c>
       <c r="AP117" t="s" s="2">
-        <v>574</v>
+        <v>137</v>
       </c>
       <c r="AQ117" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR117" t="s" s="2">
-        <v>575</v>
+        <v>84</v>
       </c>
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>762</v>
+        <v>759</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>732</v>
+        <v>701</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -17633,34 +17769,34 @@
       </c>
       <c r="E118" s="2"/>
       <c r="F118" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="G118" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H118" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I118" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J118" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K118" t="s" s="2">
-        <v>85</v>
+        <v>171</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>733</v>
+        <v>760</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>734</v>
+        <v>703</v>
       </c>
       <c r="N118" t="s" s="2">
-        <v>626</v>
+        <v>704</v>
       </c>
       <c r="O118" t="s" s="2">
-        <v>627</v>
+        <v>705</v>
       </c>
       <c r="P118" t="s" s="2">
         <v>84</v>
@@ -17670,7 +17806,7 @@
         <v>84</v>
       </c>
       <c r="S118" t="s" s="2">
-        <v>84</v>
+        <v>761</v>
       </c>
       <c r="T118" t="s" s="2">
         <v>84</v>
@@ -17685,13 +17821,13 @@
         <v>84</v>
       </c>
       <c r="X118" t="s" s="2">
-        <v>84</v>
+        <v>214</v>
       </c>
       <c r="Y118" t="s" s="2">
-        <v>84</v>
+        <v>375</v>
       </c>
       <c r="Z118" t="s" s="2">
-        <v>84</v>
+        <v>376</v>
       </c>
       <c r="AA118" t="s" s="2">
         <v>84</v>
@@ -17709,13 +17845,13 @@
         <v>84</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>732</v>
+        <v>701</v>
       </c>
       <c r="AG118" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AH118" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI118" t="s" s="2">
         <v>84</v>
@@ -17733,16 +17869,16 @@
         <v>84</v>
       </c>
       <c r="AN118" t="s" s="2">
-        <v>84</v>
+        <v>706</v>
       </c>
       <c r="AO118" t="s" s="2">
-        <v>629</v>
+        <v>379</v>
       </c>
       <c r="AP118" t="s" s="2">
-        <v>630</v>
+        <v>380</v>
       </c>
       <c r="AQ118" t="s" s="2">
-        <v>84</v>
+        <v>381</v>
       </c>
       <c r="AR118" t="s" s="2">
         <v>84</v>
@@ -17750,20 +17886,18 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>688</v>
-      </c>
-      <c r="C119" t="s" s="2">
-        <v>764</v>
-      </c>
+        <v>707</v>
+      </c>
+      <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
         <v>84</v>
       </c>
       <c r="E119" s="2"/>
       <c r="F119" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="G119" t="s" s="2">
         <v>94</v>
@@ -17778,19 +17912,19 @@
         <v>95</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>623</v>
+        <v>474</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>765</v>
+        <v>708</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>691</v>
+        <v>709</v>
       </c>
       <c r="N119" t="s" s="2">
-        <v>692</v>
+        <v>710</v>
       </c>
       <c r="O119" t="s" s="2">
-        <v>693</v>
+        <v>464</v>
       </c>
       <c r="P119" t="s" s="2">
         <v>84</v>
@@ -17815,13 +17949,13 @@
         <v>84</v>
       </c>
       <c r="X119" t="s" s="2">
-        <v>84</v>
+        <v>214</v>
       </c>
       <c r="Y119" t="s" s="2">
-        <v>84</v>
+        <v>465</v>
       </c>
       <c r="Z119" t="s" s="2">
-        <v>84</v>
+        <v>466</v>
       </c>
       <c r="AA119" t="s" s="2">
         <v>84</v>
@@ -17839,19 +17973,19 @@
         <v>84</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>688</v>
+        <v>707</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH119" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI119" t="s" s="2">
-        <v>84</v>
+        <v>711</v>
       </c>
       <c r="AJ119" t="s" s="2">
-        <v>695</v>
+        <v>106</v>
       </c>
       <c r="AK119" t="s" s="2">
         <v>84</v>
@@ -17863,27 +17997,27 @@
         <v>84</v>
       </c>
       <c r="AN119" t="s" s="2">
-        <v>84</v>
+        <v>712</v>
       </c>
       <c r="AO119" t="s" s="2">
-        <v>696</v>
+        <v>469</v>
       </c>
       <c r="AP119" t="s" s="2">
-        <v>697</v>
+        <v>470</v>
       </c>
       <c r="AQ119" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR119" t="s" s="2">
-        <v>84</v>
+        <v>471</v>
       </c>
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>766</v>
+        <v>763</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>698</v>
+        <v>734</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -18004,10 +18138,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>767</v>
+        <v>764</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>699</v>
+        <v>736</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -18077,16 +18211,16 @@
         <v>84</v>
       </c>
       <c r="AB121" t="s" s="2">
-        <v>84</v>
+        <v>142</v>
       </c>
       <c r="AC121" t="s" s="2">
-        <v>84</v>
+        <v>160</v>
       </c>
       <c r="AD121" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE121" t="s" s="2">
-        <v>84</v>
+        <v>143</v>
       </c>
       <c r="AF121" t="s" s="2">
         <v>161</v>
@@ -18130,45 +18264,45 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>768</v>
+        <v>765</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>700</v>
+        <v>738</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
-        <v>634</v>
+        <v>84</v>
       </c>
       <c r="E122" s="2"/>
       <c r="F122" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="G122" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H122" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I122" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="J122" t="s" s="2">
         <v>95</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>139</v>
+        <v>481</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>635</v>
+        <v>482</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>636</v>
+        <v>483</v>
       </c>
       <c r="N122" t="s" s="2">
-        <v>183</v>
+        <v>484</v>
       </c>
       <c r="O122" t="s" s="2">
-        <v>184</v>
+        <v>485</v>
       </c>
       <c r="P122" t="s" s="2">
         <v>84</v>
@@ -18217,25 +18351,25 @@
         <v>84</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>637</v>
+        <v>486</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH122" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI122" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ122" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK122" t="s" s="2">
-        <v>84</v>
+        <v>766</v>
       </c>
       <c r="AL122" t="s" s="2">
-        <v>84</v>
+        <v>488</v>
       </c>
       <c r="AM122" t="s" s="2">
         <v>84</v>
@@ -18244,10 +18378,10 @@
         <v>84</v>
       </c>
       <c r="AO122" t="s" s="2">
-        <v>84</v>
+        <v>489</v>
       </c>
       <c r="AP122" t="s" s="2">
-        <v>137</v>
+        <v>490</v>
       </c>
       <c r="AQ122" t="s" s="2">
         <v>84</v>
@@ -18258,10 +18392,10 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>701</v>
+        <v>741</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -18269,44 +18403,44 @@
       </c>
       <c r="E123" s="2"/>
       <c r="F123" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="G123" t="s" s="2">
         <v>94</v>
       </c>
       <c r="H123" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I123" t="s" s="2">
         <v>95</v>
-      </c>
-      <c r="I123" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="J123" t="s" s="2">
         <v>95</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>171</v>
+        <v>114</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>770</v>
+        <v>493</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>703</v>
-      </c>
-      <c r="N123" t="s" s="2">
-        <v>704</v>
-      </c>
+        <v>494</v>
+      </c>
+      <c r="N123" s="2"/>
       <c r="O123" t="s" s="2">
-        <v>705</v>
+        <v>495</v>
       </c>
       <c r="P123" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="Q123" s="2"/>
+      <c r="Q123" t="s" s="2">
+        <v>496</v>
+      </c>
       <c r="R123" t="s" s="2">
         <v>84</v>
       </c>
       <c r="S123" t="s" s="2">
-        <v>771</v>
+        <v>84</v>
       </c>
       <c r="T123" t="s" s="2">
         <v>84</v>
@@ -18321,13 +18455,13 @@
         <v>84</v>
       </c>
       <c r="X123" t="s" s="2">
-        <v>214</v>
+        <v>174</v>
       </c>
       <c r="Y123" t="s" s="2">
-        <v>375</v>
+        <v>497</v>
       </c>
       <c r="Z123" t="s" s="2">
-        <v>376</v>
+        <v>498</v>
       </c>
       <c r="AA123" t="s" s="2">
         <v>84</v>
@@ -18345,10 +18479,10 @@
         <v>84</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>701</v>
+        <v>499</v>
       </c>
       <c r="AG123" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AH123" t="s" s="2">
         <v>94</v>
@@ -18369,16 +18503,16 @@
         <v>84</v>
       </c>
       <c r="AN123" t="s" s="2">
-        <v>706</v>
+        <v>84</v>
       </c>
       <c r="AO123" t="s" s="2">
-        <v>379</v>
+        <v>500</v>
       </c>
       <c r="AP123" t="s" s="2">
-        <v>380</v>
+        <v>501</v>
       </c>
       <c r="AQ123" t="s" s="2">
-        <v>381</v>
+        <v>84</v>
       </c>
       <c r="AR123" t="s" s="2">
         <v>84</v>
@@ -18386,10 +18520,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>772</v>
+        <v>768</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>707</v>
+        <v>743</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -18397,7 +18531,7 @@
       </c>
       <c r="E124" s="2"/>
       <c r="F124" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="G124" t="s" s="2">
         <v>94</v>
@@ -18412,19 +18546,17 @@
         <v>95</v>
       </c>
       <c r="K124" t="s" s="2">
-        <v>474</v>
+        <v>196</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>708</v>
+        <v>504</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>709</v>
-      </c>
-      <c r="N124" t="s" s="2">
-        <v>710</v>
-      </c>
+        <v>505</v>
+      </c>
+      <c r="N124" s="2"/>
       <c r="O124" t="s" s="2">
-        <v>464</v>
+        <v>506</v>
       </c>
       <c r="P124" t="s" s="2">
         <v>84</v>
@@ -18449,13 +18581,13 @@
         <v>84</v>
       </c>
       <c r="X124" t="s" s="2">
-        <v>214</v>
+        <v>84</v>
       </c>
       <c r="Y124" t="s" s="2">
-        <v>465</v>
+        <v>84</v>
       </c>
       <c r="Z124" t="s" s="2">
-        <v>466</v>
+        <v>84</v>
       </c>
       <c r="AA124" t="s" s="2">
         <v>84</v>
@@ -18473,7 +18605,7 @@
         <v>84</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>707</v>
+        <v>507</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>82</v>
@@ -18482,7 +18614,7 @@
         <v>94</v>
       </c>
       <c r="AI124" t="s" s="2">
-        <v>711</v>
+        <v>84</v>
       </c>
       <c r="AJ124" t="s" s="2">
         <v>106</v>
@@ -18497,27 +18629,27 @@
         <v>84</v>
       </c>
       <c r="AN124" t="s" s="2">
-        <v>712</v>
+        <v>84</v>
       </c>
       <c r="AO124" t="s" s="2">
-        <v>469</v>
+        <v>508</v>
       </c>
       <c r="AP124" t="s" s="2">
-        <v>470</v>
+        <v>509</v>
       </c>
       <c r="AQ124" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR124" t="s" s="2">
-        <v>471</v>
+        <v>84</v>
       </c>
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>773</v>
+        <v>769</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>716</v>
+        <v>745</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -18525,37 +18657,39 @@
       </c>
       <c r="E125" s="2"/>
       <c r="F125" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="G125" t="s" s="2">
         <v>94</v>
       </c>
       <c r="H125" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I125" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J125" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>196</v>
+        <v>108</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>153</v>
+        <v>512</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>154</v>
+        <v>513</v>
       </c>
       <c r="N125" s="2"/>
-      <c r="O125" s="2"/>
+      <c r="O125" t="s" s="2">
+        <v>514</v>
+      </c>
       <c r="P125" t="s" s="2">
         <v>84</v>
       </c>
       <c r="Q125" s="2"/>
       <c r="R125" t="s" s="2">
-        <v>84</v>
+        <v>746</v>
       </c>
       <c r="S125" t="s" s="2">
         <v>84</v>
@@ -18597,7 +18731,7 @@
         <v>84</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>155</v>
+        <v>515</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>82</v>
@@ -18606,10 +18740,10 @@
         <v>94</v>
       </c>
       <c r="AI125" t="s" s="2">
-        <v>84</v>
+        <v>516</v>
       </c>
       <c r="AJ125" t="s" s="2">
-        <v>84</v>
+        <v>106</v>
       </c>
       <c r="AK125" t="s" s="2">
         <v>84</v>
@@ -18624,10 +18758,10 @@
         <v>84</v>
       </c>
       <c r="AO125" t="s" s="2">
-        <v>84</v>
+        <v>508</v>
       </c>
       <c r="AP125" t="s" s="2">
-        <v>157</v>
+        <v>517</v>
       </c>
       <c r="AQ125" t="s" s="2">
         <v>84</v>
@@ -18638,50 +18772,52 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>774</v>
+        <v>770</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>718</v>
+        <v>748</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
-        <v>180</v>
+        <v>84</v>
       </c>
       <c r="E126" s="2"/>
       <c r="F126" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="G126" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H126" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I126" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J126" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K126" t="s" s="2">
-        <v>139</v>
+        <v>114</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>198</v>
+        <v>520</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>199</v>
+        <v>521</v>
       </c>
       <c r="N126" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="O126" s="2"/>
+        <v>522</v>
+      </c>
+      <c r="O126" t="s" s="2">
+        <v>523</v>
+      </c>
       <c r="P126" t="s" s="2">
         <v>84</v>
       </c>
       <c r="Q126" s="2"/>
       <c r="R126" t="s" s="2">
-        <v>84</v>
+        <v>749</v>
       </c>
       <c r="S126" t="s" s="2">
         <v>84</v>
@@ -18711,31 +18847,31 @@
         <v>84</v>
       </c>
       <c r="AB126" t="s" s="2">
-        <v>142</v>
+        <v>84</v>
       </c>
       <c r="AC126" t="s" s="2">
-        <v>160</v>
+        <v>84</v>
       </c>
       <c r="AD126" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE126" t="s" s="2">
-        <v>143</v>
+        <v>84</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>161</v>
+        <v>524</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH126" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI126" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ126" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK126" t="s" s="2">
         <v>84</v>
@@ -18750,10 +18886,10 @@
         <v>84</v>
       </c>
       <c r="AO126" t="s" s="2">
-        <v>84</v>
+        <v>508</v>
       </c>
       <c r="AP126" t="s" s="2">
-        <v>157</v>
+        <v>526</v>
       </c>
       <c r="AQ126" t="s" s="2">
         <v>84</v>
@@ -18764,10 +18900,10 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>775</v>
+        <v>771</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>748</v>
+        <v>713</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -18775,7 +18911,7 @@
       </c>
       <c r="E127" s="2"/>
       <c r="F127" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="G127" t="s" s="2">
         <v>94</v>
@@ -18787,22 +18923,22 @@
         <v>84</v>
       </c>
       <c r="J127" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K127" t="s" s="2">
-        <v>481</v>
+        <v>171</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>482</v>
+        <v>714</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>483</v>
+        <v>715</v>
       </c>
       <c r="N127" t="s" s="2">
-        <v>484</v>
+        <v>716</v>
       </c>
       <c r="O127" t="s" s="2">
-        <v>485</v>
+        <v>558</v>
       </c>
       <c r="P127" t="s" s="2">
         <v>84</v>
@@ -18827,13 +18963,13 @@
         <v>84</v>
       </c>
       <c r="X127" t="s" s="2">
-        <v>84</v>
+        <v>214</v>
       </c>
       <c r="Y127" t="s" s="2">
-        <v>84</v>
+        <v>559</v>
       </c>
       <c r="Z127" t="s" s="2">
-        <v>84</v>
+        <v>560</v>
       </c>
       <c r="AA127" t="s" s="2">
         <v>84</v>
@@ -18851,7 +18987,7 @@
         <v>84</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>486</v>
+        <v>713</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>82</v>
@@ -18860,16 +18996,16 @@
         <v>94</v>
       </c>
       <c r="AI127" t="s" s="2">
-        <v>84</v>
+        <v>717</v>
       </c>
       <c r="AJ127" t="s" s="2">
         <v>106</v>
       </c>
       <c r="AK127" t="s" s="2">
-        <v>776</v>
+        <v>84</v>
       </c>
       <c r="AL127" t="s" s="2">
-        <v>488</v>
+        <v>84</v>
       </c>
       <c r="AM127" t="s" s="2">
         <v>84</v>
@@ -18878,10 +19014,10 @@
         <v>84</v>
       </c>
       <c r="AO127" t="s" s="2">
-        <v>489</v>
+        <v>137</v>
       </c>
       <c r="AP127" t="s" s="2">
-        <v>490</v>
+        <v>563</v>
       </c>
       <c r="AQ127" t="s" s="2">
         <v>84</v>
@@ -18892,50 +19028,50 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>777</v>
+        <v>772</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>751</v>
+        <v>719</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
-        <v>84</v>
+        <v>565</v>
       </c>
       <c r="E128" s="2"/>
       <c r="F128" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G128" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H128" t="s" s="2">
         <v>84</v>
       </c>
       <c r="I128" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="J128" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K128" t="s" s="2">
-        <v>114</v>
+        <v>171</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>493</v>
+        <v>566</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>494</v>
-      </c>
-      <c r="N128" s="2"/>
+        <v>567</v>
+      </c>
+      <c r="N128" t="s" s="2">
+        <v>568</v>
+      </c>
       <c r="O128" t="s" s="2">
-        <v>495</v>
+        <v>569</v>
       </c>
       <c r="P128" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="Q128" t="s" s="2">
-        <v>496</v>
-      </c>
+      <c r="Q128" s="2"/>
       <c r="R128" t="s" s="2">
         <v>84</v>
       </c>
@@ -18955,13 +19091,13 @@
         <v>84</v>
       </c>
       <c r="X128" t="s" s="2">
-        <v>174</v>
+        <v>214</v>
       </c>
       <c r="Y128" t="s" s="2">
-        <v>497</v>
+        <v>570</v>
       </c>
       <c r="Z128" t="s" s="2">
-        <v>498</v>
+        <v>571</v>
       </c>
       <c r="AA128" t="s" s="2">
         <v>84</v>
@@ -18979,13 +19115,13 @@
         <v>84</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>499</v>
+        <v>719</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH128" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI128" t="s" s="2">
         <v>84</v>
@@ -19003,27 +19139,27 @@
         <v>84</v>
       </c>
       <c r="AN128" t="s" s="2">
-        <v>84</v>
+        <v>572</v>
       </c>
       <c r="AO128" t="s" s="2">
-        <v>500</v>
+        <v>573</v>
       </c>
       <c r="AP128" t="s" s="2">
-        <v>501</v>
+        <v>574</v>
       </c>
       <c r="AQ128" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR128" t="s" s="2">
-        <v>84</v>
+        <v>575</v>
       </c>
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>778</v>
+        <v>773</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>753</v>
+        <v>720</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -19031,32 +19167,34 @@
       </c>
       <c r="E129" s="2"/>
       <c r="F129" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="G129" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H129" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="I129" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J129" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K129" t="s" s="2">
-        <v>196</v>
+        <v>85</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>504</v>
+        <v>721</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>505</v>
-      </c>
-      <c r="N129" s="2"/>
+        <v>722</v>
+      </c>
+      <c r="N129" t="s" s="2">
+        <v>626</v>
+      </c>
       <c r="O129" t="s" s="2">
-        <v>506</v>
+        <v>627</v>
       </c>
       <c r="P129" t="s" s="2">
         <v>84</v>
@@ -19105,13 +19243,13 @@
         <v>84</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>507</v>
+        <v>720</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH129" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI129" t="s" s="2">
         <v>84</v>
@@ -19132,10 +19270,10 @@
         <v>84</v>
       </c>
       <c r="AO129" t="s" s="2">
-        <v>508</v>
+        <v>629</v>
       </c>
       <c r="AP129" t="s" s="2">
-        <v>509</v>
+        <v>630</v>
       </c>
       <c r="AQ129" t="s" s="2">
         <v>84</v>
@@ -19146,18 +19284,20 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>779</v>
+        <v>774</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>755</v>
-      </c>
-      <c r="C130" s="2"/>
+        <v>688</v>
+      </c>
+      <c r="C130" t="s" s="2">
+        <v>775</v>
+      </c>
       <c r="D130" t="s" s="2">
         <v>84</v>
       </c>
       <c r="E130" s="2"/>
       <c r="F130" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="G130" t="s" s="2">
         <v>94</v>
@@ -19172,24 +19312,26 @@
         <v>95</v>
       </c>
       <c r="K130" t="s" s="2">
-        <v>108</v>
+        <v>623</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>512</v>
+        <v>690</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>513</v>
-      </c>
-      <c r="N130" s="2"/>
+        <v>691</v>
+      </c>
+      <c r="N130" t="s" s="2">
+        <v>692</v>
+      </c>
       <c r="O130" t="s" s="2">
-        <v>514</v>
+        <v>693</v>
       </c>
       <c r="P130" t="s" s="2">
         <v>84</v>
       </c>
       <c r="Q130" s="2"/>
       <c r="R130" t="s" s="2">
-        <v>756</v>
+        <v>84</v>
       </c>
       <c r="S130" t="s" s="2">
         <v>84</v>
@@ -19231,19 +19373,19 @@
         <v>84</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>515</v>
+        <v>688</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH130" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI130" t="s" s="2">
-        <v>516</v>
+        <v>84</v>
       </c>
       <c r="AJ130" t="s" s="2">
-        <v>106</v>
+        <v>695</v>
       </c>
       <c r="AK130" t="s" s="2">
         <v>84</v>
@@ -19258,10 +19400,10 @@
         <v>84</v>
       </c>
       <c r="AO130" t="s" s="2">
-        <v>508</v>
+        <v>696</v>
       </c>
       <c r="AP130" t="s" s="2">
-        <v>517</v>
+        <v>697</v>
       </c>
       <c r="AQ130" t="s" s="2">
         <v>84</v>
@@ -19272,10 +19414,10 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>780</v>
+        <v>776</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>758</v>
+        <v>698</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -19283,41 +19425,37 @@
       </c>
       <c r="E131" s="2"/>
       <c r="F131" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="G131" t="s" s="2">
         <v>94</v>
       </c>
       <c r="H131" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="I131" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J131" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K131" t="s" s="2">
-        <v>114</v>
+        <v>196</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>520</v>
+        <v>153</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>521</v>
-      </c>
-      <c r="N131" t="s" s="2">
-        <v>522</v>
-      </c>
-      <c r="O131" t="s" s="2">
-        <v>523</v>
-      </c>
+        <v>154</v>
+      </c>
+      <c r="N131" s="2"/>
+      <c r="O131" s="2"/>
       <c r="P131" t="s" s="2">
         <v>84</v>
       </c>
       <c r="Q131" s="2"/>
       <c r="R131" t="s" s="2">
-        <v>759</v>
+        <v>84</v>
       </c>
       <c r="S131" t="s" s="2">
         <v>84</v>
@@ -19359,7 +19497,7 @@
         <v>84</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>524</v>
+        <v>155</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>82</v>
@@ -19371,7 +19509,7 @@
         <v>84</v>
       </c>
       <c r="AJ131" t="s" s="2">
-        <v>106</v>
+        <v>84</v>
       </c>
       <c r="AK131" t="s" s="2">
         <v>84</v>
@@ -19386,10 +19524,10 @@
         <v>84</v>
       </c>
       <c r="AO131" t="s" s="2">
-        <v>508</v>
+        <v>84</v>
       </c>
       <c r="AP131" t="s" s="2">
-        <v>526</v>
+        <v>157</v>
       </c>
       <c r="AQ131" t="s" s="2">
         <v>84</v>
@@ -19400,24 +19538,24 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>781</v>
+        <v>777</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>725</v>
+        <v>699</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
-        <v>84</v>
+        <v>180</v>
       </c>
       <c r="E132" s="2"/>
       <c r="F132" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G132" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H132" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="I132" t="s" s="2">
         <v>84</v>
@@ -19426,20 +19564,18 @@
         <v>84</v>
       </c>
       <c r="K132" t="s" s="2">
-        <v>171</v>
+        <v>139</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>726</v>
+        <v>198</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>727</v>
+        <v>199</v>
       </c>
       <c r="N132" t="s" s="2">
-        <v>728</v>
-      </c>
-      <c r="O132" t="s" s="2">
-        <v>558</v>
-      </c>
+        <v>183</v>
+      </c>
+      <c r="O132" s="2"/>
       <c r="P132" t="s" s="2">
         <v>84</v>
       </c>
@@ -19463,13 +19599,13 @@
         <v>84</v>
       </c>
       <c r="X132" t="s" s="2">
-        <v>214</v>
+        <v>84</v>
       </c>
       <c r="Y132" t="s" s="2">
-        <v>559</v>
+        <v>84</v>
       </c>
       <c r="Z132" t="s" s="2">
-        <v>560</v>
+        <v>84</v>
       </c>
       <c r="AA132" t="s" s="2">
         <v>84</v>
@@ -19487,19 +19623,19 @@
         <v>84</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>725</v>
+        <v>161</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH132" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI132" t="s" s="2">
-        <v>729</v>
+        <v>84</v>
       </c>
       <c r="AJ132" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK132" t="s" s="2">
         <v>84</v>
@@ -19514,10 +19650,10 @@
         <v>84</v>
       </c>
       <c r="AO132" t="s" s="2">
-        <v>137</v>
+        <v>84</v>
       </c>
       <c r="AP132" t="s" s="2">
-        <v>563</v>
+        <v>157</v>
       </c>
       <c r="AQ132" t="s" s="2">
         <v>84</v>
@@ -19528,14 +19664,14 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>782</v>
+        <v>778</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>731</v>
+        <v>700</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
-        <v>565</v>
+        <v>634</v>
       </c>
       <c r="E133" s="2"/>
       <c r="F133" t="s" s="2">
@@ -19548,25 +19684,25 @@
         <v>84</v>
       </c>
       <c r="I133" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="J133" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K133" t="s" s="2">
-        <v>171</v>
+        <v>139</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>566</v>
+        <v>635</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>567</v>
+        <v>636</v>
       </c>
       <c r="N133" t="s" s="2">
-        <v>568</v>
+        <v>183</v>
       </c>
       <c r="O133" t="s" s="2">
-        <v>569</v>
+        <v>184</v>
       </c>
       <c r="P133" t="s" s="2">
         <v>84</v>
@@ -19591,13 +19727,13 @@
         <v>84</v>
       </c>
       <c r="X133" t="s" s="2">
-        <v>214</v>
+        <v>84</v>
       </c>
       <c r="Y133" t="s" s="2">
-        <v>570</v>
+        <v>84</v>
       </c>
       <c r="Z133" t="s" s="2">
-        <v>571</v>
+        <v>84</v>
       </c>
       <c r="AA133" t="s" s="2">
         <v>84</v>
@@ -19615,7 +19751,7 @@
         <v>84</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>731</v>
+        <v>637</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>82</v>
@@ -19627,7 +19763,7 @@
         <v>84</v>
       </c>
       <c r="AJ133" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK133" t="s" s="2">
         <v>84</v>
@@ -19639,27 +19775,27 @@
         <v>84</v>
       </c>
       <c r="AN133" t="s" s="2">
-        <v>572</v>
+        <v>84</v>
       </c>
       <c r="AO133" t="s" s="2">
-        <v>573</v>
+        <v>84</v>
       </c>
       <c r="AP133" t="s" s="2">
-        <v>574</v>
+        <v>137</v>
       </c>
       <c r="AQ133" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR133" t="s" s="2">
-        <v>575</v>
+        <v>84</v>
       </c>
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>783</v>
+        <v>779</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>732</v>
+        <v>701</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -19667,34 +19803,34 @@
       </c>
       <c r="E134" s="2"/>
       <c r="F134" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="G134" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H134" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I134" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J134" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K134" t="s" s="2">
-        <v>85</v>
+        <v>171</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>733</v>
+        <v>702</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>734</v>
+        <v>703</v>
       </c>
       <c r="N134" t="s" s="2">
-        <v>626</v>
+        <v>704</v>
       </c>
       <c r="O134" t="s" s="2">
-        <v>627</v>
+        <v>705</v>
       </c>
       <c r="P134" t="s" s="2">
         <v>84</v>
@@ -19719,13 +19855,13 @@
         <v>84</v>
       </c>
       <c r="X134" t="s" s="2">
-        <v>84</v>
+        <v>214</v>
       </c>
       <c r="Y134" t="s" s="2">
-        <v>84</v>
+        <v>375</v>
       </c>
       <c r="Z134" t="s" s="2">
-        <v>84</v>
+        <v>376</v>
       </c>
       <c r="AA134" t="s" s="2">
         <v>84</v>
@@ -19743,13 +19879,13 @@
         <v>84</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>732</v>
+        <v>701</v>
       </c>
       <c r="AG134" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AH134" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI134" t="s" s="2">
         <v>84</v>
@@ -19767,23 +19903,4727 @@
         <v>84</v>
       </c>
       <c r="AN134" t="s" s="2">
-        <v>84</v>
+        <v>706</v>
       </c>
       <c r="AO134" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="AP134" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="AQ134" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="AR134" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="135" hidden="true">
+      <c r="A135" t="s" s="2">
+        <v>780</v>
+      </c>
+      <c r="B135" t="s" s="2">
+        <v>707</v>
+      </c>
+      <c r="C135" s="2"/>
+      <c r="D135" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E135" s="2"/>
+      <c r="F135" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G135" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H135" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="I135" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J135" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K135" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="L135" t="s" s="2">
+        <v>708</v>
+      </c>
+      <c r="M135" t="s" s="2">
+        <v>709</v>
+      </c>
+      <c r="N135" t="s" s="2">
+        <v>710</v>
+      </c>
+      <c r="O135" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="P135" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q135" s="2"/>
+      <c r="R135" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S135" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T135" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U135" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V135" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W135" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X135" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="Y135" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="Z135" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="AA135" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB135" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="AC135" s="2"/>
+      <c r="AD135" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE135" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="AF135" t="s" s="2">
+        <v>707</v>
+      </c>
+      <c r="AG135" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH135" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI135" t="s" s="2">
+        <v>711</v>
+      </c>
+      <c r="AJ135" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK135" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL135" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM135" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN135" t="s" s="2">
+        <v>712</v>
+      </c>
+      <c r="AO135" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="AP135" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="AQ135" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR135" t="s" s="2">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="136" hidden="true">
+      <c r="A136" t="s" s="2">
+        <v>781</v>
+      </c>
+      <c r="B136" t="s" s="2">
+        <v>707</v>
+      </c>
+      <c r="C136" t="s" s="2">
+        <v>782</v>
+      </c>
+      <c r="D136" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E136" s="2"/>
+      <c r="F136" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G136" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H136" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="I136" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J136" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K136" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="L136" t="s" s="2">
+        <v>708</v>
+      </c>
+      <c r="M136" t="s" s="2">
+        <v>709</v>
+      </c>
+      <c r="N136" t="s" s="2">
+        <v>710</v>
+      </c>
+      <c r="O136" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="P136" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q136" s="2"/>
+      <c r="R136" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S136" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T136" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U136" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V136" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W136" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X136" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="Y136" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="Z136" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="AA136" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB136" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC136" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD136" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE136" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF136" t="s" s="2">
+        <v>707</v>
+      </c>
+      <c r="AG136" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH136" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI136" t="s" s="2">
+        <v>711</v>
+      </c>
+      <c r="AJ136" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK136" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL136" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM136" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN136" t="s" s="2">
+        <v>712</v>
+      </c>
+      <c r="AO136" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="AP136" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="AQ136" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR136" t="s" s="2">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="137" hidden="true">
+      <c r="A137" t="s" s="2">
+        <v>783</v>
+      </c>
+      <c r="B137" t="s" s="2">
+        <v>734</v>
+      </c>
+      <c r="C137" s="2"/>
+      <c r="D137" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E137" s="2"/>
+      <c r="F137" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G137" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H137" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I137" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J137" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="K137" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="L137" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="M137" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="N137" s="2"/>
+      <c r="O137" s="2"/>
+      <c r="P137" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q137" s="2"/>
+      <c r="R137" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S137" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T137" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U137" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V137" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W137" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X137" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y137" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z137" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA137" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB137" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC137" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD137" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE137" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF137" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="AG137" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH137" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI137" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ137" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AK137" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL137" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM137" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN137" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO137" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP137" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="AQ137" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR137" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="138" hidden="true">
+      <c r="A138" t="s" s="2">
+        <v>784</v>
+      </c>
+      <c r="B138" t="s" s="2">
+        <v>736</v>
+      </c>
+      <c r="C138" s="2"/>
+      <c r="D138" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="E138" s="2"/>
+      <c r="F138" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G138" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H138" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I138" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J138" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="K138" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="L138" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="M138" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="N138" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="O138" s="2"/>
+      <c r="P138" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q138" s="2"/>
+      <c r="R138" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S138" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T138" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U138" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V138" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W138" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X138" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y138" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z138" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA138" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB138" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="AC138" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="AD138" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE138" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="AF138" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="AG138" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH138" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI138" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ138" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="AK138" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL138" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM138" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN138" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO138" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP138" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="AQ138" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR138" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="139" hidden="true">
+      <c r="A139" t="s" s="2">
+        <v>785</v>
+      </c>
+      <c r="B139" t="s" s="2">
+        <v>786</v>
+      </c>
+      <c r="C139" s="2"/>
+      <c r="D139" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E139" s="2"/>
+      <c r="F139" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G139" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H139" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="I139" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J139" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K139" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="L139" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="M139" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="N139" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="O139" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="P139" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q139" s="2"/>
+      <c r="R139" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S139" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T139" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U139" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V139" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W139" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X139" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="Y139" s="2"/>
+      <c r="Z139" t="s" s="2">
+        <v>787</v>
+      </c>
+      <c r="AA139" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB139" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC139" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD139" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE139" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF139" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="AG139" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH139" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI139" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ139" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK139" t="s" s="2">
+        <v>788</v>
+      </c>
+      <c r="AL139" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM139" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN139" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO139" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="AP139" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="AQ139" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR139" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="140" hidden="true">
+      <c r="A140" t="s" s="2">
+        <v>789</v>
+      </c>
+      <c r="B140" t="s" s="2">
+        <v>790</v>
+      </c>
+      <c r="C140" s="2"/>
+      <c r="D140" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E140" s="2"/>
+      <c r="F140" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G140" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H140" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I140" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J140" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K140" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="L140" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="M140" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="N140" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="O140" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="P140" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q140" s="2"/>
+      <c r="R140" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S140" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T140" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U140" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V140" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W140" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X140" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y140" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z140" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA140" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB140" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC140" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD140" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE140" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF140" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="AG140" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH140" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI140" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ140" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK140" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL140" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM140" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN140" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO140" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="AP140" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="AQ140" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR140" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="141" hidden="true">
+      <c r="A141" t="s" s="2">
+        <v>791</v>
+      </c>
+      <c r="B141" t="s" s="2">
+        <v>713</v>
+      </c>
+      <c r="C141" s="2"/>
+      <c r="D141" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E141" s="2"/>
+      <c r="F141" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G141" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H141" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="I141" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J141" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="K141" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="L141" t="s" s="2">
+        <v>714</v>
+      </c>
+      <c r="M141" t="s" s="2">
+        <v>715</v>
+      </c>
+      <c r="N141" t="s" s="2">
+        <v>716</v>
+      </c>
+      <c r="O141" t="s" s="2">
+        <v>558</v>
+      </c>
+      <c r="P141" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q141" s="2"/>
+      <c r="R141" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S141" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T141" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U141" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V141" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W141" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X141" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="Y141" t="s" s="2">
+        <v>559</v>
+      </c>
+      <c r="Z141" t="s" s="2">
+        <v>560</v>
+      </c>
+      <c r="AA141" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB141" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC141" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD141" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE141" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF141" t="s" s="2">
+        <v>713</v>
+      </c>
+      <c r="AG141" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH141" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI141" t="s" s="2">
+        <v>717</v>
+      </c>
+      <c r="AJ141" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK141" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL141" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM141" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN141" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO141" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="AP141" t="s" s="2">
+        <v>563</v>
+      </c>
+      <c r="AQ141" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR141" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="142" hidden="true">
+      <c r="A142" t="s" s="2">
+        <v>792</v>
+      </c>
+      <c r="B142" t="s" s="2">
+        <v>719</v>
+      </c>
+      <c r="C142" s="2"/>
+      <c r="D142" t="s" s="2">
+        <v>565</v>
+      </c>
+      <c r="E142" s="2"/>
+      <c r="F142" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G142" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H142" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I142" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J142" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="K142" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="L142" t="s" s="2">
+        <v>566</v>
+      </c>
+      <c r="M142" t="s" s="2">
+        <v>567</v>
+      </c>
+      <c r="N142" t="s" s="2">
+        <v>568</v>
+      </c>
+      <c r="O142" t="s" s="2">
+        <v>569</v>
+      </c>
+      <c r="P142" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q142" s="2"/>
+      <c r="R142" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S142" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T142" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U142" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V142" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W142" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X142" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="Y142" t="s" s="2">
+        <v>570</v>
+      </c>
+      <c r="Z142" t="s" s="2">
+        <v>571</v>
+      </c>
+      <c r="AA142" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB142" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC142" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD142" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE142" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF142" t="s" s="2">
+        <v>719</v>
+      </c>
+      <c r="AG142" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH142" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI142" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ142" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK142" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL142" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM142" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN142" t="s" s="2">
+        <v>572</v>
+      </c>
+      <c r="AO142" t="s" s="2">
+        <v>573</v>
+      </c>
+      <c r="AP142" t="s" s="2">
+        <v>574</v>
+      </c>
+      <c r="AQ142" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR142" t="s" s="2">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="143" hidden="true">
+      <c r="A143" t="s" s="2">
+        <v>793</v>
+      </c>
+      <c r="B143" t="s" s="2">
+        <v>720</v>
+      </c>
+      <c r="C143" s="2"/>
+      <c r="D143" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E143" s="2"/>
+      <c r="F143" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G143" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H143" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I143" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J143" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="K143" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="L143" t="s" s="2">
+        <v>721</v>
+      </c>
+      <c r="M143" t="s" s="2">
+        <v>722</v>
+      </c>
+      <c r="N143" t="s" s="2">
+        <v>626</v>
+      </c>
+      <c r="O143" t="s" s="2">
+        <v>627</v>
+      </c>
+      <c r="P143" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q143" s="2"/>
+      <c r="R143" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S143" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T143" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U143" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V143" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W143" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X143" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y143" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z143" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA143" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB143" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC143" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD143" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE143" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF143" t="s" s="2">
+        <v>720</v>
+      </c>
+      <c r="AG143" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH143" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI143" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ143" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK143" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL143" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM143" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN143" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO143" t="s" s="2">
         <v>629</v>
       </c>
-      <c r="AP134" t="s" s="2">
+      <c r="AP143" t="s" s="2">
         <v>630</v>
       </c>
-      <c r="AQ134" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR134" t="s" s="2">
+      <c r="AQ143" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR143" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="144" hidden="true">
+      <c r="A144" t="s" s="2">
+        <v>794</v>
+      </c>
+      <c r="B144" t="s" s="2">
+        <v>688</v>
+      </c>
+      <c r="C144" t="s" s="2">
+        <v>795</v>
+      </c>
+      <c r="D144" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E144" s="2"/>
+      <c r="F144" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G144" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H144" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="I144" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J144" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K144" t="s" s="2">
+        <v>623</v>
+      </c>
+      <c r="L144" t="s" s="2">
+        <v>690</v>
+      </c>
+      <c r="M144" t="s" s="2">
+        <v>691</v>
+      </c>
+      <c r="N144" t="s" s="2">
+        <v>692</v>
+      </c>
+      <c r="O144" t="s" s="2">
+        <v>693</v>
+      </c>
+      <c r="P144" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q144" s="2"/>
+      <c r="R144" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S144" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T144" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U144" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V144" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W144" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X144" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y144" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z144" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA144" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB144" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC144" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD144" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE144" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF144" t="s" s="2">
+        <v>688</v>
+      </c>
+      <c r="AG144" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH144" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI144" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ144" t="s" s="2">
+        <v>695</v>
+      </c>
+      <c r="AK144" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL144" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM144" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN144" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO144" t="s" s="2">
+        <v>696</v>
+      </c>
+      <c r="AP144" t="s" s="2">
+        <v>697</v>
+      </c>
+      <c r="AQ144" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR144" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="145" hidden="true">
+      <c r="A145" t="s" s="2">
+        <v>796</v>
+      </c>
+      <c r="B145" t="s" s="2">
+        <v>698</v>
+      </c>
+      <c r="C145" s="2"/>
+      <c r="D145" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E145" s="2"/>
+      <c r="F145" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G145" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H145" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I145" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J145" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="K145" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="L145" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="M145" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="N145" s="2"/>
+      <c r="O145" s="2"/>
+      <c r="P145" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q145" s="2"/>
+      <c r="R145" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S145" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T145" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U145" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V145" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W145" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X145" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y145" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z145" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA145" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB145" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC145" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD145" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE145" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF145" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="AG145" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH145" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI145" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ145" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AK145" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL145" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM145" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN145" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO145" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP145" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="AQ145" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR145" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="146" hidden="true">
+      <c r="A146" t="s" s="2">
+        <v>797</v>
+      </c>
+      <c r="B146" t="s" s="2">
+        <v>699</v>
+      </c>
+      <c r="C146" s="2"/>
+      <c r="D146" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="E146" s="2"/>
+      <c r="F146" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G146" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H146" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I146" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J146" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="K146" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="L146" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="M146" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="N146" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="O146" s="2"/>
+      <c r="P146" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q146" s="2"/>
+      <c r="R146" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S146" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T146" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U146" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V146" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W146" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X146" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y146" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z146" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA146" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB146" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC146" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD146" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE146" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF146" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="AG146" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH146" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI146" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ146" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="AK146" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL146" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM146" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN146" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO146" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP146" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="AQ146" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR146" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="147" hidden="true">
+      <c r="A147" t="s" s="2">
+        <v>798</v>
+      </c>
+      <c r="B147" t="s" s="2">
+        <v>700</v>
+      </c>
+      <c r="C147" s="2"/>
+      <c r="D147" t="s" s="2">
+        <v>634</v>
+      </c>
+      <c r="E147" s="2"/>
+      <c r="F147" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G147" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H147" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I147" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="J147" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K147" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="L147" t="s" s="2">
+        <v>635</v>
+      </c>
+      <c r="M147" t="s" s="2">
+        <v>636</v>
+      </c>
+      <c r="N147" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="O147" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="P147" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q147" s="2"/>
+      <c r="R147" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S147" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T147" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U147" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V147" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W147" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X147" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y147" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z147" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA147" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB147" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC147" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD147" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE147" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF147" t="s" s="2">
+        <v>637</v>
+      </c>
+      <c r="AG147" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH147" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI147" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ147" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="AK147" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL147" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM147" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN147" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO147" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP147" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="AQ147" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR147" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="148" hidden="true">
+      <c r="A148" t="s" s="2">
+        <v>799</v>
+      </c>
+      <c r="B148" t="s" s="2">
+        <v>701</v>
+      </c>
+      <c r="C148" s="2"/>
+      <c r="D148" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E148" s="2"/>
+      <c r="F148" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="G148" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H148" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="I148" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J148" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K148" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="L148" t="s" s="2">
+        <v>702</v>
+      </c>
+      <c r="M148" t="s" s="2">
+        <v>703</v>
+      </c>
+      <c r="N148" t="s" s="2">
+        <v>704</v>
+      </c>
+      <c r="O148" t="s" s="2">
+        <v>705</v>
+      </c>
+      <c r="P148" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q148" s="2"/>
+      <c r="R148" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S148" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T148" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U148" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V148" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W148" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X148" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="Y148" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="Z148" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="AA148" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB148" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC148" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD148" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE148" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF148" t="s" s="2">
+        <v>701</v>
+      </c>
+      <c r="AG148" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AH148" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI148" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ148" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK148" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL148" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM148" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN148" t="s" s="2">
+        <v>706</v>
+      </c>
+      <c r="AO148" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="AP148" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="AQ148" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="AR148" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="149" hidden="true">
+      <c r="A149" t="s" s="2">
+        <v>800</v>
+      </c>
+      <c r="B149" t="s" s="2">
+        <v>707</v>
+      </c>
+      <c r="C149" s="2"/>
+      <c r="D149" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E149" s="2"/>
+      <c r="F149" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G149" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H149" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="I149" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J149" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K149" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="L149" t="s" s="2">
+        <v>708</v>
+      </c>
+      <c r="M149" t="s" s="2">
+        <v>709</v>
+      </c>
+      <c r="N149" t="s" s="2">
+        <v>710</v>
+      </c>
+      <c r="O149" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="P149" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q149" s="2"/>
+      <c r="R149" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S149" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T149" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U149" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V149" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W149" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X149" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="Y149" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="Z149" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="AA149" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB149" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="AC149" s="2"/>
+      <c r="AD149" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE149" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="AF149" t="s" s="2">
+        <v>707</v>
+      </c>
+      <c r="AG149" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH149" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI149" t="s" s="2">
+        <v>711</v>
+      </c>
+      <c r="AJ149" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK149" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL149" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM149" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN149" t="s" s="2">
+        <v>712</v>
+      </c>
+      <c r="AO149" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="AP149" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="AQ149" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR149" t="s" s="2">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="150" hidden="true">
+      <c r="A150" t="s" s="2">
+        <v>801</v>
+      </c>
+      <c r="B150" t="s" s="2">
+        <v>707</v>
+      </c>
+      <c r="C150" t="s" s="2">
+        <v>782</v>
+      </c>
+      <c r="D150" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E150" s="2"/>
+      <c r="F150" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G150" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H150" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="I150" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J150" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K150" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="L150" t="s" s="2">
+        <v>708</v>
+      </c>
+      <c r="M150" t="s" s="2">
+        <v>709</v>
+      </c>
+      <c r="N150" t="s" s="2">
+        <v>710</v>
+      </c>
+      <c r="O150" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="P150" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q150" s="2"/>
+      <c r="R150" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S150" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T150" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U150" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V150" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W150" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X150" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="Y150" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="Z150" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="AA150" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB150" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC150" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD150" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE150" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF150" t="s" s="2">
+        <v>707</v>
+      </c>
+      <c r="AG150" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH150" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI150" t="s" s="2">
+        <v>711</v>
+      </c>
+      <c r="AJ150" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK150" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL150" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM150" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN150" t="s" s="2">
+        <v>712</v>
+      </c>
+      <c r="AO150" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="AP150" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="AQ150" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR150" t="s" s="2">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="151" hidden="true">
+      <c r="A151" t="s" s="2">
+        <v>802</v>
+      </c>
+      <c r="B151" t="s" s="2">
+        <v>734</v>
+      </c>
+      <c r="C151" s="2"/>
+      <c r="D151" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E151" s="2"/>
+      <c r="F151" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G151" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H151" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I151" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J151" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="K151" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="L151" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="M151" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="N151" s="2"/>
+      <c r="O151" s="2"/>
+      <c r="P151" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q151" s="2"/>
+      <c r="R151" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S151" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T151" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U151" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V151" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W151" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X151" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y151" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z151" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA151" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB151" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC151" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD151" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE151" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF151" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="AG151" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH151" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI151" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ151" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AK151" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL151" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM151" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN151" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO151" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP151" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="AQ151" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR151" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="152" hidden="true">
+      <c r="A152" t="s" s="2">
+        <v>803</v>
+      </c>
+      <c r="B152" t="s" s="2">
+        <v>736</v>
+      </c>
+      <c r="C152" s="2"/>
+      <c r="D152" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="E152" s="2"/>
+      <c r="F152" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G152" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H152" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I152" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J152" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="K152" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="L152" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="M152" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="N152" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="O152" s="2"/>
+      <c r="P152" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q152" s="2"/>
+      <c r="R152" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S152" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T152" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U152" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V152" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W152" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X152" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y152" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z152" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA152" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB152" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="AC152" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="AD152" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE152" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="AF152" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="AG152" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH152" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI152" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ152" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="AK152" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL152" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM152" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN152" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO152" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP152" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="AQ152" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR152" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="153" hidden="true">
+      <c r="A153" t="s" s="2">
+        <v>804</v>
+      </c>
+      <c r="B153" t="s" s="2">
+        <v>786</v>
+      </c>
+      <c r="C153" s="2"/>
+      <c r="D153" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E153" s="2"/>
+      <c r="F153" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G153" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H153" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="I153" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J153" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K153" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="L153" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="M153" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="N153" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="O153" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="P153" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q153" s="2"/>
+      <c r="R153" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S153" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T153" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U153" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V153" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W153" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X153" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="Y153" s="2"/>
+      <c r="Z153" t="s" s="2">
+        <v>805</v>
+      </c>
+      <c r="AA153" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB153" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC153" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD153" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE153" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF153" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="AG153" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH153" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI153" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ153" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK153" t="s" s="2">
+        <v>806</v>
+      </c>
+      <c r="AL153" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM153" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN153" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO153" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="AP153" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="AQ153" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR153" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="154" hidden="true">
+      <c r="A154" t="s" s="2">
+        <v>807</v>
+      </c>
+      <c r="B154" t="s" s="2">
+        <v>790</v>
+      </c>
+      <c r="C154" s="2"/>
+      <c r="D154" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E154" s="2"/>
+      <c r="F154" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G154" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H154" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I154" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J154" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K154" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="L154" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="M154" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="N154" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="O154" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="P154" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q154" s="2"/>
+      <c r="R154" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S154" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T154" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U154" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V154" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W154" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X154" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y154" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z154" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA154" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB154" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC154" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD154" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE154" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF154" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="AG154" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH154" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI154" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ154" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK154" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL154" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM154" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN154" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO154" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="AP154" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="AQ154" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR154" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="155" hidden="true">
+      <c r="A155" t="s" s="2">
+        <v>808</v>
+      </c>
+      <c r="B155" t="s" s="2">
+        <v>713</v>
+      </c>
+      <c r="C155" s="2"/>
+      <c r="D155" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E155" s="2"/>
+      <c r="F155" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G155" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H155" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="I155" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J155" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="K155" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="L155" t="s" s="2">
+        <v>714</v>
+      </c>
+      <c r="M155" t="s" s="2">
+        <v>715</v>
+      </c>
+      <c r="N155" t="s" s="2">
+        <v>716</v>
+      </c>
+      <c r="O155" t="s" s="2">
+        <v>558</v>
+      </c>
+      <c r="P155" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q155" s="2"/>
+      <c r="R155" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S155" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T155" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U155" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V155" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W155" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X155" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="Y155" t="s" s="2">
+        <v>559</v>
+      </c>
+      <c r="Z155" t="s" s="2">
+        <v>560</v>
+      </c>
+      <c r="AA155" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB155" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC155" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD155" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE155" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF155" t="s" s="2">
+        <v>713</v>
+      </c>
+      <c r="AG155" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH155" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI155" t="s" s="2">
+        <v>717</v>
+      </c>
+      <c r="AJ155" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK155" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL155" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM155" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN155" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO155" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="AP155" t="s" s="2">
+        <v>563</v>
+      </c>
+      <c r="AQ155" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR155" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="156" hidden="true">
+      <c r="A156" t="s" s="2">
+        <v>809</v>
+      </c>
+      <c r="B156" t="s" s="2">
+        <v>719</v>
+      </c>
+      <c r="C156" s="2"/>
+      <c r="D156" t="s" s="2">
+        <v>565</v>
+      </c>
+      <c r="E156" s="2"/>
+      <c r="F156" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G156" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H156" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I156" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J156" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="K156" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="L156" t="s" s="2">
+        <v>566</v>
+      </c>
+      <c r="M156" t="s" s="2">
+        <v>567</v>
+      </c>
+      <c r="N156" t="s" s="2">
+        <v>568</v>
+      </c>
+      <c r="O156" t="s" s="2">
+        <v>569</v>
+      </c>
+      <c r="P156" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q156" s="2"/>
+      <c r="R156" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S156" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T156" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U156" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V156" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W156" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X156" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="Y156" t="s" s="2">
+        <v>570</v>
+      </c>
+      <c r="Z156" t="s" s="2">
+        <v>571</v>
+      </c>
+      <c r="AA156" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB156" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC156" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD156" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE156" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF156" t="s" s="2">
+        <v>719</v>
+      </c>
+      <c r="AG156" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH156" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI156" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ156" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK156" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL156" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM156" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN156" t="s" s="2">
+        <v>572</v>
+      </c>
+      <c r="AO156" t="s" s="2">
+        <v>573</v>
+      </c>
+      <c r="AP156" t="s" s="2">
+        <v>574</v>
+      </c>
+      <c r="AQ156" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR156" t="s" s="2">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="157" hidden="true">
+      <c r="A157" t="s" s="2">
+        <v>810</v>
+      </c>
+      <c r="B157" t="s" s="2">
+        <v>720</v>
+      </c>
+      <c r="C157" s="2"/>
+      <c r="D157" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E157" s="2"/>
+      <c r="F157" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G157" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H157" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I157" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J157" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="K157" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="L157" t="s" s="2">
+        <v>721</v>
+      </c>
+      <c r="M157" t="s" s="2">
+        <v>722</v>
+      </c>
+      <c r="N157" t="s" s="2">
+        <v>626</v>
+      </c>
+      <c r="O157" t="s" s="2">
+        <v>627</v>
+      </c>
+      <c r="P157" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q157" s="2"/>
+      <c r="R157" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S157" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T157" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U157" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V157" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W157" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X157" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y157" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z157" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA157" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB157" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC157" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD157" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE157" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF157" t="s" s="2">
+        <v>720</v>
+      </c>
+      <c r="AG157" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH157" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI157" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ157" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK157" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL157" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM157" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN157" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO157" t="s" s="2">
+        <v>629</v>
+      </c>
+      <c r="AP157" t="s" s="2">
+        <v>630</v>
+      </c>
+      <c r="AQ157" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR157" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="158" hidden="true">
+      <c r="A158" t="s" s="2">
+        <v>811</v>
+      </c>
+      <c r="B158" t="s" s="2">
+        <v>688</v>
+      </c>
+      <c r="C158" t="s" s="2">
+        <v>812</v>
+      </c>
+      <c r="D158" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E158" s="2"/>
+      <c r="F158" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G158" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H158" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="I158" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J158" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K158" t="s" s="2">
+        <v>623</v>
+      </c>
+      <c r="L158" t="s" s="2">
+        <v>690</v>
+      </c>
+      <c r="M158" t="s" s="2">
+        <v>691</v>
+      </c>
+      <c r="N158" t="s" s="2">
+        <v>692</v>
+      </c>
+      <c r="O158" t="s" s="2">
+        <v>693</v>
+      </c>
+      <c r="P158" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q158" s="2"/>
+      <c r="R158" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S158" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T158" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U158" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V158" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W158" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X158" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y158" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z158" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA158" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB158" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC158" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD158" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE158" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF158" t="s" s="2">
+        <v>688</v>
+      </c>
+      <c r="AG158" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH158" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI158" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ158" t="s" s="2">
+        <v>695</v>
+      </c>
+      <c r="AK158" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL158" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM158" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN158" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO158" t="s" s="2">
+        <v>696</v>
+      </c>
+      <c r="AP158" t="s" s="2">
+        <v>697</v>
+      </c>
+      <c r="AQ158" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR158" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="159" hidden="true">
+      <c r="A159" t="s" s="2">
+        <v>813</v>
+      </c>
+      <c r="B159" t="s" s="2">
+        <v>698</v>
+      </c>
+      <c r="C159" s="2"/>
+      <c r="D159" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E159" s="2"/>
+      <c r="F159" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G159" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H159" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I159" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J159" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="K159" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="L159" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="M159" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="N159" s="2"/>
+      <c r="O159" s="2"/>
+      <c r="P159" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q159" s="2"/>
+      <c r="R159" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S159" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T159" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U159" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V159" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W159" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X159" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y159" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z159" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA159" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB159" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC159" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD159" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE159" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF159" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="AG159" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH159" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI159" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ159" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AK159" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL159" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM159" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN159" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO159" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP159" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="AQ159" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR159" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="160" hidden="true">
+      <c r="A160" t="s" s="2">
+        <v>814</v>
+      </c>
+      <c r="B160" t="s" s="2">
+        <v>699</v>
+      </c>
+      <c r="C160" s="2"/>
+      <c r="D160" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="E160" s="2"/>
+      <c r="F160" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G160" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H160" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I160" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J160" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="K160" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="L160" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="M160" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="N160" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="O160" s="2"/>
+      <c r="P160" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q160" s="2"/>
+      <c r="R160" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S160" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T160" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U160" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V160" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W160" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X160" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y160" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z160" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA160" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB160" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC160" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD160" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE160" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF160" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="AG160" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH160" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI160" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ160" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="AK160" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL160" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM160" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN160" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO160" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP160" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="AQ160" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR160" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="161" hidden="true">
+      <c r="A161" t="s" s="2">
+        <v>815</v>
+      </c>
+      <c r="B161" t="s" s="2">
+        <v>700</v>
+      </c>
+      <c r="C161" s="2"/>
+      <c r="D161" t="s" s="2">
+        <v>634</v>
+      </c>
+      <c r="E161" s="2"/>
+      <c r="F161" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G161" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H161" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I161" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="J161" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K161" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="L161" t="s" s="2">
+        <v>635</v>
+      </c>
+      <c r="M161" t="s" s="2">
+        <v>636</v>
+      </c>
+      <c r="N161" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="O161" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="P161" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q161" s="2"/>
+      <c r="R161" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S161" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T161" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U161" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V161" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W161" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X161" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y161" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z161" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA161" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB161" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC161" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD161" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE161" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF161" t="s" s="2">
+        <v>637</v>
+      </c>
+      <c r="AG161" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH161" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI161" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ161" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="AK161" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL161" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM161" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN161" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO161" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP161" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="AQ161" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR161" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="162" hidden="true">
+      <c r="A162" t="s" s="2">
+        <v>816</v>
+      </c>
+      <c r="B162" t="s" s="2">
+        <v>701</v>
+      </c>
+      <c r="C162" s="2"/>
+      <c r="D162" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E162" s="2"/>
+      <c r="F162" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="G162" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H162" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="I162" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J162" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K162" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="L162" t="s" s="2">
+        <v>702</v>
+      </c>
+      <c r="M162" t="s" s="2">
+        <v>703</v>
+      </c>
+      <c r="N162" t="s" s="2">
+        <v>704</v>
+      </c>
+      <c r="O162" t="s" s="2">
+        <v>705</v>
+      </c>
+      <c r="P162" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q162" s="2"/>
+      <c r="R162" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S162" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T162" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U162" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V162" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W162" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X162" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="Y162" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="Z162" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="AA162" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB162" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC162" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD162" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE162" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF162" t="s" s="2">
+        <v>701</v>
+      </c>
+      <c r="AG162" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AH162" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI162" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ162" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK162" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL162" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM162" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN162" t="s" s="2">
+        <v>706</v>
+      </c>
+      <c r="AO162" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="AP162" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="AQ162" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="AR162" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="163" hidden="true">
+      <c r="A163" t="s" s="2">
+        <v>817</v>
+      </c>
+      <c r="B163" t="s" s="2">
+        <v>707</v>
+      </c>
+      <c r="C163" s="2"/>
+      <c r="D163" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E163" s="2"/>
+      <c r="F163" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G163" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H163" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="I163" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J163" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K163" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="L163" t="s" s="2">
+        <v>708</v>
+      </c>
+      <c r="M163" t="s" s="2">
+        <v>709</v>
+      </c>
+      <c r="N163" t="s" s="2">
+        <v>710</v>
+      </c>
+      <c r="O163" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="P163" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q163" s="2"/>
+      <c r="R163" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S163" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T163" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U163" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V163" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W163" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X163" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="Y163" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="Z163" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="AA163" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB163" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="AC163" s="2"/>
+      <c r="AD163" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE163" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="AF163" t="s" s="2">
+        <v>707</v>
+      </c>
+      <c r="AG163" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH163" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI163" t="s" s="2">
+        <v>711</v>
+      </c>
+      <c r="AJ163" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK163" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL163" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM163" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN163" t="s" s="2">
+        <v>712</v>
+      </c>
+      <c r="AO163" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="AP163" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="AQ163" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR163" t="s" s="2">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="164" hidden="true">
+      <c r="A164" t="s" s="2">
+        <v>818</v>
+      </c>
+      <c r="B164" t="s" s="2">
+        <v>707</v>
+      </c>
+      <c r="C164" t="s" s="2">
+        <v>782</v>
+      </c>
+      <c r="D164" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E164" s="2"/>
+      <c r="F164" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G164" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H164" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="I164" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J164" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K164" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="L164" t="s" s="2">
+        <v>708</v>
+      </c>
+      <c r="M164" t="s" s="2">
+        <v>709</v>
+      </c>
+      <c r="N164" t="s" s="2">
+        <v>710</v>
+      </c>
+      <c r="O164" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="P164" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q164" s="2"/>
+      <c r="R164" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S164" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T164" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U164" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V164" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W164" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X164" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="Y164" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="Z164" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="AA164" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB164" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC164" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD164" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE164" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF164" t="s" s="2">
+        <v>707</v>
+      </c>
+      <c r="AG164" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH164" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI164" t="s" s="2">
+        <v>711</v>
+      </c>
+      <c r="AJ164" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK164" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL164" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM164" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN164" t="s" s="2">
+        <v>712</v>
+      </c>
+      <c r="AO164" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="AP164" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="AQ164" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR164" t="s" s="2">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="165" hidden="true">
+      <c r="A165" t="s" s="2">
+        <v>819</v>
+      </c>
+      <c r="B165" t="s" s="2">
+        <v>734</v>
+      </c>
+      <c r="C165" s="2"/>
+      <c r="D165" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E165" s="2"/>
+      <c r="F165" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G165" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H165" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I165" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J165" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="K165" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="L165" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="M165" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="N165" s="2"/>
+      <c r="O165" s="2"/>
+      <c r="P165" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q165" s="2"/>
+      <c r="R165" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S165" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T165" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U165" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V165" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W165" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X165" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y165" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z165" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA165" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB165" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC165" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD165" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE165" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF165" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="AG165" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH165" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI165" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ165" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AK165" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL165" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM165" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN165" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO165" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP165" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="AQ165" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR165" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="166" hidden="true">
+      <c r="A166" t="s" s="2">
+        <v>820</v>
+      </c>
+      <c r="B166" t="s" s="2">
+        <v>736</v>
+      </c>
+      <c r="C166" s="2"/>
+      <c r="D166" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="E166" s="2"/>
+      <c r="F166" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G166" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H166" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I166" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J166" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="K166" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="L166" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="M166" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="N166" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="O166" s="2"/>
+      <c r="P166" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q166" s="2"/>
+      <c r="R166" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S166" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T166" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U166" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V166" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W166" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X166" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y166" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z166" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA166" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB166" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="AC166" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="AD166" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE166" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="AF166" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="AG166" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH166" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI166" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ166" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="AK166" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL166" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM166" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN166" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO166" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP166" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="AQ166" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR166" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="167" hidden="true">
+      <c r="A167" t="s" s="2">
+        <v>821</v>
+      </c>
+      <c r="B167" t="s" s="2">
+        <v>786</v>
+      </c>
+      <c r="C167" s="2"/>
+      <c r="D167" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E167" s="2"/>
+      <c r="F167" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G167" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H167" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="I167" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J167" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K167" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="L167" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="M167" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="N167" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="O167" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="P167" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q167" s="2"/>
+      <c r="R167" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S167" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T167" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U167" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V167" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W167" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X167" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="Y167" s="2"/>
+      <c r="Z167" t="s" s="2">
+        <v>822</v>
+      </c>
+      <c r="AA167" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB167" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC167" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD167" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE167" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF167" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="AG167" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH167" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI167" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ167" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK167" t="s" s="2">
+        <v>823</v>
+      </c>
+      <c r="AL167" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM167" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN167" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO167" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="AP167" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="AQ167" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR167" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="168" hidden="true">
+      <c r="A168" t="s" s="2">
+        <v>824</v>
+      </c>
+      <c r="B168" t="s" s="2">
+        <v>790</v>
+      </c>
+      <c r="C168" s="2"/>
+      <c r="D168" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E168" s="2"/>
+      <c r="F168" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G168" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H168" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I168" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J168" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K168" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="L168" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="M168" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="N168" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="O168" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="P168" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q168" s="2"/>
+      <c r="R168" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S168" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T168" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U168" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V168" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W168" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X168" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y168" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z168" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA168" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB168" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC168" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD168" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE168" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF168" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="AG168" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH168" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI168" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ168" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK168" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL168" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM168" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN168" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO168" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="AP168" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="AQ168" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR168" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="169" hidden="true">
+      <c r="A169" t="s" s="2">
+        <v>825</v>
+      </c>
+      <c r="B169" t="s" s="2">
+        <v>713</v>
+      </c>
+      <c r="C169" s="2"/>
+      <c r="D169" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E169" s="2"/>
+      <c r="F169" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G169" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H169" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="I169" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J169" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="K169" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="L169" t="s" s="2">
+        <v>714</v>
+      </c>
+      <c r="M169" t="s" s="2">
+        <v>715</v>
+      </c>
+      <c r="N169" t="s" s="2">
+        <v>716</v>
+      </c>
+      <c r="O169" t="s" s="2">
+        <v>558</v>
+      </c>
+      <c r="P169" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q169" s="2"/>
+      <c r="R169" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S169" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T169" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U169" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V169" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W169" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X169" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="Y169" t="s" s="2">
+        <v>559</v>
+      </c>
+      <c r="Z169" t="s" s="2">
+        <v>560</v>
+      </c>
+      <c r="AA169" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB169" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC169" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD169" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE169" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF169" t="s" s="2">
+        <v>713</v>
+      </c>
+      <c r="AG169" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH169" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI169" t="s" s="2">
+        <v>717</v>
+      </c>
+      <c r="AJ169" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK169" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL169" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM169" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN169" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO169" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="AP169" t="s" s="2">
+        <v>563</v>
+      </c>
+      <c r="AQ169" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR169" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="170" hidden="true">
+      <c r="A170" t="s" s="2">
+        <v>826</v>
+      </c>
+      <c r="B170" t="s" s="2">
+        <v>719</v>
+      </c>
+      <c r="C170" s="2"/>
+      <c r="D170" t="s" s="2">
+        <v>565</v>
+      </c>
+      <c r="E170" s="2"/>
+      <c r="F170" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G170" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H170" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I170" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J170" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="K170" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="L170" t="s" s="2">
+        <v>566</v>
+      </c>
+      <c r="M170" t="s" s="2">
+        <v>567</v>
+      </c>
+      <c r="N170" t="s" s="2">
+        <v>568</v>
+      </c>
+      <c r="O170" t="s" s="2">
+        <v>569</v>
+      </c>
+      <c r="P170" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q170" s="2"/>
+      <c r="R170" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S170" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T170" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U170" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V170" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W170" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X170" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="Y170" t="s" s="2">
+        <v>570</v>
+      </c>
+      <c r="Z170" t="s" s="2">
+        <v>571</v>
+      </c>
+      <c r="AA170" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB170" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC170" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD170" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE170" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF170" t="s" s="2">
+        <v>719</v>
+      </c>
+      <c r="AG170" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH170" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI170" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ170" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK170" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL170" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM170" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN170" t="s" s="2">
+        <v>572</v>
+      </c>
+      <c r="AO170" t="s" s="2">
+        <v>573</v>
+      </c>
+      <c r="AP170" t="s" s="2">
+        <v>574</v>
+      </c>
+      <c r="AQ170" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR170" t="s" s="2">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="171" hidden="true">
+      <c r="A171" t="s" s="2">
+        <v>827</v>
+      </c>
+      <c r="B171" t="s" s="2">
+        <v>720</v>
+      </c>
+      <c r="C171" s="2"/>
+      <c r="D171" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E171" s="2"/>
+      <c r="F171" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G171" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H171" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I171" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J171" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="K171" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="L171" t="s" s="2">
+        <v>721</v>
+      </c>
+      <c r="M171" t="s" s="2">
+        <v>722</v>
+      </c>
+      <c r="N171" t="s" s="2">
+        <v>626</v>
+      </c>
+      <c r="O171" t="s" s="2">
+        <v>627</v>
+      </c>
+      <c r="P171" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q171" s="2"/>
+      <c r="R171" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S171" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T171" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U171" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V171" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W171" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X171" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y171" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z171" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA171" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB171" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC171" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD171" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE171" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF171" t="s" s="2">
+        <v>720</v>
+      </c>
+      <c r="AG171" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH171" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI171" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ171" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK171" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL171" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM171" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN171" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO171" t="s" s="2">
+        <v>629</v>
+      </c>
+      <c r="AP171" t="s" s="2">
+        <v>630</v>
+      </c>
+      <c r="AQ171" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR171" t="s" s="2">
         <v>84</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AR134">
+  <autoFilter ref="A1:AR171">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -19793,7 +24633,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI133">
+  <conditionalFormatting sqref="A2:AI170">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/docs/StructureDefinition-VitalSignsBPObservation.xlsx
+++ b/docs/StructureDefinition-VitalSignsBPObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.52.0</t>
+    <t>0.53.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-19T08:28:17+00:00</t>
+    <t>2024-05-22T14:44:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsBPObservation.xlsx
+++ b/docs/StructureDefinition-VitalSignsBPObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.53.0</t>
+    <t>0.54.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-22T14:44:53+00:00</t>
+    <t>2024-05-25T10:26:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -713,7 +713,7 @@
     <t>There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
   </si>
   <si>
-    <t>http://va.gov/fhir/identifiers/Sta3n&lt;stationNr&gt;/&lt;fileNr&gt;</t>
+    <t>http://va.gov/fhir/identifiers/Sta3n$stationNr/120.5</t>
   </si>
   <si>
     <t>http://www.acme.com/identifiers/patient</t>
@@ -722,7 +722,7 @@
     <t>Identifier.system</t>
   </si>
   <si>
-    <t>660-1: fixed value = http://va.gov/fhir/identifiers/Sta3n&lt;stationNr&gt;/&lt;fileNr&gt;</t>
+    <t>660-1: fixed value = http://va.gov/fhir/identifiers/Sta3n$stationNr/120.5</t>
   </si>
   <si>
     <t>CX.4 / EI-2-4</t>

--- a/docs/StructureDefinition-VitalSignsBPObservation.xlsx
+++ b/docs/StructureDefinition-VitalSignsBPObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.54.0</t>
+    <t>0.57.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-25T10:26:15+00:00</t>
+    <t>2024-06-04T15:52:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -713,7 +713,7 @@
     <t>There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
   </si>
   <si>
-    <t>http://va.gov/fhir/identifiers/Sta3n$stationNr/120.5</t>
+    <t>http://va.gov/identifiers/$Sta3n/120.5</t>
   </si>
   <si>
     <t>http://www.acme.com/identifiers/patient</t>
@@ -722,7 +722,7 @@
     <t>Identifier.system</t>
   </si>
   <si>
-    <t>660-1: fixed value = http://va.gov/fhir/identifiers/Sta3n$stationNr/120.5</t>
+    <t>660-1: fixed value = http://va.gov/identifiers/$Sta3n/120.5</t>
   </si>
   <si>
     <t>CX.4 / EI-2-4</t>

--- a/docs/StructureDefinition-VitalSignsBPObservation.xlsx
+++ b/docs/StructureDefinition-VitalSignsBPObservation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-04T15:52:07+00:00</t>
+    <t>2024-06-11T05:38:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsBPObservation.xlsx
+++ b/docs/StructureDefinition-VitalSignsBPObservation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-11T05:38:55+00:00</t>
+    <t>2024-06-12T18:51:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsBPObservation.xlsx
+++ b/docs/StructureDefinition-VitalSignsBPObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.57.0</t>
+    <t>0.58.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-12T18:51:20+00:00</t>
+    <t>2024-06-14T11:56:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsBPObservation.xlsx
+++ b/docs/StructureDefinition-VitalSignsBPObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.58.0</t>
+    <t>0.59.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-14T11:56:40+00:00</t>
+    <t>2024-06-21T15:05:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsBPObservation.xlsx
+++ b/docs/StructureDefinition-VitalSignsBPObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.59.0</t>
+    <t>0.61.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-09T16:26:13+00:00</t>
+    <t>2024-07-24T18:59:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsBPObservation.xlsx
+++ b/docs/StructureDefinition-VitalSignsBPObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.61.0</t>
+    <t>0.62.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-24T18:59:55+00:00</t>
+    <t>2024-07-28T09:11:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsBPObservation.xlsx
+++ b/docs/StructureDefinition-VitalSignsBPObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.62.0</t>
+    <t>0.63.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-28T09:11:13+00:00</t>
+    <t>2024-07-31T09:58:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsBPObservation.xlsx
+++ b/docs/StructureDefinition-VitalSignsBPObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.63.0</t>
+    <t>0.64.311</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-31T09:58:27+00:00</t>
+    <t>2024-07-31T19:09:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
